--- a/contract/sample-output.xlsx
+++ b/contract/sample-output.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="405">
   <si>
     <t>샘플 태양광 100MW</t>
   </si>
@@ -2809,7 +2809,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="49" spans="2:90" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="33" t="s">
         <v>178</v>
       </c>
@@ -3980,244 +3980,244 @@
         <f>J64*$D$56*100</f>
       </c>
       <c r="K8" s="31">
-        <f>K64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="L8" s="31">
-        <f>L64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="M8" s="31">
-        <f>M64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="N8" s="31">
-        <f>N64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="O8" s="31">
-        <f>O64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="P8" s="31">
-        <f>P64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="Q8" s="31">
-        <f>Q64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="R8" s="31">
-        <f>R64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="S8" s="31">
-        <f>S64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="T8" s="31">
-        <f>T64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="U8" s="31">
-        <f>U64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="V8" s="31">
-        <f>V64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="W8" s="31">
-        <f>W64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="X8" s="31">
-        <f>X64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="Y8" s="31">
-        <f>Y64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="Z8" s="31">
-        <f>Z64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AA8" s="31">
-        <f>AA64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AB8" s="31">
-        <f>AB64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AC8" s="31">
-        <f>AC64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AD8" s="31">
-        <f>AD64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AE8" s="31">
-        <f>AE64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AF8" s="31">
-        <f>AF64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AG8" s="31">
-        <f>AG64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AH8" s="31">
-        <f>AH64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AI8" s="31">
-        <f>AI64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AJ8" s="31">
-        <f>AJ64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AK8" s="31">
-        <f>AK64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AL8" s="31">
-        <f>AL64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AM8" s="31">
-        <f>AM64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AN8" s="31">
-        <f>AN64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AO8" s="31">
-        <f>AO64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AP8" s="31">
-        <f>AP64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AQ8" s="31">
-        <f>AQ64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AR8" s="31">
-        <f>AR64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AS8" s="31">
-        <f>AS64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AT8" s="31">
-        <f>AT64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AU8" s="31">
-        <f>AU64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AV8" s="31">
-        <f>AV64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AW8" s="31">
-        <f>AW64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AX8" s="31">
-        <f>AX64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AY8" s="31">
-        <f>AY64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="AZ8" s="31">
-        <f>AZ64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BA8" s="31">
-        <f>BA64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BB8" s="31">
-        <f>BB64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BC8" s="31">
-        <f>BC64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BD8" s="31">
-        <f>BD64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BE8" s="31">
-        <f>BE64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BF8" s="31">
-        <f>BF64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BG8" s="31">
-        <f>BG64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BH8" s="31">
-        <f>BH64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BI8" s="31">
-        <f>BI64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BJ8" s="31">
-        <f>BJ64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BK8" s="31">
-        <f>BK64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BL8" s="31">
-        <f>BL64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BM8" s="31">
-        <f>BM64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BN8" s="31">
-        <f>BN64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BO8" s="31">
-        <f>BO64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BP8" s="31">
-        <f>BP64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BQ8" s="31">
-        <f>BQ64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BR8" s="31">
-        <f>BR64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BS8" s="31">
-        <f>BS64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BT8" s="31">
-        <f>BT64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BU8" s="31">
-        <f>BU64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BV8" s="31">
-        <f>BV64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BW8" s="31">
-        <f>BW64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BX8" s="31">
-        <f>BX64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BY8" s="31">
-        <f>BY64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="BZ8" s="31">
-        <f>BZ64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CA8" s="31">
-        <f>CA64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CB8" s="31">
-        <f>CB64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CC8" s="31">
-        <f>CC64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CD8" s="31">
-        <f>CD64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CE8" s="31">
-        <f>CE64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CF8" s="31">
-        <f>CF64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CG8" s="31">
-        <f>CG64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CH8" s="31">
-        <f>CH64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CI8" s="31">
-        <f>CI64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CJ8" s="31">
-        <f>CJ64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CK8" s="31">
-        <f>CK64*$D$56*100</f>
+        <v>0</v>
       </c>
       <c r="CL8" s="31">
-        <f>CL64*$D$56*100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
@@ -12326,7 +12326,7 @@
         <f>'입력값'!E42</f>
       </c>
     </row>
-    <row r="64" spans="2:90" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="33" t="s">
         <v>246</v>
       </c>
@@ -12350,246 +12350,6 @@
       </c>
       <c r="J64" s="52">
         <f>'입력값'!J49</f>
-      </c>
-      <c r="K64" s="45">
-        <f>'입력값'!K49</f>
-      </c>
-      <c r="L64" s="45">
-        <f>'입력값'!L49</f>
-      </c>
-      <c r="M64" s="45">
-        <f>'입력값'!M49</f>
-      </c>
-      <c r="N64" s="45">
-        <f>'입력값'!N49</f>
-      </c>
-      <c r="O64" s="45">
-        <f>'입력값'!O49</f>
-      </c>
-      <c r="P64" s="45">
-        <f>'입력값'!P49</f>
-      </c>
-      <c r="Q64" s="45">
-        <f>'입력값'!Q49</f>
-      </c>
-      <c r="R64" s="45">
-        <f>'입력값'!R49</f>
-      </c>
-      <c r="S64" s="45">
-        <f>'입력값'!S49</f>
-      </c>
-      <c r="T64" s="45">
-        <f>'입력값'!T49</f>
-      </c>
-      <c r="U64" s="45">
-        <f>'입력값'!U49</f>
-      </c>
-      <c r="V64" s="45">
-        <f>'입력값'!V49</f>
-      </c>
-      <c r="W64" s="45">
-        <f>'입력값'!W49</f>
-      </c>
-      <c r="X64" s="45">
-        <f>'입력값'!X49</f>
-      </c>
-      <c r="Y64" s="45">
-        <f>'입력값'!Y49</f>
-      </c>
-      <c r="Z64" s="45">
-        <f>'입력값'!Z49</f>
-      </c>
-      <c r="AA64" s="45">
-        <f>'입력값'!AA49</f>
-      </c>
-      <c r="AB64" s="45">
-        <f>'입력값'!AB49</f>
-      </c>
-      <c r="AC64" s="45">
-        <f>'입력값'!AC49</f>
-      </c>
-      <c r="AD64" s="45">
-        <f>'입력값'!AD49</f>
-      </c>
-      <c r="AE64" s="45">
-        <f>'입력값'!AE49</f>
-      </c>
-      <c r="AF64" s="45">
-        <f>'입력값'!AF49</f>
-      </c>
-      <c r="AG64" s="45">
-        <f>'입력값'!AG49</f>
-      </c>
-      <c r="AH64" s="45">
-        <f>'입력값'!AH49</f>
-      </c>
-      <c r="AI64" s="45">
-        <f>'입력값'!AI49</f>
-      </c>
-      <c r="AJ64" s="45">
-        <f>'입력값'!AJ49</f>
-      </c>
-      <c r="AK64" s="45">
-        <f>'입력값'!AK49</f>
-      </c>
-      <c r="AL64" s="45">
-        <f>'입력값'!AL49</f>
-      </c>
-      <c r="AM64" s="45">
-        <f>'입력값'!AM49</f>
-      </c>
-      <c r="AN64" s="45">
-        <f>'입력값'!AN49</f>
-      </c>
-      <c r="AO64" s="45">
-        <f>'입력값'!AO49</f>
-      </c>
-      <c r="AP64" s="45">
-        <f>'입력값'!AP49</f>
-      </c>
-      <c r="AQ64" s="45">
-        <f>'입력값'!AQ49</f>
-      </c>
-      <c r="AR64" s="45">
-        <f>'입력값'!AR49</f>
-      </c>
-      <c r="AS64" s="45">
-        <f>'입력값'!AS49</f>
-      </c>
-      <c r="AT64" s="45">
-        <f>'입력값'!AT49</f>
-      </c>
-      <c r="AU64" s="45">
-        <f>'입력값'!AU49</f>
-      </c>
-      <c r="AV64" s="45">
-        <f>'입력값'!AV49</f>
-      </c>
-      <c r="AW64" s="45">
-        <f>'입력값'!AW49</f>
-      </c>
-      <c r="AX64" s="45">
-        <f>'입력값'!AX49</f>
-      </c>
-      <c r="AY64" s="45">
-        <f>'입력값'!AY49</f>
-      </c>
-      <c r="AZ64" s="45">
-        <f>'입력값'!AZ49</f>
-      </c>
-      <c r="BA64" s="45">
-        <f>'입력값'!BA49</f>
-      </c>
-      <c r="BB64" s="45">
-        <f>'입력값'!BB49</f>
-      </c>
-      <c r="BC64" s="45">
-        <f>'입력값'!BC49</f>
-      </c>
-      <c r="BD64" s="45">
-        <f>'입력값'!BD49</f>
-      </c>
-      <c r="BE64" s="45">
-        <f>'입력값'!BE49</f>
-      </c>
-      <c r="BF64" s="45">
-        <f>'입력값'!BF49</f>
-      </c>
-      <c r="BG64" s="45">
-        <f>'입력값'!BG49</f>
-      </c>
-      <c r="BH64" s="45">
-        <f>'입력값'!BH49</f>
-      </c>
-      <c r="BI64" s="45">
-        <f>'입력값'!BI49</f>
-      </c>
-      <c r="BJ64" s="45">
-        <f>'입력값'!BJ49</f>
-      </c>
-      <c r="BK64" s="45">
-        <f>'입력값'!BK49</f>
-      </c>
-      <c r="BL64" s="45">
-        <f>'입력값'!BL49</f>
-      </c>
-      <c r="BM64" s="45">
-        <f>'입력값'!BM49</f>
-      </c>
-      <c r="BN64" s="45">
-        <f>'입력값'!BN49</f>
-      </c>
-      <c r="BO64" s="45">
-        <f>'입력값'!BO49</f>
-      </c>
-      <c r="BP64" s="45">
-        <f>'입력값'!BP49</f>
-      </c>
-      <c r="BQ64" s="45">
-        <f>'입력값'!BQ49</f>
-      </c>
-      <c r="BR64" s="45">
-        <f>'입력값'!BR49</f>
-      </c>
-      <c r="BS64" s="45">
-        <f>'입력값'!BS49</f>
-      </c>
-      <c r="BT64" s="45">
-        <f>'입력값'!BT49</f>
-      </c>
-      <c r="BU64" s="45">
-        <f>'입력값'!BU49</f>
-      </c>
-      <c r="BV64" s="45">
-        <f>'입력값'!BV49</f>
-      </c>
-      <c r="BW64" s="45">
-        <f>'입력값'!BW49</f>
-      </c>
-      <c r="BX64" s="45">
-        <f>'입력값'!BX49</f>
-      </c>
-      <c r="BY64" s="45">
-        <f>'입력값'!BY49</f>
-      </c>
-      <c r="BZ64" s="45">
-        <f>'입력값'!BZ49</f>
-      </c>
-      <c r="CA64" s="45">
-        <f>'입력값'!CA49</f>
-      </c>
-      <c r="CB64" s="45">
-        <f>'입력값'!CB49</f>
-      </c>
-      <c r="CC64" s="45">
-        <f>'입력값'!CC49</f>
-      </c>
-      <c r="CD64" s="45">
-        <f>'입력값'!CD49</f>
-      </c>
-      <c r="CE64" s="45">
-        <f>'입력값'!CE49</f>
-      </c>
-      <c r="CF64" s="45">
-        <f>'입력값'!CF49</f>
-      </c>
-      <c r="CG64" s="45">
-        <f>'입력값'!CG49</f>
-      </c>
-      <c r="CH64" s="45">
-        <f>'입력값'!CH49</f>
-      </c>
-      <c r="CI64" s="45">
-        <f>'입력값'!CI49</f>
-      </c>
-      <c r="CJ64" s="45">
-        <f>'입력값'!CJ49</f>
-      </c>
-      <c r="CK64" s="45">
-        <f>'입력값'!CK49</f>
-      </c>
-      <c r="CL64" s="45">
-        <f>'입력값'!CL49</f>
       </c>
     </row>
   </sheetData>
@@ -22921,7 +22681,7 @@
   <sheetPr>
     <tabColor rgb="FF2E7D62"/>
   </sheetPr>
-  <dimension ref="A1:CM79"/>
+  <dimension ref="A1:CM77"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -24338,7 +24098,7 @@
         <f>CK9-CK10-CK14-'Opex'!CK9+CK19</f>
       </c>
       <c r="CL13" s="14">
-        <f>CL9-CL10-CL14-'Opex'!CL9-$D$74*100+CL19</f>
+        <f>CL9-CL10-CL14-'Opex'!CL9-$D$73*100+CL19</f>
       </c>
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
@@ -24905,241 +24665,241 @@
         <f>0</f>
       </c>
       <c r="K16" s="42">
-        <f>IF(AND(0&gt;=($D$78-1),OR(ISBLANK(K11),K11&gt;=$D$76),OR(ISBLANK(K48),K48&gt;=$D$77)),MAX(0,K18-$D$75*100),0)</f>
+        <f>IF(AND(0&gt;=($D$77-1),OR(ISBLANK(K11),K11&gt;=$D$75),OR(ISBLANK(K48),K48&gt;=$D$76)),MAX(0,K18-$D$74*100),0)</f>
       </c>
       <c r="L16" s="42">
-        <f>IF(AND(0&gt;=($D$78-1),OR(ISBLANK(L11),L11&gt;=$D$76),OR(ISBLANK(L48),L48&gt;=$D$77)),MAX(0,L18-$D$75*100),0)</f>
+        <f>IF(AND(0&gt;=($D$77-1),OR(ISBLANK(L11),L11&gt;=$D$75),OR(ISBLANK(L48),L48&gt;=$D$76)),MAX(0,L18-$D$74*100),0)</f>
       </c>
       <c r="M16" s="42">
-        <f>IF(AND(0&gt;=($D$78-1),OR(ISBLANK(M11),M11&gt;=$D$76),OR(ISBLANK(M48),M48&gt;=$D$77)),MAX(0,M18-$D$75*100),0)</f>
+        <f>IF(AND(0&gt;=($D$77-1),OR(ISBLANK(M11),M11&gt;=$D$75),OR(ISBLANK(M48),M48&gt;=$D$76)),MAX(0,M18-$D$74*100),0)</f>
       </c>
       <c r="N16" s="42">
-        <f>IF(AND(0&gt;=($D$78-1),OR(ISBLANK(N11),N11&gt;=$D$76),OR(ISBLANK(N48),N48&gt;=$D$77)),MAX(0,N18-$D$75*100),0)</f>
+        <f>IF(AND(0&gt;=($D$77-1),OR(ISBLANK(N11),N11&gt;=$D$75),OR(ISBLANK(N48),N48&gt;=$D$76)),MAX(0,N18-$D$74*100),0)</f>
       </c>
       <c r="O16" s="42">
-        <f>IF(AND(1&gt;=($D$78-1),OR(ISBLANK(O11),O11&gt;=$D$76),OR(ISBLANK(O48),O48&gt;=$D$77)),MAX(0,O18-$D$75*100),0)</f>
+        <f>IF(AND(1&gt;=($D$77-1),OR(ISBLANK(O11),O11&gt;=$D$75),OR(ISBLANK(O48),O48&gt;=$D$76)),MAX(0,O18-$D$74*100),0)</f>
       </c>
       <c r="P16" s="42">
-        <f>IF(AND(1&gt;=($D$78-1),OR(ISBLANK(P11),P11&gt;=$D$76),OR(ISBLANK(P48),P48&gt;=$D$77)),MAX(0,P18-$D$75*100),0)</f>
+        <f>IF(AND(1&gt;=($D$77-1),OR(ISBLANK(P11),P11&gt;=$D$75),OR(ISBLANK(P48),P48&gt;=$D$76)),MAX(0,P18-$D$74*100),0)</f>
       </c>
       <c r="Q16" s="42">
-        <f>IF(AND(1&gt;=($D$78-1),OR(ISBLANK(Q11),Q11&gt;=$D$76),OR(ISBLANK(Q48),Q48&gt;=$D$77)),MAX(0,Q18-$D$75*100),0)</f>
+        <f>IF(AND(1&gt;=($D$77-1),OR(ISBLANK(Q11),Q11&gt;=$D$75),OR(ISBLANK(Q48),Q48&gt;=$D$76)),MAX(0,Q18-$D$74*100),0)</f>
       </c>
       <c r="R16" s="42">
-        <f>IF(AND(1&gt;=($D$78-1),OR(ISBLANK(R11),R11&gt;=$D$76),OR(ISBLANK(R48),R48&gt;=$D$77)),MAX(0,R18-$D$75*100),0)</f>
+        <f>IF(AND(1&gt;=($D$77-1),OR(ISBLANK(R11),R11&gt;=$D$75),OR(ISBLANK(R48),R48&gt;=$D$76)),MAX(0,R18-$D$74*100),0)</f>
       </c>
       <c r="S16" s="42">
-        <f>IF(AND(2&gt;=($D$78-1),OR(ISBLANK(S11),S11&gt;=$D$76),OR(ISBLANK(S48),S48&gt;=$D$77)),MAX(0,S18-$D$75*100),0)</f>
+        <f>IF(AND(2&gt;=($D$77-1),OR(ISBLANK(S11),S11&gt;=$D$75),OR(ISBLANK(S48),S48&gt;=$D$76)),MAX(0,S18-$D$74*100),0)</f>
       </c>
       <c r="T16" s="42">
-        <f>IF(AND(2&gt;=($D$78-1),OR(ISBLANK(T11),T11&gt;=$D$76),OR(ISBLANK(T48),T48&gt;=$D$77)),MAX(0,T18-$D$75*100),0)</f>
+        <f>IF(AND(2&gt;=($D$77-1),OR(ISBLANK(T11),T11&gt;=$D$75),OR(ISBLANK(T48),T48&gt;=$D$76)),MAX(0,T18-$D$74*100),0)</f>
       </c>
       <c r="U16" s="42">
-        <f>IF(AND(2&gt;=($D$78-1),OR(ISBLANK(U11),U11&gt;=$D$76),OR(ISBLANK(U48),U48&gt;=$D$77)),MAX(0,U18-$D$75*100),0)</f>
+        <f>IF(AND(2&gt;=($D$77-1),OR(ISBLANK(U11),U11&gt;=$D$75),OR(ISBLANK(U48),U48&gt;=$D$76)),MAX(0,U18-$D$74*100),0)</f>
       </c>
       <c r="V16" s="42">
-        <f>IF(AND(2&gt;=($D$78-1),OR(ISBLANK(V11),V11&gt;=$D$76),OR(ISBLANK(V48),V48&gt;=$D$77)),MAX(0,V18-$D$75*100),0)</f>
+        <f>IF(AND(2&gt;=($D$77-1),OR(ISBLANK(V11),V11&gt;=$D$75),OR(ISBLANK(V48),V48&gt;=$D$76)),MAX(0,V18-$D$74*100),0)</f>
       </c>
       <c r="W16" s="42">
-        <f>IF(AND(3&gt;=($D$78-1),OR(ISBLANK(W11),W11&gt;=$D$76),OR(ISBLANK(W48),W48&gt;=$D$77)),MAX(0,W18-$D$75*100),0)</f>
+        <f>IF(AND(3&gt;=($D$77-1),OR(ISBLANK(W11),W11&gt;=$D$75),OR(ISBLANK(W48),W48&gt;=$D$76)),MAX(0,W18-$D$74*100),0)</f>
       </c>
       <c r="X16" s="42">
-        <f>IF(AND(3&gt;=($D$78-1),OR(ISBLANK(X11),X11&gt;=$D$76),OR(ISBLANK(X48),X48&gt;=$D$77)),MAX(0,X18-$D$75*100),0)</f>
+        <f>IF(AND(3&gt;=($D$77-1),OR(ISBLANK(X11),X11&gt;=$D$75),OR(ISBLANK(X48),X48&gt;=$D$76)),MAX(0,X18-$D$74*100),0)</f>
       </c>
       <c r="Y16" s="42">
-        <f>IF(AND(3&gt;=($D$78-1),OR(ISBLANK(Y11),Y11&gt;=$D$76),OR(ISBLANK(Y48),Y48&gt;=$D$77)),MAX(0,Y18-$D$75*100),0)</f>
+        <f>IF(AND(3&gt;=($D$77-1),OR(ISBLANK(Y11),Y11&gt;=$D$75),OR(ISBLANK(Y48),Y48&gt;=$D$76)),MAX(0,Y18-$D$74*100),0)</f>
       </c>
       <c r="Z16" s="42">
-        <f>IF(AND(3&gt;=($D$78-1),OR(ISBLANK(Z11),Z11&gt;=$D$76),OR(ISBLANK(Z48),Z48&gt;=$D$77)),MAX(0,Z18-$D$75*100),0)</f>
+        <f>IF(AND(3&gt;=($D$77-1),OR(ISBLANK(Z11),Z11&gt;=$D$75),OR(ISBLANK(Z48),Z48&gt;=$D$76)),MAX(0,Z18-$D$74*100),0)</f>
       </c>
       <c r="AA16" s="42">
-        <f>IF(AND(4&gt;=($D$78-1),OR(ISBLANK(AA11),AA11&gt;=$D$76),OR(ISBLANK(AA48),AA48&gt;=$D$77)),MAX(0,AA18-$D$75*100),0)</f>
+        <f>IF(AND(4&gt;=($D$77-1),OR(ISBLANK(AA11),AA11&gt;=$D$75),OR(ISBLANK(AA48),AA48&gt;=$D$76)),MAX(0,AA18-$D$74*100),0)</f>
       </c>
       <c r="AB16" s="42">
-        <f>IF(AND(4&gt;=($D$78-1),OR(ISBLANK(AB11),AB11&gt;=$D$76),OR(ISBLANK(AB48),AB48&gt;=$D$77)),MAX(0,AB18-$D$75*100),0)</f>
+        <f>IF(AND(4&gt;=($D$77-1),OR(ISBLANK(AB11),AB11&gt;=$D$75),OR(ISBLANK(AB48),AB48&gt;=$D$76)),MAX(0,AB18-$D$74*100),0)</f>
       </c>
       <c r="AC16" s="42">
-        <f>IF(AND(4&gt;=($D$78-1),OR(ISBLANK(AC11),AC11&gt;=$D$76),OR(ISBLANK(AC48),AC48&gt;=$D$77)),MAX(0,AC18-$D$75*100),0)</f>
+        <f>IF(AND(4&gt;=($D$77-1),OR(ISBLANK(AC11),AC11&gt;=$D$75),OR(ISBLANK(AC48),AC48&gt;=$D$76)),MAX(0,AC18-$D$74*100),0)</f>
       </c>
       <c r="AD16" s="42">
-        <f>IF(AND(4&gt;=($D$78-1),OR(ISBLANK(AD11),AD11&gt;=$D$76),OR(ISBLANK(AD48),AD48&gt;=$D$77)),MAX(0,AD18-$D$75*100),0)</f>
+        <f>IF(AND(4&gt;=($D$77-1),OR(ISBLANK(AD11),AD11&gt;=$D$75),OR(ISBLANK(AD48),AD48&gt;=$D$76)),MAX(0,AD18-$D$74*100),0)</f>
       </c>
       <c r="AE16" s="42">
-        <f>IF(AND(5&gt;=($D$78-1),OR(ISBLANK(AE11),AE11&gt;=$D$76),OR(ISBLANK(AE48),AE48&gt;=$D$77)),MAX(0,AE18-$D$75*100),0)</f>
+        <f>IF(AND(5&gt;=($D$77-1),OR(ISBLANK(AE11),AE11&gt;=$D$75),OR(ISBLANK(AE48),AE48&gt;=$D$76)),MAX(0,AE18-$D$74*100),0)</f>
       </c>
       <c r="AF16" s="42">
-        <f>IF(AND(5&gt;=($D$78-1),OR(ISBLANK(AF11),AF11&gt;=$D$76),OR(ISBLANK(AF48),AF48&gt;=$D$77)),MAX(0,AF18-$D$75*100),0)</f>
+        <f>IF(AND(5&gt;=($D$77-1),OR(ISBLANK(AF11),AF11&gt;=$D$75),OR(ISBLANK(AF48),AF48&gt;=$D$76)),MAX(0,AF18-$D$74*100),0)</f>
       </c>
       <c r="AG16" s="42">
-        <f>IF(AND(5&gt;=($D$78-1),OR(ISBLANK(AG11),AG11&gt;=$D$76),OR(ISBLANK(AG48),AG48&gt;=$D$77)),MAX(0,AG18-$D$75*100),0)</f>
+        <f>IF(AND(5&gt;=($D$77-1),OR(ISBLANK(AG11),AG11&gt;=$D$75),OR(ISBLANK(AG48),AG48&gt;=$D$76)),MAX(0,AG18-$D$74*100),0)</f>
       </c>
       <c r="AH16" s="42">
-        <f>IF(AND(5&gt;=($D$78-1),OR(ISBLANK(AH11),AH11&gt;=$D$76),OR(ISBLANK(AH48),AH48&gt;=$D$77)),MAX(0,AH18-$D$75*100),0)</f>
+        <f>IF(AND(5&gt;=($D$77-1),OR(ISBLANK(AH11),AH11&gt;=$D$75),OR(ISBLANK(AH48),AH48&gt;=$D$76)),MAX(0,AH18-$D$74*100),0)</f>
       </c>
       <c r="AI16" s="42">
-        <f>IF(AND(6&gt;=($D$78-1),OR(ISBLANK(AI11),AI11&gt;=$D$76),OR(ISBLANK(AI48),AI48&gt;=$D$77)),MAX(0,AI18-$D$75*100),0)</f>
+        <f>IF(AND(6&gt;=($D$77-1),OR(ISBLANK(AI11),AI11&gt;=$D$75),OR(ISBLANK(AI48),AI48&gt;=$D$76)),MAX(0,AI18-$D$74*100),0)</f>
       </c>
       <c r="AJ16" s="42">
-        <f>IF(AND(6&gt;=($D$78-1),OR(ISBLANK(AJ11),AJ11&gt;=$D$76),OR(ISBLANK(AJ48),AJ48&gt;=$D$77)),MAX(0,AJ18-$D$75*100),0)</f>
+        <f>IF(AND(6&gt;=($D$77-1),OR(ISBLANK(AJ11),AJ11&gt;=$D$75),OR(ISBLANK(AJ48),AJ48&gt;=$D$76)),MAX(0,AJ18-$D$74*100),0)</f>
       </c>
       <c r="AK16" s="42">
-        <f>IF(AND(6&gt;=($D$78-1),OR(ISBLANK(AK11),AK11&gt;=$D$76),OR(ISBLANK(AK48),AK48&gt;=$D$77)),MAX(0,AK18-$D$75*100),0)</f>
+        <f>IF(AND(6&gt;=($D$77-1),OR(ISBLANK(AK11),AK11&gt;=$D$75),OR(ISBLANK(AK48),AK48&gt;=$D$76)),MAX(0,AK18-$D$74*100),0)</f>
       </c>
       <c r="AL16" s="42">
-        <f>IF(AND(6&gt;=($D$78-1),OR(ISBLANK(AL11),AL11&gt;=$D$76),OR(ISBLANK(AL48),AL48&gt;=$D$77)),MAX(0,AL18-$D$75*100),0)</f>
+        <f>IF(AND(6&gt;=($D$77-1),OR(ISBLANK(AL11),AL11&gt;=$D$75),OR(ISBLANK(AL48),AL48&gt;=$D$76)),MAX(0,AL18-$D$74*100),0)</f>
       </c>
       <c r="AM16" s="42">
-        <f>IF(AND(7&gt;=($D$78-1),OR(ISBLANK(AM11),AM11&gt;=$D$76),OR(ISBLANK(AM48),AM48&gt;=$D$77)),MAX(0,AM18-$D$75*100),0)</f>
+        <f>IF(AND(7&gt;=($D$77-1),OR(ISBLANK(AM11),AM11&gt;=$D$75),OR(ISBLANK(AM48),AM48&gt;=$D$76)),MAX(0,AM18-$D$74*100),0)</f>
       </c>
       <c r="AN16" s="42">
-        <f>IF(AND(7&gt;=($D$78-1),OR(ISBLANK(AN11),AN11&gt;=$D$76),OR(ISBLANK(AN48),AN48&gt;=$D$77)),MAX(0,AN18-$D$75*100),0)</f>
+        <f>IF(AND(7&gt;=($D$77-1),OR(ISBLANK(AN11),AN11&gt;=$D$75),OR(ISBLANK(AN48),AN48&gt;=$D$76)),MAX(0,AN18-$D$74*100),0)</f>
       </c>
       <c r="AO16" s="42">
-        <f>IF(AND(7&gt;=($D$78-1),OR(ISBLANK(AO11),AO11&gt;=$D$76),OR(ISBLANK(AO48),AO48&gt;=$D$77)),MAX(0,AO18-$D$75*100),0)</f>
+        <f>IF(AND(7&gt;=($D$77-1),OR(ISBLANK(AO11),AO11&gt;=$D$75),OR(ISBLANK(AO48),AO48&gt;=$D$76)),MAX(0,AO18-$D$74*100),0)</f>
       </c>
       <c r="AP16" s="42">
-        <f>IF(AND(7&gt;=($D$78-1),OR(ISBLANK(AP11),AP11&gt;=$D$76),OR(ISBLANK(AP48),AP48&gt;=$D$77)),MAX(0,AP18-$D$75*100),0)</f>
+        <f>IF(AND(7&gt;=($D$77-1),OR(ISBLANK(AP11),AP11&gt;=$D$75),OR(ISBLANK(AP48),AP48&gt;=$D$76)),MAX(0,AP18-$D$74*100),0)</f>
       </c>
       <c r="AQ16" s="42">
-        <f>IF(AND(8&gt;=($D$78-1),OR(ISBLANK(AQ11),AQ11&gt;=$D$76),OR(ISBLANK(AQ48),AQ48&gt;=$D$77)),MAX(0,AQ18-$D$75*100),0)</f>
+        <f>IF(AND(8&gt;=($D$77-1),OR(ISBLANK(AQ11),AQ11&gt;=$D$75),OR(ISBLANK(AQ48),AQ48&gt;=$D$76)),MAX(0,AQ18-$D$74*100),0)</f>
       </c>
       <c r="AR16" s="42">
-        <f>IF(AND(8&gt;=($D$78-1),OR(ISBLANK(AR11),AR11&gt;=$D$76),OR(ISBLANK(AR48),AR48&gt;=$D$77)),MAX(0,AR18-$D$75*100),0)</f>
+        <f>IF(AND(8&gt;=($D$77-1),OR(ISBLANK(AR11),AR11&gt;=$D$75),OR(ISBLANK(AR48),AR48&gt;=$D$76)),MAX(0,AR18-$D$74*100),0)</f>
       </c>
       <c r="AS16" s="42">
-        <f>IF(AND(8&gt;=($D$78-1),OR(ISBLANK(AS11),AS11&gt;=$D$76),OR(ISBLANK(AS48),AS48&gt;=$D$77)),MAX(0,AS18-$D$75*100),0)</f>
+        <f>IF(AND(8&gt;=($D$77-1),OR(ISBLANK(AS11),AS11&gt;=$D$75),OR(ISBLANK(AS48),AS48&gt;=$D$76)),MAX(0,AS18-$D$74*100),0)</f>
       </c>
       <c r="AT16" s="42">
-        <f>IF(AND(8&gt;=($D$78-1),OR(ISBLANK(AT11),AT11&gt;=$D$76),OR(ISBLANK(AT48),AT48&gt;=$D$77)),MAX(0,AT18-$D$75*100),0)</f>
+        <f>IF(AND(8&gt;=($D$77-1),OR(ISBLANK(AT11),AT11&gt;=$D$75),OR(ISBLANK(AT48),AT48&gt;=$D$76)),MAX(0,AT18-$D$74*100),0)</f>
       </c>
       <c r="AU16" s="42">
-        <f>IF(AND(9&gt;=($D$78-1),OR(ISBLANK(AU11),AU11&gt;=$D$76),OR(ISBLANK(AU48),AU48&gt;=$D$77)),MAX(0,AU18-$D$75*100),0)</f>
+        <f>IF(AND(9&gt;=($D$77-1),OR(ISBLANK(AU11),AU11&gt;=$D$75),OR(ISBLANK(AU48),AU48&gt;=$D$76)),MAX(0,AU18-$D$74*100),0)</f>
       </c>
       <c r="AV16" s="42">
-        <f>IF(AND(9&gt;=($D$78-1),OR(ISBLANK(AV11),AV11&gt;=$D$76),OR(ISBLANK(AV48),AV48&gt;=$D$77)),MAX(0,AV18-$D$75*100),0)</f>
+        <f>IF(AND(9&gt;=($D$77-1),OR(ISBLANK(AV11),AV11&gt;=$D$75),OR(ISBLANK(AV48),AV48&gt;=$D$76)),MAX(0,AV18-$D$74*100),0)</f>
       </c>
       <c r="AW16" s="42">
-        <f>IF(AND(9&gt;=($D$78-1),OR(ISBLANK(AW11),AW11&gt;=$D$76),OR(ISBLANK(AW48),AW48&gt;=$D$77)),MAX(0,AW18-$D$75*100),0)</f>
+        <f>IF(AND(9&gt;=($D$77-1),OR(ISBLANK(AW11),AW11&gt;=$D$75),OR(ISBLANK(AW48),AW48&gt;=$D$76)),MAX(0,AW18-$D$74*100),0)</f>
       </c>
       <c r="AX16" s="42">
-        <f>IF(AND(9&gt;=($D$78-1),OR(ISBLANK(AX11),AX11&gt;=$D$76),OR(ISBLANK(AX48),AX48&gt;=$D$77)),MAX(0,AX18-$D$75*100),0)</f>
+        <f>IF(AND(9&gt;=($D$77-1),OR(ISBLANK(AX11),AX11&gt;=$D$75),OR(ISBLANK(AX48),AX48&gt;=$D$76)),MAX(0,AX18-$D$74*100),0)</f>
       </c>
       <c r="AY16" s="42">
-        <f>IF(AND(10&gt;=($D$78-1),OR(ISBLANK(AY11),AY11&gt;=$D$76),OR(ISBLANK(AY48),AY48&gt;=$D$77)),MAX(0,AY18-$D$75*100),0)</f>
+        <f>IF(AND(10&gt;=($D$77-1),OR(ISBLANK(AY11),AY11&gt;=$D$75),OR(ISBLANK(AY48),AY48&gt;=$D$76)),MAX(0,AY18-$D$74*100),0)</f>
       </c>
       <c r="AZ16" s="42">
-        <f>IF(AND(10&gt;=($D$78-1),OR(ISBLANK(AZ11),AZ11&gt;=$D$76),OR(ISBLANK(AZ48),AZ48&gt;=$D$77)),MAX(0,AZ18-$D$75*100),0)</f>
+        <f>IF(AND(10&gt;=($D$77-1),OR(ISBLANK(AZ11),AZ11&gt;=$D$75),OR(ISBLANK(AZ48),AZ48&gt;=$D$76)),MAX(0,AZ18-$D$74*100),0)</f>
       </c>
       <c r="BA16" s="42">
-        <f>IF(AND(10&gt;=($D$78-1),OR(ISBLANK(BA11),BA11&gt;=$D$76),OR(ISBLANK(BA48),BA48&gt;=$D$77)),MAX(0,BA18-$D$75*100),0)</f>
+        <f>IF(AND(10&gt;=($D$77-1),OR(ISBLANK(BA11),BA11&gt;=$D$75),OR(ISBLANK(BA48),BA48&gt;=$D$76)),MAX(0,BA18-$D$74*100),0)</f>
       </c>
       <c r="BB16" s="42">
-        <f>IF(AND(10&gt;=($D$78-1),OR(ISBLANK(BB11),BB11&gt;=$D$76),OR(ISBLANK(BB48),BB48&gt;=$D$77)),MAX(0,BB18-$D$75*100),0)</f>
+        <f>IF(AND(10&gt;=($D$77-1),OR(ISBLANK(BB11),BB11&gt;=$D$75),OR(ISBLANK(BB48),BB48&gt;=$D$76)),MAX(0,BB18-$D$74*100),0)</f>
       </c>
       <c r="BC16" s="42">
-        <f>IF(AND(11&gt;=($D$78-1),OR(ISBLANK(BC11),BC11&gt;=$D$76),OR(ISBLANK(BC48),BC48&gt;=$D$77)),MAX(0,BC18-$D$75*100),0)</f>
+        <f>IF(AND(11&gt;=($D$77-1),OR(ISBLANK(BC11),BC11&gt;=$D$75),OR(ISBLANK(BC48),BC48&gt;=$D$76)),MAX(0,BC18-$D$74*100),0)</f>
       </c>
       <c r="BD16" s="42">
-        <f>IF(AND(11&gt;=($D$78-1),OR(ISBLANK(BD11),BD11&gt;=$D$76),OR(ISBLANK(BD48),BD48&gt;=$D$77)),MAX(0,BD18-$D$75*100),0)</f>
+        <f>IF(AND(11&gt;=($D$77-1),OR(ISBLANK(BD11),BD11&gt;=$D$75),OR(ISBLANK(BD48),BD48&gt;=$D$76)),MAX(0,BD18-$D$74*100),0)</f>
       </c>
       <c r="BE16" s="42">
-        <f>IF(AND(11&gt;=($D$78-1),OR(ISBLANK(BE11),BE11&gt;=$D$76),OR(ISBLANK(BE48),BE48&gt;=$D$77)),MAX(0,BE18-$D$75*100),0)</f>
+        <f>IF(AND(11&gt;=($D$77-1),OR(ISBLANK(BE11),BE11&gt;=$D$75),OR(ISBLANK(BE48),BE48&gt;=$D$76)),MAX(0,BE18-$D$74*100),0)</f>
       </c>
       <c r="BF16" s="42">
-        <f>IF(AND(11&gt;=($D$78-1),OR(ISBLANK(BF11),BF11&gt;=$D$76),OR(ISBLANK(BF48),BF48&gt;=$D$77)),MAX(0,BF18-$D$75*100),0)</f>
+        <f>IF(AND(11&gt;=($D$77-1),OR(ISBLANK(BF11),BF11&gt;=$D$75),OR(ISBLANK(BF48),BF48&gt;=$D$76)),MAX(0,BF18-$D$74*100),0)</f>
       </c>
       <c r="BG16" s="42">
-        <f>IF(AND(12&gt;=($D$78-1),OR(ISBLANK(BG11),BG11&gt;=$D$76),OR(ISBLANK(BG48),BG48&gt;=$D$77)),MAX(0,BG18-$D$75*100),0)</f>
+        <f>IF(AND(12&gt;=($D$77-1),OR(ISBLANK(BG11),BG11&gt;=$D$75),OR(ISBLANK(BG48),BG48&gt;=$D$76)),MAX(0,BG18-$D$74*100),0)</f>
       </c>
       <c r="BH16" s="42">
-        <f>IF(AND(12&gt;=($D$78-1),OR(ISBLANK(BH11),BH11&gt;=$D$76),OR(ISBLANK(BH48),BH48&gt;=$D$77)),MAX(0,BH18-$D$75*100),0)</f>
+        <f>IF(AND(12&gt;=($D$77-1),OR(ISBLANK(BH11),BH11&gt;=$D$75),OR(ISBLANK(BH48),BH48&gt;=$D$76)),MAX(0,BH18-$D$74*100),0)</f>
       </c>
       <c r="BI16" s="42">
-        <f>IF(AND(12&gt;=($D$78-1),OR(ISBLANK(BI11),BI11&gt;=$D$76),OR(ISBLANK(BI48),BI48&gt;=$D$77)),MAX(0,BI18-$D$75*100),0)</f>
+        <f>IF(AND(12&gt;=($D$77-1),OR(ISBLANK(BI11),BI11&gt;=$D$75),OR(ISBLANK(BI48),BI48&gt;=$D$76)),MAX(0,BI18-$D$74*100),0)</f>
       </c>
       <c r="BJ16" s="42">
-        <f>IF(AND(12&gt;=($D$78-1),OR(ISBLANK(BJ11),BJ11&gt;=$D$76),OR(ISBLANK(BJ48),BJ48&gt;=$D$77)),MAX(0,BJ18-$D$75*100),0)</f>
+        <f>IF(AND(12&gt;=($D$77-1),OR(ISBLANK(BJ11),BJ11&gt;=$D$75),OR(ISBLANK(BJ48),BJ48&gt;=$D$76)),MAX(0,BJ18-$D$74*100),0)</f>
       </c>
       <c r="BK16" s="42">
-        <f>IF(AND(13&gt;=($D$78-1),OR(ISBLANK(BK11),BK11&gt;=$D$76),OR(ISBLANK(BK48),BK48&gt;=$D$77)),MAX(0,BK18-$D$75*100),0)</f>
+        <f>IF(AND(13&gt;=($D$77-1),OR(ISBLANK(BK11),BK11&gt;=$D$75),OR(ISBLANK(BK48),BK48&gt;=$D$76)),MAX(0,BK18-$D$74*100),0)</f>
       </c>
       <c r="BL16" s="42">
-        <f>IF(AND(13&gt;=($D$78-1),OR(ISBLANK(BL11),BL11&gt;=$D$76),OR(ISBLANK(BL48),BL48&gt;=$D$77)),MAX(0,BL18-$D$75*100),0)</f>
+        <f>IF(AND(13&gt;=($D$77-1),OR(ISBLANK(BL11),BL11&gt;=$D$75),OR(ISBLANK(BL48),BL48&gt;=$D$76)),MAX(0,BL18-$D$74*100),0)</f>
       </c>
       <c r="BM16" s="42">
-        <f>IF(AND(13&gt;=($D$78-1),OR(ISBLANK(BM11),BM11&gt;=$D$76),OR(ISBLANK(BM48),BM48&gt;=$D$77)),MAX(0,BM18-$D$75*100),0)</f>
+        <f>IF(AND(13&gt;=($D$77-1),OR(ISBLANK(BM11),BM11&gt;=$D$75),OR(ISBLANK(BM48),BM48&gt;=$D$76)),MAX(0,BM18-$D$74*100),0)</f>
       </c>
       <c r="BN16" s="42">
-        <f>IF(AND(13&gt;=($D$78-1),OR(ISBLANK(BN11),BN11&gt;=$D$76),OR(ISBLANK(BN48),BN48&gt;=$D$77)),MAX(0,BN18-$D$75*100),0)</f>
+        <f>IF(AND(13&gt;=($D$77-1),OR(ISBLANK(BN11),BN11&gt;=$D$75),OR(ISBLANK(BN48),BN48&gt;=$D$76)),MAX(0,BN18-$D$74*100),0)</f>
       </c>
       <c r="BO16" s="42">
-        <f>IF(AND(14&gt;=($D$78-1),OR(ISBLANK(BO11),BO11&gt;=$D$76),OR(ISBLANK(BO48),BO48&gt;=$D$77)),MAX(0,BO18-$D$75*100),0)</f>
+        <f>IF(AND(14&gt;=($D$77-1),OR(ISBLANK(BO11),BO11&gt;=$D$75),OR(ISBLANK(BO48),BO48&gt;=$D$76)),MAX(0,BO18-$D$74*100),0)</f>
       </c>
       <c r="BP16" s="42">
-        <f>IF(AND(14&gt;=($D$78-1),OR(ISBLANK(BP11),BP11&gt;=$D$76),OR(ISBLANK(BP48),BP48&gt;=$D$77)),MAX(0,BP18-$D$75*100),0)</f>
+        <f>IF(AND(14&gt;=($D$77-1),OR(ISBLANK(BP11),BP11&gt;=$D$75),OR(ISBLANK(BP48),BP48&gt;=$D$76)),MAX(0,BP18-$D$74*100),0)</f>
       </c>
       <c r="BQ16" s="42">
-        <f>IF(AND(14&gt;=($D$78-1),OR(ISBLANK(BQ11),BQ11&gt;=$D$76),OR(ISBLANK(BQ48),BQ48&gt;=$D$77)),MAX(0,BQ18-$D$75*100),0)</f>
+        <f>IF(AND(14&gt;=($D$77-1),OR(ISBLANK(BQ11),BQ11&gt;=$D$75),OR(ISBLANK(BQ48),BQ48&gt;=$D$76)),MAX(0,BQ18-$D$74*100),0)</f>
       </c>
       <c r="BR16" s="42">
-        <f>IF(AND(14&gt;=($D$78-1),OR(ISBLANK(BR11),BR11&gt;=$D$76),OR(ISBLANK(BR48),BR48&gt;=$D$77)),MAX(0,BR18-$D$75*100),0)</f>
+        <f>IF(AND(14&gt;=($D$77-1),OR(ISBLANK(BR11),BR11&gt;=$D$75),OR(ISBLANK(BR48),BR48&gt;=$D$76)),MAX(0,BR18-$D$74*100),0)</f>
       </c>
       <c r="BS16" s="42">
-        <f>IF(AND(15&gt;=($D$78-1),OR(ISBLANK(BS11),BS11&gt;=$D$76),OR(ISBLANK(BS48),BS48&gt;=$D$77)),MAX(0,BS18-$D$75*100),0)</f>
+        <f>IF(AND(15&gt;=($D$77-1),OR(ISBLANK(BS11),BS11&gt;=$D$75),OR(ISBLANK(BS48),BS48&gt;=$D$76)),MAX(0,BS18-$D$74*100),0)</f>
       </c>
       <c r="BT16" s="42">
-        <f>IF(AND(15&gt;=($D$78-1),OR(ISBLANK(BT11),BT11&gt;=$D$76),OR(ISBLANK(BT48),BT48&gt;=$D$77)),MAX(0,BT18-$D$75*100),0)</f>
+        <f>IF(AND(15&gt;=($D$77-1),OR(ISBLANK(BT11),BT11&gt;=$D$75),OR(ISBLANK(BT48),BT48&gt;=$D$76)),MAX(0,BT18-$D$74*100),0)</f>
       </c>
       <c r="BU16" s="42">
-        <f>IF(AND(15&gt;=($D$78-1),OR(ISBLANK(BU11),BU11&gt;=$D$76),OR(ISBLANK(BU48),BU48&gt;=$D$77)),MAX(0,BU18-$D$75*100),0)</f>
+        <f>IF(AND(15&gt;=($D$77-1),OR(ISBLANK(BU11),BU11&gt;=$D$75),OR(ISBLANK(BU48),BU48&gt;=$D$76)),MAX(0,BU18-$D$74*100),0)</f>
       </c>
       <c r="BV16" s="42">
-        <f>IF(AND(15&gt;=($D$78-1),OR(ISBLANK(BV11),BV11&gt;=$D$76),OR(ISBLANK(BV48),BV48&gt;=$D$77)),MAX(0,BV18-$D$75*100),0)</f>
+        <f>IF(AND(15&gt;=($D$77-1),OR(ISBLANK(BV11),BV11&gt;=$D$75),OR(ISBLANK(BV48),BV48&gt;=$D$76)),MAX(0,BV18-$D$74*100),0)</f>
       </c>
       <c r="BW16" s="42">
-        <f>IF(AND(16&gt;=($D$78-1),OR(ISBLANK(BW11),BW11&gt;=$D$76),OR(ISBLANK(BW48),BW48&gt;=$D$77)),MAX(0,BW18-$D$75*100),0)</f>
+        <f>IF(AND(16&gt;=($D$77-1),OR(ISBLANK(BW11),BW11&gt;=$D$75),OR(ISBLANK(BW48),BW48&gt;=$D$76)),MAX(0,BW18-$D$74*100),0)</f>
       </c>
       <c r="BX16" s="42">
-        <f>IF(AND(16&gt;=($D$78-1),OR(ISBLANK(BX11),BX11&gt;=$D$76),OR(ISBLANK(BX48),BX48&gt;=$D$77)),MAX(0,BX18-$D$75*100),0)</f>
+        <f>IF(AND(16&gt;=($D$77-1),OR(ISBLANK(BX11),BX11&gt;=$D$75),OR(ISBLANK(BX48),BX48&gt;=$D$76)),MAX(0,BX18-$D$74*100),0)</f>
       </c>
       <c r="BY16" s="42">
-        <f>IF(AND(16&gt;=($D$78-1),OR(ISBLANK(BY11),BY11&gt;=$D$76),OR(ISBLANK(BY48),BY48&gt;=$D$77)),MAX(0,BY18-$D$75*100),0)</f>
+        <f>IF(AND(16&gt;=($D$77-1),OR(ISBLANK(BY11),BY11&gt;=$D$75),OR(ISBLANK(BY48),BY48&gt;=$D$76)),MAX(0,BY18-$D$74*100),0)</f>
       </c>
       <c r="BZ16" s="42">
-        <f>IF(AND(16&gt;=($D$78-1),OR(ISBLANK(BZ11),BZ11&gt;=$D$76),OR(ISBLANK(BZ48),BZ48&gt;=$D$77)),MAX(0,BZ18-$D$75*100),0)</f>
+        <f>IF(AND(16&gt;=($D$77-1),OR(ISBLANK(BZ11),BZ11&gt;=$D$75),OR(ISBLANK(BZ48),BZ48&gt;=$D$76)),MAX(0,BZ18-$D$74*100),0)</f>
       </c>
       <c r="CA16" s="42">
-        <f>IF(AND(17&gt;=($D$78-1),OR(ISBLANK(CA11),CA11&gt;=$D$76),OR(ISBLANK(CA48),CA48&gt;=$D$77)),MAX(0,CA18-$D$75*100),0)</f>
+        <f>IF(AND(17&gt;=($D$77-1),OR(ISBLANK(CA11),CA11&gt;=$D$75),OR(ISBLANK(CA48),CA48&gt;=$D$76)),MAX(0,CA18-$D$74*100),0)</f>
       </c>
       <c r="CB16" s="42">
-        <f>IF(AND(17&gt;=($D$78-1),OR(ISBLANK(CB11),CB11&gt;=$D$76),OR(ISBLANK(CB48),CB48&gt;=$D$77)),MAX(0,CB18-$D$75*100),0)</f>
+        <f>IF(AND(17&gt;=($D$77-1),OR(ISBLANK(CB11),CB11&gt;=$D$75),OR(ISBLANK(CB48),CB48&gt;=$D$76)),MAX(0,CB18-$D$74*100),0)</f>
       </c>
       <c r="CC16" s="42">
-        <f>IF(AND(17&gt;=($D$78-1),OR(ISBLANK(CC11),CC11&gt;=$D$76),OR(ISBLANK(CC48),CC48&gt;=$D$77)),MAX(0,CC18-$D$75*100),0)</f>
+        <f>IF(AND(17&gt;=($D$77-1),OR(ISBLANK(CC11),CC11&gt;=$D$75),OR(ISBLANK(CC48),CC48&gt;=$D$76)),MAX(0,CC18-$D$74*100),0)</f>
       </c>
       <c r="CD16" s="42">
-        <f>IF(AND(17&gt;=($D$78-1),OR(ISBLANK(CD11),CD11&gt;=$D$76),OR(ISBLANK(CD48),CD48&gt;=$D$77)),MAX(0,CD18-$D$75*100),0)</f>
+        <f>IF(AND(17&gt;=($D$77-1),OR(ISBLANK(CD11),CD11&gt;=$D$75),OR(ISBLANK(CD48),CD48&gt;=$D$76)),MAX(0,CD18-$D$74*100),0)</f>
       </c>
       <c r="CE16" s="42">
-        <f>IF(AND(18&gt;=($D$78-1),OR(ISBLANK(CE11),CE11&gt;=$D$76),OR(ISBLANK(CE48),CE48&gt;=$D$77)),MAX(0,CE18-$D$75*100),0)</f>
+        <f>IF(AND(18&gt;=($D$77-1),OR(ISBLANK(CE11),CE11&gt;=$D$75),OR(ISBLANK(CE48),CE48&gt;=$D$76)),MAX(0,CE18-$D$74*100),0)</f>
       </c>
       <c r="CF16" s="42">
-        <f>IF(AND(18&gt;=($D$78-1),OR(ISBLANK(CF11),CF11&gt;=$D$76),OR(ISBLANK(CF48),CF48&gt;=$D$77)),MAX(0,CF18-$D$75*100),0)</f>
+        <f>IF(AND(18&gt;=($D$77-1),OR(ISBLANK(CF11),CF11&gt;=$D$75),OR(ISBLANK(CF48),CF48&gt;=$D$76)),MAX(0,CF18-$D$74*100),0)</f>
       </c>
       <c r="CG16" s="42">
-        <f>IF(AND(18&gt;=($D$78-1),OR(ISBLANK(CG11),CG11&gt;=$D$76),OR(ISBLANK(CG48),CG48&gt;=$D$77)),MAX(0,CG18-$D$75*100),0)</f>
+        <f>IF(AND(18&gt;=($D$77-1),OR(ISBLANK(CG11),CG11&gt;=$D$75),OR(ISBLANK(CG48),CG48&gt;=$D$76)),MAX(0,CG18-$D$74*100),0)</f>
       </c>
       <c r="CH16" s="42">
-        <f>IF(AND(18&gt;=($D$78-1),OR(ISBLANK(CH11),CH11&gt;=$D$76),OR(ISBLANK(CH48),CH48&gt;=$D$77)),MAX(0,CH18-$D$75*100),0)</f>
+        <f>IF(AND(18&gt;=($D$77-1),OR(ISBLANK(CH11),CH11&gt;=$D$75),OR(ISBLANK(CH48),CH48&gt;=$D$76)),MAX(0,CH18-$D$74*100),0)</f>
       </c>
       <c r="CI16" s="42">
-        <f>IF(AND(19&gt;=($D$78-1),OR(ISBLANK(CI11),CI11&gt;=$D$76),OR(ISBLANK(CI48),CI48&gt;=$D$77)),MAX(0,CI18-$D$75*100),0)</f>
+        <f>IF(AND(19&gt;=($D$77-1),OR(ISBLANK(CI11),CI11&gt;=$D$75),OR(ISBLANK(CI48),CI48&gt;=$D$76)),MAX(0,CI18-$D$74*100),0)</f>
       </c>
       <c r="CJ16" s="42">
-        <f>IF(AND(19&gt;=($D$78-1),OR(ISBLANK(CJ11),CJ11&gt;=$D$76),OR(ISBLANK(CJ48),CJ48&gt;=$D$77)),MAX(0,CJ18-$D$75*100),0)</f>
+        <f>IF(AND(19&gt;=($D$77-1),OR(ISBLANK(CJ11),CJ11&gt;=$D$75),OR(ISBLANK(CJ48),CJ48&gt;=$D$76)),MAX(0,CJ18-$D$74*100),0)</f>
       </c>
       <c r="CK16" s="42">
-        <f>IF(AND(19&gt;=($D$78-1),OR(ISBLANK(CK11),CK11&gt;=$D$76),OR(ISBLANK(CK48),CK48&gt;=$D$77)),MAX(0,CK18-$D$75*100),0)</f>
+        <f>IF(AND(19&gt;=($D$77-1),OR(ISBLANK(CK11),CK11&gt;=$D$75),OR(ISBLANK(CK48),CK48&gt;=$D$76)),MAX(0,CK18-$D$74*100),0)</f>
       </c>
       <c r="CL16" s="42">
         <f>MAX(0,CL18)</f>
@@ -29224,262 +28984,262 @@
         <v>210</v>
       </c>
       <c r="E56" s="31">
-        <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E28+'IS(Q)'!E18+'Revenue'!E19-(E79*$D$73*100)</f>
+        <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E28+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
       </c>
       <c r="F56" s="31">
-        <f>'Revenue'!F14-'Opex'!F10+'IS(Q)'!F28+'IS(Q)'!F18+'Revenue'!F19-(F79*$D$73*100)</f>
+        <f>'Revenue'!F14-'Opex'!F10+'IS(Q)'!F28+'IS(Q)'!F18+'Revenue'!F19-('Debt'!F8)</f>
       </c>
       <c r="G56" s="31">
-        <f>'Revenue'!G14-'Opex'!G10+'IS(Q)'!G28+'IS(Q)'!G18+'Revenue'!G19-(G79*$D$73*100)</f>
+        <f>'Revenue'!G14-'Opex'!G10+'IS(Q)'!G28+'IS(Q)'!G18+'Revenue'!G19-('Debt'!G8)</f>
       </c>
       <c r="H56" s="31">
-        <f>'Revenue'!H14-'Opex'!H10+'IS(Q)'!H28+'IS(Q)'!H18+'Revenue'!H19-(H79*$D$73*100)</f>
+        <f>'Revenue'!H14-'Opex'!H10+'IS(Q)'!H28+'IS(Q)'!H18+'Revenue'!H19-('Debt'!H8)</f>
       </c>
       <c r="I56" s="31">
-        <f>'Revenue'!I14-'Opex'!I10+'IS(Q)'!I28+'IS(Q)'!I18+'Revenue'!I19-(I79*$D$73*100)</f>
+        <f>'Revenue'!I14-'Opex'!I10+'IS(Q)'!I28+'IS(Q)'!I18+'Revenue'!I19-('Debt'!I8)</f>
       </c>
       <c r="J56" s="31">
-        <f>'Revenue'!J14-'Opex'!J10+'IS(Q)'!J28+'IS(Q)'!J18+'Revenue'!J19-(J79*$D$73*100)</f>
+        <f>'Revenue'!J14-'Opex'!J10+'IS(Q)'!J28+'IS(Q)'!J18+'Revenue'!J19-('Debt'!J8)</f>
       </c>
       <c r="K56" s="31">
-        <f>'Revenue'!K14-'Opex'!K10+'IS(Q)'!K28+'IS(Q)'!K18+'Revenue'!K19-(K79*$D$73*100)</f>
+        <f>'Revenue'!K14-'Opex'!K10+'IS(Q)'!K28+'IS(Q)'!K18+'Revenue'!K19-('Debt'!K8)</f>
       </c>
       <c r="L56" s="31">
-        <f>'Revenue'!L14-'Opex'!L10+'IS(Q)'!L28+'IS(Q)'!L18+'Revenue'!L19-(L79*$D$73*100)</f>
+        <f>'Revenue'!L14-'Opex'!L10+'IS(Q)'!L28+'IS(Q)'!L18+'Revenue'!L19-('Debt'!L8)</f>
       </c>
       <c r="M56" s="31">
-        <f>'Revenue'!M14-'Opex'!M10+'IS(Q)'!M28+'IS(Q)'!M18+'Revenue'!M19-(M79*$D$73*100)</f>
+        <f>'Revenue'!M14-'Opex'!M10+'IS(Q)'!M28+'IS(Q)'!M18+'Revenue'!M19-('Debt'!M8)</f>
       </c>
       <c r="N56" s="31">
-        <f>'Revenue'!N14-'Opex'!N10+'IS(Q)'!N28+'IS(Q)'!N18+'Revenue'!N19-(N79*$D$73*100)</f>
+        <f>'Revenue'!N14-'Opex'!N10+'IS(Q)'!N28+'IS(Q)'!N18+'Revenue'!N19-('Debt'!N8)</f>
       </c>
       <c r="O56" s="31">
-        <f>'Revenue'!O14-'Opex'!O10+'IS(Q)'!O28+'IS(Q)'!O18+'Revenue'!O19-(O79*$D$73*100)</f>
+        <f>'Revenue'!O14-'Opex'!O10+'IS(Q)'!O28+'IS(Q)'!O18+'Revenue'!O19-('Debt'!O8)</f>
       </c>
       <c r="P56" s="31">
-        <f>'Revenue'!P14-'Opex'!P10+'IS(Q)'!P28+'IS(Q)'!P18+'Revenue'!P19-(P79*$D$73*100)</f>
+        <f>'Revenue'!P14-'Opex'!P10+'IS(Q)'!P28+'IS(Q)'!P18+'Revenue'!P19-('Debt'!P8)</f>
       </c>
       <c r="Q56" s="31">
-        <f>'Revenue'!Q14-'Opex'!Q10+'IS(Q)'!Q28+'IS(Q)'!Q18+'Revenue'!Q19-(Q79*$D$73*100)</f>
+        <f>'Revenue'!Q14-'Opex'!Q10+'IS(Q)'!Q28+'IS(Q)'!Q18+'Revenue'!Q19-('Debt'!Q8)</f>
       </c>
       <c r="R56" s="31">
-        <f>'Revenue'!R14-'Opex'!R10+'IS(Q)'!R28+'IS(Q)'!R18+'Revenue'!R19-(R79*$D$73*100)</f>
+        <f>'Revenue'!R14-'Opex'!R10+'IS(Q)'!R28+'IS(Q)'!R18+'Revenue'!R19-('Debt'!R8)</f>
       </c>
       <c r="S56" s="31">
-        <f>'Revenue'!S14-'Opex'!S10+'IS(Q)'!S28+'IS(Q)'!S18+'Revenue'!S19-(S79*$D$73*100)</f>
+        <f>'Revenue'!S14-'Opex'!S10+'IS(Q)'!S28+'IS(Q)'!S18+'Revenue'!S19-('Debt'!S8)</f>
       </c>
       <c r="T56" s="31">
-        <f>'Revenue'!T14-'Opex'!T10+'IS(Q)'!T28+'IS(Q)'!T18+'Revenue'!T19-(T79*$D$73*100)</f>
+        <f>'Revenue'!T14-'Opex'!T10+'IS(Q)'!T28+'IS(Q)'!T18+'Revenue'!T19-('Debt'!T8)</f>
       </c>
       <c r="U56" s="31">
-        <f>'Revenue'!U14-'Opex'!U10+'IS(Q)'!U28+'IS(Q)'!U18+'Revenue'!U19-(U79*$D$73*100)</f>
+        <f>'Revenue'!U14-'Opex'!U10+'IS(Q)'!U28+'IS(Q)'!U18+'Revenue'!U19-('Debt'!U8)</f>
       </c>
       <c r="V56" s="31">
-        <f>'Revenue'!V14-'Opex'!V10+'IS(Q)'!V28+'IS(Q)'!V18+'Revenue'!V19-(V79*$D$73*100)</f>
+        <f>'Revenue'!V14-'Opex'!V10+'IS(Q)'!V28+'IS(Q)'!V18+'Revenue'!V19-('Debt'!V8)</f>
       </c>
       <c r="W56" s="31">
-        <f>'Revenue'!W14-'Opex'!W10+'IS(Q)'!W28+'IS(Q)'!W18+'Revenue'!W19-(W79*$D$73*100)</f>
+        <f>'Revenue'!W14-'Opex'!W10+'IS(Q)'!W28+'IS(Q)'!W18+'Revenue'!W19-('Debt'!W8)</f>
       </c>
       <c r="X56" s="31">
-        <f>'Revenue'!X14-'Opex'!X10+'IS(Q)'!X28+'IS(Q)'!X18+'Revenue'!X19-(X79*$D$73*100)</f>
+        <f>'Revenue'!X14-'Opex'!X10+'IS(Q)'!X28+'IS(Q)'!X18+'Revenue'!X19-('Debt'!X8)</f>
       </c>
       <c r="Y56" s="31">
-        <f>'Revenue'!Y14-'Opex'!Y10+'IS(Q)'!Y28+'IS(Q)'!Y18+'Revenue'!Y19-(Y79*$D$73*100)</f>
+        <f>'Revenue'!Y14-'Opex'!Y10+'IS(Q)'!Y28+'IS(Q)'!Y18+'Revenue'!Y19-('Debt'!Y8)</f>
       </c>
       <c r="Z56" s="31">
-        <f>'Revenue'!Z14-'Opex'!Z10+'IS(Q)'!Z28+'IS(Q)'!Z18+'Revenue'!Z19-(Z79*$D$73*100)</f>
+        <f>'Revenue'!Z14-'Opex'!Z10+'IS(Q)'!Z28+'IS(Q)'!Z18+'Revenue'!Z19-('Debt'!Z8)</f>
       </c>
       <c r="AA56" s="31">
-        <f>'Revenue'!AA14-'Opex'!AA10+'IS(Q)'!AA28+'IS(Q)'!AA18+'Revenue'!AA19-(AA79*$D$73*100)</f>
+        <f>'Revenue'!AA14-'Opex'!AA10+'IS(Q)'!AA28+'IS(Q)'!AA18+'Revenue'!AA19-('Debt'!AA8)</f>
       </c>
       <c r="AB56" s="31">
-        <f>'Revenue'!AB14-'Opex'!AB10+'IS(Q)'!AB28+'IS(Q)'!AB18+'Revenue'!AB19-(AB79*$D$73*100)</f>
+        <f>'Revenue'!AB14-'Opex'!AB10+'IS(Q)'!AB28+'IS(Q)'!AB18+'Revenue'!AB19-('Debt'!AB8)</f>
       </c>
       <c r="AC56" s="31">
-        <f>'Revenue'!AC14-'Opex'!AC10+'IS(Q)'!AC28+'IS(Q)'!AC18+'Revenue'!AC19-(AC79*$D$73*100)</f>
+        <f>'Revenue'!AC14-'Opex'!AC10+'IS(Q)'!AC28+'IS(Q)'!AC18+'Revenue'!AC19-('Debt'!AC8)</f>
       </c>
       <c r="AD56" s="31">
-        <f>'Revenue'!AD14-'Opex'!AD10+'IS(Q)'!AD28+'IS(Q)'!AD18+'Revenue'!AD19-(AD79*$D$73*100)</f>
+        <f>'Revenue'!AD14-'Opex'!AD10+'IS(Q)'!AD28+'IS(Q)'!AD18+'Revenue'!AD19-('Debt'!AD8)</f>
       </c>
       <c r="AE56" s="31">
-        <f>'Revenue'!AE14-'Opex'!AE10+'IS(Q)'!AE28+'IS(Q)'!AE18+'Revenue'!AE19-(AE79*$D$73*100)</f>
+        <f>'Revenue'!AE14-'Opex'!AE10+'IS(Q)'!AE28+'IS(Q)'!AE18+'Revenue'!AE19-('Debt'!AE8)</f>
       </c>
       <c r="AF56" s="31">
-        <f>'Revenue'!AF14-'Opex'!AF10+'IS(Q)'!AF28+'IS(Q)'!AF18+'Revenue'!AF19-(AF79*$D$73*100)</f>
+        <f>'Revenue'!AF14-'Opex'!AF10+'IS(Q)'!AF28+'IS(Q)'!AF18+'Revenue'!AF19-('Debt'!AF8)</f>
       </c>
       <c r="AG56" s="31">
-        <f>'Revenue'!AG14-'Opex'!AG10+'IS(Q)'!AG28+'IS(Q)'!AG18+'Revenue'!AG19-(AG79*$D$73*100)</f>
+        <f>'Revenue'!AG14-'Opex'!AG10+'IS(Q)'!AG28+'IS(Q)'!AG18+'Revenue'!AG19-('Debt'!AG8)</f>
       </c>
       <c r="AH56" s="31">
-        <f>'Revenue'!AH14-'Opex'!AH10+'IS(Q)'!AH28+'IS(Q)'!AH18+'Revenue'!AH19-(AH79*$D$73*100)</f>
+        <f>'Revenue'!AH14-'Opex'!AH10+'IS(Q)'!AH28+'IS(Q)'!AH18+'Revenue'!AH19-('Debt'!AH8)</f>
       </c>
       <c r="AI56" s="31">
-        <f>'Revenue'!AI14-'Opex'!AI10+'IS(Q)'!AI28+'IS(Q)'!AI18+'Revenue'!AI19-(AI79*$D$73*100)</f>
+        <f>'Revenue'!AI14-'Opex'!AI10+'IS(Q)'!AI28+'IS(Q)'!AI18+'Revenue'!AI19-('Debt'!AI8)</f>
       </c>
       <c r="AJ56" s="31">
-        <f>'Revenue'!AJ14-'Opex'!AJ10+'IS(Q)'!AJ28+'IS(Q)'!AJ18+'Revenue'!AJ19-(AJ79*$D$73*100)</f>
+        <f>'Revenue'!AJ14-'Opex'!AJ10+'IS(Q)'!AJ28+'IS(Q)'!AJ18+'Revenue'!AJ19-('Debt'!AJ8)</f>
       </c>
       <c r="AK56" s="31">
-        <f>'Revenue'!AK14-'Opex'!AK10+'IS(Q)'!AK28+'IS(Q)'!AK18+'Revenue'!AK19-(AK79*$D$73*100)</f>
+        <f>'Revenue'!AK14-'Opex'!AK10+'IS(Q)'!AK28+'IS(Q)'!AK18+'Revenue'!AK19-('Debt'!AK8)</f>
       </c>
       <c r="AL56" s="31">
-        <f>'Revenue'!AL14-'Opex'!AL10+'IS(Q)'!AL28+'IS(Q)'!AL18+'Revenue'!AL19-(AL79*$D$73*100)</f>
+        <f>'Revenue'!AL14-'Opex'!AL10+'IS(Q)'!AL28+'IS(Q)'!AL18+'Revenue'!AL19-('Debt'!AL8)</f>
       </c>
       <c r="AM56" s="31">
-        <f>'Revenue'!AM14-'Opex'!AM10+'IS(Q)'!AM28+'IS(Q)'!AM18+'Revenue'!AM19-(AM79*$D$73*100)</f>
+        <f>'Revenue'!AM14-'Opex'!AM10+'IS(Q)'!AM28+'IS(Q)'!AM18+'Revenue'!AM19-('Debt'!AM8)</f>
       </c>
       <c r="AN56" s="31">
-        <f>'Revenue'!AN14-'Opex'!AN10+'IS(Q)'!AN28+'IS(Q)'!AN18+'Revenue'!AN19-(AN79*$D$73*100)</f>
+        <f>'Revenue'!AN14-'Opex'!AN10+'IS(Q)'!AN28+'IS(Q)'!AN18+'Revenue'!AN19-('Debt'!AN8)</f>
       </c>
       <c r="AO56" s="31">
-        <f>'Revenue'!AO14-'Opex'!AO10+'IS(Q)'!AO28+'IS(Q)'!AO18+'Revenue'!AO19-(AO79*$D$73*100)</f>
+        <f>'Revenue'!AO14-'Opex'!AO10+'IS(Q)'!AO28+'IS(Q)'!AO18+'Revenue'!AO19-('Debt'!AO8)</f>
       </c>
       <c r="AP56" s="31">
-        <f>'Revenue'!AP14-'Opex'!AP10+'IS(Q)'!AP28+'IS(Q)'!AP18+'Revenue'!AP19-(AP79*$D$73*100)</f>
+        <f>'Revenue'!AP14-'Opex'!AP10+'IS(Q)'!AP28+'IS(Q)'!AP18+'Revenue'!AP19-('Debt'!AP8)</f>
       </c>
       <c r="AQ56" s="31">
-        <f>'Revenue'!AQ14-'Opex'!AQ10+'IS(Q)'!AQ28+'IS(Q)'!AQ18+'Revenue'!AQ19-(AQ79*$D$73*100)</f>
+        <f>'Revenue'!AQ14-'Opex'!AQ10+'IS(Q)'!AQ28+'IS(Q)'!AQ18+'Revenue'!AQ19-('Debt'!AQ8)</f>
       </c>
       <c r="AR56" s="31">
-        <f>'Revenue'!AR14-'Opex'!AR10+'IS(Q)'!AR28+'IS(Q)'!AR18+'Revenue'!AR19-(AR79*$D$73*100)</f>
+        <f>'Revenue'!AR14-'Opex'!AR10+'IS(Q)'!AR28+'IS(Q)'!AR18+'Revenue'!AR19-('Debt'!AR8)</f>
       </c>
       <c r="AS56" s="31">
-        <f>'Revenue'!AS14-'Opex'!AS10+'IS(Q)'!AS28+'IS(Q)'!AS18+'Revenue'!AS19-(AS79*$D$73*100)</f>
+        <f>'Revenue'!AS14-'Opex'!AS10+'IS(Q)'!AS28+'IS(Q)'!AS18+'Revenue'!AS19-('Debt'!AS8)</f>
       </c>
       <c r="AT56" s="31">
-        <f>'Revenue'!AT14-'Opex'!AT10+'IS(Q)'!AT28+'IS(Q)'!AT18+'Revenue'!AT19-(AT79*$D$73*100)</f>
+        <f>'Revenue'!AT14-'Opex'!AT10+'IS(Q)'!AT28+'IS(Q)'!AT18+'Revenue'!AT19-('Debt'!AT8)</f>
       </c>
       <c r="AU56" s="31">
-        <f>'Revenue'!AU14-'Opex'!AU10+'IS(Q)'!AU28+'IS(Q)'!AU18+'Revenue'!AU19-(AU79*$D$73*100)</f>
+        <f>'Revenue'!AU14-'Opex'!AU10+'IS(Q)'!AU28+'IS(Q)'!AU18+'Revenue'!AU19-('Debt'!AU8)</f>
       </c>
       <c r="AV56" s="31">
-        <f>'Revenue'!AV14-'Opex'!AV10+'IS(Q)'!AV28+'IS(Q)'!AV18+'Revenue'!AV19-(AV79*$D$73*100)</f>
+        <f>'Revenue'!AV14-'Opex'!AV10+'IS(Q)'!AV28+'IS(Q)'!AV18+'Revenue'!AV19-('Debt'!AV8)</f>
       </c>
       <c r="AW56" s="31">
-        <f>'Revenue'!AW14-'Opex'!AW10+'IS(Q)'!AW28+'IS(Q)'!AW18+'Revenue'!AW19-(AW79*$D$73*100)</f>
+        <f>'Revenue'!AW14-'Opex'!AW10+'IS(Q)'!AW28+'IS(Q)'!AW18+'Revenue'!AW19-('Debt'!AW8)</f>
       </c>
       <c r="AX56" s="31">
-        <f>'Revenue'!AX14-'Opex'!AX10+'IS(Q)'!AX28+'IS(Q)'!AX18+'Revenue'!AX19-(AX79*$D$73*100)</f>
+        <f>'Revenue'!AX14-'Opex'!AX10+'IS(Q)'!AX28+'IS(Q)'!AX18+'Revenue'!AX19-('Debt'!AX8)</f>
       </c>
       <c r="AY56" s="31">
-        <f>'Revenue'!AY14-'Opex'!AY10+'IS(Q)'!AY28+'IS(Q)'!AY18+'Revenue'!AY19-(AY79*$D$73*100)</f>
+        <f>'Revenue'!AY14-'Opex'!AY10+'IS(Q)'!AY28+'IS(Q)'!AY18+'Revenue'!AY19-('Debt'!AY8)</f>
       </c>
       <c r="AZ56" s="31">
-        <f>'Revenue'!AZ14-'Opex'!AZ10+'IS(Q)'!AZ28+'IS(Q)'!AZ18+'Revenue'!AZ19-(AZ79*$D$73*100)</f>
+        <f>'Revenue'!AZ14-'Opex'!AZ10+'IS(Q)'!AZ28+'IS(Q)'!AZ18+'Revenue'!AZ19-('Debt'!AZ8)</f>
       </c>
       <c r="BA56" s="31">
-        <f>'Revenue'!BA14-'Opex'!BA10+'IS(Q)'!BA28+'IS(Q)'!BA18+'Revenue'!BA19-(BA79*$D$73*100)</f>
+        <f>'Revenue'!BA14-'Opex'!BA10+'IS(Q)'!BA28+'IS(Q)'!BA18+'Revenue'!BA19-('Debt'!BA8)</f>
       </c>
       <c r="BB56" s="31">
-        <f>'Revenue'!BB14-'Opex'!BB10+'IS(Q)'!BB28+'IS(Q)'!BB18+'Revenue'!BB19-(BB79*$D$73*100)</f>
+        <f>'Revenue'!BB14-'Opex'!BB10+'IS(Q)'!BB28+'IS(Q)'!BB18+'Revenue'!BB19-('Debt'!BB8)</f>
       </c>
       <c r="BC56" s="31">
-        <f>'Revenue'!BC14-'Opex'!BC10+'IS(Q)'!BC28+'IS(Q)'!BC18+'Revenue'!BC19-(BC79*$D$73*100)</f>
+        <f>'Revenue'!BC14-'Opex'!BC10+'IS(Q)'!BC28+'IS(Q)'!BC18+'Revenue'!BC19-('Debt'!BC8)</f>
       </c>
       <c r="BD56" s="31">
-        <f>'Revenue'!BD14-'Opex'!BD10+'IS(Q)'!BD28+'IS(Q)'!BD18+'Revenue'!BD19-(BD79*$D$73*100)</f>
+        <f>'Revenue'!BD14-'Opex'!BD10+'IS(Q)'!BD28+'IS(Q)'!BD18+'Revenue'!BD19-('Debt'!BD8)</f>
       </c>
       <c r="BE56" s="31">
-        <f>'Revenue'!BE14-'Opex'!BE10+'IS(Q)'!BE28+'IS(Q)'!BE18+'Revenue'!BE19-(BE79*$D$73*100)</f>
+        <f>'Revenue'!BE14-'Opex'!BE10+'IS(Q)'!BE28+'IS(Q)'!BE18+'Revenue'!BE19-('Debt'!BE8)</f>
       </c>
       <c r="BF56" s="31">
-        <f>'Revenue'!BF14-'Opex'!BF10+'IS(Q)'!BF28+'IS(Q)'!BF18+'Revenue'!BF19-(BF79*$D$73*100)</f>
+        <f>'Revenue'!BF14-'Opex'!BF10+'IS(Q)'!BF28+'IS(Q)'!BF18+'Revenue'!BF19-('Debt'!BF8)</f>
       </c>
       <c r="BG56" s="31">
-        <f>'Revenue'!BG14-'Opex'!BG10+'IS(Q)'!BG28+'IS(Q)'!BG18+'Revenue'!BG19-(BG79*$D$73*100)</f>
+        <f>'Revenue'!BG14-'Opex'!BG10+'IS(Q)'!BG28+'IS(Q)'!BG18+'Revenue'!BG19-('Debt'!BG8)</f>
       </c>
       <c r="BH56" s="31">
-        <f>'Revenue'!BH14-'Opex'!BH10+'IS(Q)'!BH28+'IS(Q)'!BH18+'Revenue'!BH19-(BH79*$D$73*100)</f>
+        <f>'Revenue'!BH14-'Opex'!BH10+'IS(Q)'!BH28+'IS(Q)'!BH18+'Revenue'!BH19-('Debt'!BH8)</f>
       </c>
       <c r="BI56" s="31">
-        <f>'Revenue'!BI14-'Opex'!BI10+'IS(Q)'!BI28+'IS(Q)'!BI18+'Revenue'!BI19-(BI79*$D$73*100)</f>
+        <f>'Revenue'!BI14-'Opex'!BI10+'IS(Q)'!BI28+'IS(Q)'!BI18+'Revenue'!BI19-('Debt'!BI8)</f>
       </c>
       <c r="BJ56" s="31">
-        <f>'Revenue'!BJ14-'Opex'!BJ10+'IS(Q)'!BJ28+'IS(Q)'!BJ18+'Revenue'!BJ19-(BJ79*$D$73*100)</f>
+        <f>'Revenue'!BJ14-'Opex'!BJ10+'IS(Q)'!BJ28+'IS(Q)'!BJ18+'Revenue'!BJ19-('Debt'!BJ8)</f>
       </c>
       <c r="BK56" s="31">
-        <f>'Revenue'!BK14-'Opex'!BK10+'IS(Q)'!BK28+'IS(Q)'!BK18+'Revenue'!BK19-(BK79*$D$73*100)</f>
+        <f>'Revenue'!BK14-'Opex'!BK10+'IS(Q)'!BK28+'IS(Q)'!BK18+'Revenue'!BK19-('Debt'!BK8)</f>
       </c>
       <c r="BL56" s="31">
-        <f>'Revenue'!BL14-'Opex'!BL10+'IS(Q)'!BL28+'IS(Q)'!BL18+'Revenue'!BL19-(BL79*$D$73*100)</f>
+        <f>'Revenue'!BL14-'Opex'!BL10+'IS(Q)'!BL28+'IS(Q)'!BL18+'Revenue'!BL19-('Debt'!BL8)</f>
       </c>
       <c r="BM56" s="31">
-        <f>'Revenue'!BM14-'Opex'!BM10+'IS(Q)'!BM28+'IS(Q)'!BM18+'Revenue'!BM19-(BM79*$D$73*100)</f>
+        <f>'Revenue'!BM14-'Opex'!BM10+'IS(Q)'!BM28+'IS(Q)'!BM18+'Revenue'!BM19-('Debt'!BM8)</f>
       </c>
       <c r="BN56" s="31">
-        <f>'Revenue'!BN14-'Opex'!BN10+'IS(Q)'!BN28+'IS(Q)'!BN18+'Revenue'!BN19-(BN79*$D$73*100)</f>
+        <f>'Revenue'!BN14-'Opex'!BN10+'IS(Q)'!BN28+'IS(Q)'!BN18+'Revenue'!BN19-('Debt'!BN8)</f>
       </c>
       <c r="BO56" s="31">
-        <f>'Revenue'!BO14-'Opex'!BO10+'IS(Q)'!BO28+'IS(Q)'!BO18+'Revenue'!BO19-(BO79*$D$73*100)</f>
+        <f>'Revenue'!BO14-'Opex'!BO10+'IS(Q)'!BO28+'IS(Q)'!BO18+'Revenue'!BO19-('Debt'!BO8)</f>
       </c>
       <c r="BP56" s="31">
-        <f>'Revenue'!BP14-'Opex'!BP10+'IS(Q)'!BP28+'IS(Q)'!BP18+'Revenue'!BP19-(BP79*$D$73*100)</f>
+        <f>'Revenue'!BP14-'Opex'!BP10+'IS(Q)'!BP28+'IS(Q)'!BP18+'Revenue'!BP19-('Debt'!BP8)</f>
       </c>
       <c r="BQ56" s="31">
-        <f>'Revenue'!BQ14-'Opex'!BQ10+'IS(Q)'!BQ28+'IS(Q)'!BQ18+'Revenue'!BQ19-(BQ79*$D$73*100)</f>
+        <f>'Revenue'!BQ14-'Opex'!BQ10+'IS(Q)'!BQ28+'IS(Q)'!BQ18+'Revenue'!BQ19-('Debt'!BQ8)</f>
       </c>
       <c r="BR56" s="31">
-        <f>'Revenue'!BR14-'Opex'!BR10+'IS(Q)'!BR28+'IS(Q)'!BR18+'Revenue'!BR19-(BR79*$D$73*100)</f>
+        <f>'Revenue'!BR14-'Opex'!BR10+'IS(Q)'!BR28+'IS(Q)'!BR18+'Revenue'!BR19-('Debt'!BR8)</f>
       </c>
       <c r="BS56" s="31">
-        <f>'Revenue'!BS14-'Opex'!BS10+'IS(Q)'!BS28+'IS(Q)'!BS18+'Revenue'!BS19-(BS79*$D$73*100)</f>
+        <f>'Revenue'!BS14-'Opex'!BS10+'IS(Q)'!BS28+'IS(Q)'!BS18+'Revenue'!BS19-('Debt'!BS8)</f>
       </c>
       <c r="BT56" s="31">
-        <f>'Revenue'!BT14-'Opex'!BT10+'IS(Q)'!BT28+'IS(Q)'!BT18+'Revenue'!BT19-(BT79*$D$73*100)</f>
+        <f>'Revenue'!BT14-'Opex'!BT10+'IS(Q)'!BT28+'IS(Q)'!BT18+'Revenue'!BT19-('Debt'!BT8)</f>
       </c>
       <c r="BU56" s="31">
-        <f>'Revenue'!BU14-'Opex'!BU10+'IS(Q)'!BU28+'IS(Q)'!BU18+'Revenue'!BU19-(BU79*$D$73*100)</f>
+        <f>'Revenue'!BU14-'Opex'!BU10+'IS(Q)'!BU28+'IS(Q)'!BU18+'Revenue'!BU19-('Debt'!BU8)</f>
       </c>
       <c r="BV56" s="31">
-        <f>'Revenue'!BV14-'Opex'!BV10+'IS(Q)'!BV28+'IS(Q)'!BV18+'Revenue'!BV19-(BV79*$D$73*100)</f>
+        <f>'Revenue'!BV14-'Opex'!BV10+'IS(Q)'!BV28+'IS(Q)'!BV18+'Revenue'!BV19-('Debt'!BV8)</f>
       </c>
       <c r="BW56" s="31">
-        <f>'Revenue'!BW14-'Opex'!BW10+'IS(Q)'!BW28+'IS(Q)'!BW18+'Revenue'!BW19-(BW79*$D$73*100)</f>
+        <f>'Revenue'!BW14-'Opex'!BW10+'IS(Q)'!BW28+'IS(Q)'!BW18+'Revenue'!BW19-('Debt'!BW8)</f>
       </c>
       <c r="BX56" s="31">
-        <f>'Revenue'!BX14-'Opex'!BX10+'IS(Q)'!BX28+'IS(Q)'!BX18+'Revenue'!BX19-(BX79*$D$73*100)</f>
+        <f>'Revenue'!BX14-'Opex'!BX10+'IS(Q)'!BX28+'IS(Q)'!BX18+'Revenue'!BX19-('Debt'!BX8)</f>
       </c>
       <c r="BY56" s="31">
-        <f>'Revenue'!BY14-'Opex'!BY10+'IS(Q)'!BY28+'IS(Q)'!BY18+'Revenue'!BY19-(BY79*$D$73*100)</f>
+        <f>'Revenue'!BY14-'Opex'!BY10+'IS(Q)'!BY28+'IS(Q)'!BY18+'Revenue'!BY19-('Debt'!BY8)</f>
       </c>
       <c r="BZ56" s="31">
-        <f>'Revenue'!BZ14-'Opex'!BZ10+'IS(Q)'!BZ28+'IS(Q)'!BZ18+'Revenue'!BZ19-(BZ79*$D$73*100)</f>
+        <f>'Revenue'!BZ14-'Opex'!BZ10+'IS(Q)'!BZ28+'IS(Q)'!BZ18+'Revenue'!BZ19-('Debt'!BZ8)</f>
       </c>
       <c r="CA56" s="31">
-        <f>'Revenue'!CA14-'Opex'!CA10+'IS(Q)'!CA28+'IS(Q)'!CA18+'Revenue'!CA19-(CA79*$D$73*100)</f>
+        <f>'Revenue'!CA14-'Opex'!CA10+'IS(Q)'!CA28+'IS(Q)'!CA18+'Revenue'!CA19-('Debt'!CA8)</f>
       </c>
       <c r="CB56" s="31">
-        <f>'Revenue'!CB14-'Opex'!CB10+'IS(Q)'!CB28+'IS(Q)'!CB18+'Revenue'!CB19-(CB79*$D$73*100)</f>
+        <f>'Revenue'!CB14-'Opex'!CB10+'IS(Q)'!CB28+'IS(Q)'!CB18+'Revenue'!CB19-('Debt'!CB8)</f>
       </c>
       <c r="CC56" s="31">
-        <f>'Revenue'!CC14-'Opex'!CC10+'IS(Q)'!CC28+'IS(Q)'!CC18+'Revenue'!CC19-(CC79*$D$73*100)</f>
+        <f>'Revenue'!CC14-'Opex'!CC10+'IS(Q)'!CC28+'IS(Q)'!CC18+'Revenue'!CC19-('Debt'!CC8)</f>
       </c>
       <c r="CD56" s="31">
-        <f>'Revenue'!CD14-'Opex'!CD10+'IS(Q)'!CD28+'IS(Q)'!CD18+'Revenue'!CD19-(CD79*$D$73*100)</f>
+        <f>'Revenue'!CD14-'Opex'!CD10+'IS(Q)'!CD28+'IS(Q)'!CD18+'Revenue'!CD19-('Debt'!CD8)</f>
       </c>
       <c r="CE56" s="31">
-        <f>'Revenue'!CE14-'Opex'!CE10+'IS(Q)'!CE28+'IS(Q)'!CE18+'Revenue'!CE19-(CE79*$D$73*100)</f>
+        <f>'Revenue'!CE14-'Opex'!CE10+'IS(Q)'!CE28+'IS(Q)'!CE18+'Revenue'!CE19-('Debt'!CE8)</f>
       </c>
       <c r="CF56" s="31">
-        <f>'Revenue'!CF14-'Opex'!CF10+'IS(Q)'!CF28+'IS(Q)'!CF18+'Revenue'!CF19-(CF79*$D$73*100)</f>
+        <f>'Revenue'!CF14-'Opex'!CF10+'IS(Q)'!CF28+'IS(Q)'!CF18+'Revenue'!CF19-('Debt'!CF8)</f>
       </c>
       <c r="CG56" s="31">
-        <f>'Revenue'!CG14-'Opex'!CG10+'IS(Q)'!CG28+'IS(Q)'!CG18+'Revenue'!CG19-(CG79*$D$73*100)</f>
+        <f>'Revenue'!CG14-'Opex'!CG10+'IS(Q)'!CG28+'IS(Q)'!CG18+'Revenue'!CG19-('Debt'!CG8)</f>
       </c>
       <c r="CH56" s="31">
-        <f>'Revenue'!CH14-'Opex'!CH10+'IS(Q)'!CH28+'IS(Q)'!CH18+'Revenue'!CH19-(CH79*$D$73*100)</f>
+        <f>'Revenue'!CH14-'Opex'!CH10+'IS(Q)'!CH28+'IS(Q)'!CH18+'Revenue'!CH19-('Debt'!CH8)</f>
       </c>
       <c r="CI56" s="31">
-        <f>'Revenue'!CI14-'Opex'!CI10+'IS(Q)'!CI28+'IS(Q)'!CI18+'Revenue'!CI19-(CI79*$D$73*100)</f>
+        <f>'Revenue'!CI14-'Opex'!CI10+'IS(Q)'!CI28+'IS(Q)'!CI18+'Revenue'!CI19-('Debt'!CI8)</f>
       </c>
       <c r="CJ56" s="31">
-        <f>'Revenue'!CJ14-'Opex'!CJ10+'IS(Q)'!CJ28+'IS(Q)'!CJ18+'Revenue'!CJ19-(CJ79*$D$73*100)</f>
+        <f>'Revenue'!CJ14-'Opex'!CJ10+'IS(Q)'!CJ28+'IS(Q)'!CJ18+'Revenue'!CJ19-('Debt'!CJ8)</f>
       </c>
       <c r="CK56" s="31">
-        <f>'Revenue'!CK14-'Opex'!CK10+'IS(Q)'!CK28+'IS(Q)'!CK18+'Revenue'!CK19-(CK79*$D$73*100)</f>
+        <f>'Revenue'!CK14-'Opex'!CK10+'IS(Q)'!CK28+'IS(Q)'!CK18+'Revenue'!CK19-('Debt'!CK8)</f>
       </c>
       <c r="CL56" s="31">
-        <f>'Revenue'!CL14-'Opex'!CL10+'IS(Q)'!CL28-$D$74*100+'IS(Q)'!CL18+'Revenue'!CL19-(CL79*$D$73*100)</f>
+        <f>'Revenue'!CL14-'Opex'!CL10+'IS(Q)'!CL28-$D$73*100+'IS(Q)'!CL18+'Revenue'!CL19-('Debt'!CL8)</f>
       </c>
     </row>
     <row r="57" spans="2:90" x14ac:dyDescent="0.25">
@@ -29490,262 +29250,262 @@
         <v>210</v>
       </c>
       <c r="E57" s="31">
-        <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E18+'Revenue'!E19-(E79*$D$73*100)</f>
+        <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
       </c>
       <c r="F57" s="31">
-        <f>'Revenue'!F14-'Opex'!F10+'IS(Q)'!F18+'Revenue'!F19-(F79*$D$73*100)</f>
+        <f>'Revenue'!F14-'Opex'!F10+'IS(Q)'!F18+'Revenue'!F19-('Debt'!F8)</f>
       </c>
       <c r="G57" s="31">
-        <f>'Revenue'!G14-'Opex'!G10+'IS(Q)'!G18+'Revenue'!G19-(G79*$D$73*100)</f>
+        <f>'Revenue'!G14-'Opex'!G10+'IS(Q)'!G18+'Revenue'!G19-('Debt'!G8)</f>
       </c>
       <c r="H57" s="31">
-        <f>'Revenue'!H14-'Opex'!H10+'IS(Q)'!H18+'Revenue'!H19-(H79*$D$73*100)</f>
+        <f>'Revenue'!H14-'Opex'!H10+'IS(Q)'!H18+'Revenue'!H19-('Debt'!H8)</f>
       </c>
       <c r="I57" s="31">
-        <f>'Revenue'!I14-'Opex'!I10+'IS(Q)'!I18+'Revenue'!I19-(I79*$D$73*100)</f>
+        <f>'Revenue'!I14-'Opex'!I10+'IS(Q)'!I18+'Revenue'!I19-('Debt'!I8)</f>
       </c>
       <c r="J57" s="31">
-        <f>'Revenue'!J14-'Opex'!J10+'IS(Q)'!J18+'Revenue'!J19-(J79*$D$73*100)</f>
+        <f>'Revenue'!J14-'Opex'!J10+'IS(Q)'!J18+'Revenue'!J19-('Debt'!J8)</f>
       </c>
       <c r="K57" s="31">
-        <f>'Revenue'!K14-'Opex'!K10+'IS(Q)'!K18+'Revenue'!K19-(K79*$D$73*100)</f>
+        <f>'Revenue'!K14-'Opex'!K10+'IS(Q)'!K18+'Revenue'!K19-('Debt'!K8)</f>
       </c>
       <c r="L57" s="31">
-        <f>'Revenue'!L14-'Opex'!L10+'IS(Q)'!L18+'Revenue'!L19-(L79*$D$73*100)</f>
+        <f>'Revenue'!L14-'Opex'!L10+'IS(Q)'!L18+'Revenue'!L19-('Debt'!L8)</f>
       </c>
       <c r="M57" s="31">
-        <f>'Revenue'!M14-'Opex'!M10+'IS(Q)'!M18+'Revenue'!M19-(M79*$D$73*100)</f>
+        <f>'Revenue'!M14-'Opex'!M10+'IS(Q)'!M18+'Revenue'!M19-('Debt'!M8)</f>
       </c>
       <c r="N57" s="31">
-        <f>'Revenue'!N14-'Opex'!N10+'IS(Q)'!N18+'Revenue'!N19-(N79*$D$73*100)</f>
+        <f>'Revenue'!N14-'Opex'!N10+'IS(Q)'!N18+'Revenue'!N19-('Debt'!N8)</f>
       </c>
       <c r="O57" s="31">
-        <f>'Revenue'!O14-'Opex'!O10+'IS(Q)'!O18+'Revenue'!O19-(O79*$D$73*100)</f>
+        <f>'Revenue'!O14-'Opex'!O10+'IS(Q)'!O18+'Revenue'!O19-('Debt'!O8)</f>
       </c>
       <c r="P57" s="31">
-        <f>'Revenue'!P14-'Opex'!P10+'IS(Q)'!P18+'Revenue'!P19-(P79*$D$73*100)</f>
+        <f>'Revenue'!P14-'Opex'!P10+'IS(Q)'!P18+'Revenue'!P19-('Debt'!P8)</f>
       </c>
       <c r="Q57" s="31">
-        <f>'Revenue'!Q14-'Opex'!Q10+'IS(Q)'!Q18+'Revenue'!Q19-(Q79*$D$73*100)</f>
+        <f>'Revenue'!Q14-'Opex'!Q10+'IS(Q)'!Q18+'Revenue'!Q19-('Debt'!Q8)</f>
       </c>
       <c r="R57" s="31">
-        <f>'Revenue'!R14-'Opex'!R10+'IS(Q)'!R18+'Revenue'!R19-(R79*$D$73*100)</f>
+        <f>'Revenue'!R14-'Opex'!R10+'IS(Q)'!R18+'Revenue'!R19-('Debt'!R8)</f>
       </c>
       <c r="S57" s="31">
-        <f>'Revenue'!S14-'Opex'!S10+'IS(Q)'!S18+'Revenue'!S19-(S79*$D$73*100)</f>
+        <f>'Revenue'!S14-'Opex'!S10+'IS(Q)'!S18+'Revenue'!S19-('Debt'!S8)</f>
       </c>
       <c r="T57" s="31">
-        <f>'Revenue'!T14-'Opex'!T10+'IS(Q)'!T18+'Revenue'!T19-(T79*$D$73*100)</f>
+        <f>'Revenue'!T14-'Opex'!T10+'IS(Q)'!T18+'Revenue'!T19-('Debt'!T8)</f>
       </c>
       <c r="U57" s="31">
-        <f>'Revenue'!U14-'Opex'!U10+'IS(Q)'!U18+'Revenue'!U19-(U79*$D$73*100)</f>
+        <f>'Revenue'!U14-'Opex'!U10+'IS(Q)'!U18+'Revenue'!U19-('Debt'!U8)</f>
       </c>
       <c r="V57" s="31">
-        <f>'Revenue'!V14-'Opex'!V10+'IS(Q)'!V18+'Revenue'!V19-(V79*$D$73*100)</f>
+        <f>'Revenue'!V14-'Opex'!V10+'IS(Q)'!V18+'Revenue'!V19-('Debt'!V8)</f>
       </c>
       <c r="W57" s="31">
-        <f>'Revenue'!W14-'Opex'!W10+'IS(Q)'!W18+'Revenue'!W19-(W79*$D$73*100)</f>
+        <f>'Revenue'!W14-'Opex'!W10+'IS(Q)'!W18+'Revenue'!W19-('Debt'!W8)</f>
       </c>
       <c r="X57" s="31">
-        <f>'Revenue'!X14-'Opex'!X10+'IS(Q)'!X18+'Revenue'!X19-(X79*$D$73*100)</f>
+        <f>'Revenue'!X14-'Opex'!X10+'IS(Q)'!X18+'Revenue'!X19-('Debt'!X8)</f>
       </c>
       <c r="Y57" s="31">
-        <f>'Revenue'!Y14-'Opex'!Y10+'IS(Q)'!Y18+'Revenue'!Y19-(Y79*$D$73*100)</f>
+        <f>'Revenue'!Y14-'Opex'!Y10+'IS(Q)'!Y18+'Revenue'!Y19-('Debt'!Y8)</f>
       </c>
       <c r="Z57" s="31">
-        <f>'Revenue'!Z14-'Opex'!Z10+'IS(Q)'!Z18+'Revenue'!Z19-(Z79*$D$73*100)</f>
+        <f>'Revenue'!Z14-'Opex'!Z10+'IS(Q)'!Z18+'Revenue'!Z19-('Debt'!Z8)</f>
       </c>
       <c r="AA57" s="31">
-        <f>'Revenue'!AA14-'Opex'!AA10+'IS(Q)'!AA18+'Revenue'!AA19-(AA79*$D$73*100)</f>
+        <f>'Revenue'!AA14-'Opex'!AA10+'IS(Q)'!AA18+'Revenue'!AA19-('Debt'!AA8)</f>
       </c>
       <c r="AB57" s="31">
-        <f>'Revenue'!AB14-'Opex'!AB10+'IS(Q)'!AB18+'Revenue'!AB19-(AB79*$D$73*100)</f>
+        <f>'Revenue'!AB14-'Opex'!AB10+'IS(Q)'!AB18+'Revenue'!AB19-('Debt'!AB8)</f>
       </c>
       <c r="AC57" s="31">
-        <f>'Revenue'!AC14-'Opex'!AC10+'IS(Q)'!AC18+'Revenue'!AC19-(AC79*$D$73*100)</f>
+        <f>'Revenue'!AC14-'Opex'!AC10+'IS(Q)'!AC18+'Revenue'!AC19-('Debt'!AC8)</f>
       </c>
       <c r="AD57" s="31">
-        <f>'Revenue'!AD14-'Opex'!AD10+'IS(Q)'!AD18+'Revenue'!AD19-(AD79*$D$73*100)</f>
+        <f>'Revenue'!AD14-'Opex'!AD10+'IS(Q)'!AD18+'Revenue'!AD19-('Debt'!AD8)</f>
       </c>
       <c r="AE57" s="31">
-        <f>'Revenue'!AE14-'Opex'!AE10+'IS(Q)'!AE18+'Revenue'!AE19-(AE79*$D$73*100)</f>
+        <f>'Revenue'!AE14-'Opex'!AE10+'IS(Q)'!AE18+'Revenue'!AE19-('Debt'!AE8)</f>
       </c>
       <c r="AF57" s="31">
-        <f>'Revenue'!AF14-'Opex'!AF10+'IS(Q)'!AF18+'Revenue'!AF19-(AF79*$D$73*100)</f>
+        <f>'Revenue'!AF14-'Opex'!AF10+'IS(Q)'!AF18+'Revenue'!AF19-('Debt'!AF8)</f>
       </c>
       <c r="AG57" s="31">
-        <f>'Revenue'!AG14-'Opex'!AG10+'IS(Q)'!AG18+'Revenue'!AG19-(AG79*$D$73*100)</f>
+        <f>'Revenue'!AG14-'Opex'!AG10+'IS(Q)'!AG18+'Revenue'!AG19-('Debt'!AG8)</f>
       </c>
       <c r="AH57" s="31">
-        <f>'Revenue'!AH14-'Opex'!AH10+'IS(Q)'!AH18+'Revenue'!AH19-(AH79*$D$73*100)</f>
+        <f>'Revenue'!AH14-'Opex'!AH10+'IS(Q)'!AH18+'Revenue'!AH19-('Debt'!AH8)</f>
       </c>
       <c r="AI57" s="31">
-        <f>'Revenue'!AI14-'Opex'!AI10+'IS(Q)'!AI18+'Revenue'!AI19-(AI79*$D$73*100)</f>
+        <f>'Revenue'!AI14-'Opex'!AI10+'IS(Q)'!AI18+'Revenue'!AI19-('Debt'!AI8)</f>
       </c>
       <c r="AJ57" s="31">
-        <f>'Revenue'!AJ14-'Opex'!AJ10+'IS(Q)'!AJ18+'Revenue'!AJ19-(AJ79*$D$73*100)</f>
+        <f>'Revenue'!AJ14-'Opex'!AJ10+'IS(Q)'!AJ18+'Revenue'!AJ19-('Debt'!AJ8)</f>
       </c>
       <c r="AK57" s="31">
-        <f>'Revenue'!AK14-'Opex'!AK10+'IS(Q)'!AK18+'Revenue'!AK19-(AK79*$D$73*100)</f>
+        <f>'Revenue'!AK14-'Opex'!AK10+'IS(Q)'!AK18+'Revenue'!AK19-('Debt'!AK8)</f>
       </c>
       <c r="AL57" s="31">
-        <f>'Revenue'!AL14-'Opex'!AL10+'IS(Q)'!AL18+'Revenue'!AL19-(AL79*$D$73*100)</f>
+        <f>'Revenue'!AL14-'Opex'!AL10+'IS(Q)'!AL18+'Revenue'!AL19-('Debt'!AL8)</f>
       </c>
       <c r="AM57" s="31">
-        <f>'Revenue'!AM14-'Opex'!AM10+'IS(Q)'!AM18+'Revenue'!AM19-(AM79*$D$73*100)</f>
+        <f>'Revenue'!AM14-'Opex'!AM10+'IS(Q)'!AM18+'Revenue'!AM19-('Debt'!AM8)</f>
       </c>
       <c r="AN57" s="31">
-        <f>'Revenue'!AN14-'Opex'!AN10+'IS(Q)'!AN18+'Revenue'!AN19-(AN79*$D$73*100)</f>
+        <f>'Revenue'!AN14-'Opex'!AN10+'IS(Q)'!AN18+'Revenue'!AN19-('Debt'!AN8)</f>
       </c>
       <c r="AO57" s="31">
-        <f>'Revenue'!AO14-'Opex'!AO10+'IS(Q)'!AO18+'Revenue'!AO19-(AO79*$D$73*100)</f>
+        <f>'Revenue'!AO14-'Opex'!AO10+'IS(Q)'!AO18+'Revenue'!AO19-('Debt'!AO8)</f>
       </c>
       <c r="AP57" s="31">
-        <f>'Revenue'!AP14-'Opex'!AP10+'IS(Q)'!AP18+'Revenue'!AP19-(AP79*$D$73*100)</f>
+        <f>'Revenue'!AP14-'Opex'!AP10+'IS(Q)'!AP18+'Revenue'!AP19-('Debt'!AP8)</f>
       </c>
       <c r="AQ57" s="31">
-        <f>'Revenue'!AQ14-'Opex'!AQ10+'IS(Q)'!AQ18+'Revenue'!AQ19-(AQ79*$D$73*100)</f>
+        <f>'Revenue'!AQ14-'Opex'!AQ10+'IS(Q)'!AQ18+'Revenue'!AQ19-('Debt'!AQ8)</f>
       </c>
       <c r="AR57" s="31">
-        <f>'Revenue'!AR14-'Opex'!AR10+'IS(Q)'!AR18+'Revenue'!AR19-(AR79*$D$73*100)</f>
+        <f>'Revenue'!AR14-'Opex'!AR10+'IS(Q)'!AR18+'Revenue'!AR19-('Debt'!AR8)</f>
       </c>
       <c r="AS57" s="31">
-        <f>'Revenue'!AS14-'Opex'!AS10+'IS(Q)'!AS18+'Revenue'!AS19-(AS79*$D$73*100)</f>
+        <f>'Revenue'!AS14-'Opex'!AS10+'IS(Q)'!AS18+'Revenue'!AS19-('Debt'!AS8)</f>
       </c>
       <c r="AT57" s="31">
-        <f>'Revenue'!AT14-'Opex'!AT10+'IS(Q)'!AT18+'Revenue'!AT19-(AT79*$D$73*100)</f>
+        <f>'Revenue'!AT14-'Opex'!AT10+'IS(Q)'!AT18+'Revenue'!AT19-('Debt'!AT8)</f>
       </c>
       <c r="AU57" s="31">
-        <f>'Revenue'!AU14-'Opex'!AU10+'IS(Q)'!AU18+'Revenue'!AU19-(AU79*$D$73*100)</f>
+        <f>'Revenue'!AU14-'Opex'!AU10+'IS(Q)'!AU18+'Revenue'!AU19-('Debt'!AU8)</f>
       </c>
       <c r="AV57" s="31">
-        <f>'Revenue'!AV14-'Opex'!AV10+'IS(Q)'!AV18+'Revenue'!AV19-(AV79*$D$73*100)</f>
+        <f>'Revenue'!AV14-'Opex'!AV10+'IS(Q)'!AV18+'Revenue'!AV19-('Debt'!AV8)</f>
       </c>
       <c r="AW57" s="31">
-        <f>'Revenue'!AW14-'Opex'!AW10+'IS(Q)'!AW18+'Revenue'!AW19-(AW79*$D$73*100)</f>
+        <f>'Revenue'!AW14-'Opex'!AW10+'IS(Q)'!AW18+'Revenue'!AW19-('Debt'!AW8)</f>
       </c>
       <c r="AX57" s="31">
-        <f>'Revenue'!AX14-'Opex'!AX10+'IS(Q)'!AX18+'Revenue'!AX19-(AX79*$D$73*100)</f>
+        <f>'Revenue'!AX14-'Opex'!AX10+'IS(Q)'!AX18+'Revenue'!AX19-('Debt'!AX8)</f>
       </c>
       <c r="AY57" s="31">
-        <f>'Revenue'!AY14-'Opex'!AY10+'IS(Q)'!AY18+'Revenue'!AY19-(AY79*$D$73*100)</f>
+        <f>'Revenue'!AY14-'Opex'!AY10+'IS(Q)'!AY18+'Revenue'!AY19-('Debt'!AY8)</f>
       </c>
       <c r="AZ57" s="31">
-        <f>'Revenue'!AZ14-'Opex'!AZ10+'IS(Q)'!AZ18+'Revenue'!AZ19-(AZ79*$D$73*100)</f>
+        <f>'Revenue'!AZ14-'Opex'!AZ10+'IS(Q)'!AZ18+'Revenue'!AZ19-('Debt'!AZ8)</f>
       </c>
       <c r="BA57" s="31">
-        <f>'Revenue'!BA14-'Opex'!BA10+'IS(Q)'!BA18+'Revenue'!BA19-(BA79*$D$73*100)</f>
+        <f>'Revenue'!BA14-'Opex'!BA10+'IS(Q)'!BA18+'Revenue'!BA19-('Debt'!BA8)</f>
       </c>
       <c r="BB57" s="31">
-        <f>'Revenue'!BB14-'Opex'!BB10+'IS(Q)'!BB18+'Revenue'!BB19-(BB79*$D$73*100)</f>
+        <f>'Revenue'!BB14-'Opex'!BB10+'IS(Q)'!BB18+'Revenue'!BB19-('Debt'!BB8)</f>
       </c>
       <c r="BC57" s="31">
-        <f>'Revenue'!BC14-'Opex'!BC10+'IS(Q)'!BC18+'Revenue'!BC19-(BC79*$D$73*100)</f>
+        <f>'Revenue'!BC14-'Opex'!BC10+'IS(Q)'!BC18+'Revenue'!BC19-('Debt'!BC8)</f>
       </c>
       <c r="BD57" s="31">
-        <f>'Revenue'!BD14-'Opex'!BD10+'IS(Q)'!BD18+'Revenue'!BD19-(BD79*$D$73*100)</f>
+        <f>'Revenue'!BD14-'Opex'!BD10+'IS(Q)'!BD18+'Revenue'!BD19-('Debt'!BD8)</f>
       </c>
       <c r="BE57" s="31">
-        <f>'Revenue'!BE14-'Opex'!BE10+'IS(Q)'!BE18+'Revenue'!BE19-(BE79*$D$73*100)</f>
+        <f>'Revenue'!BE14-'Opex'!BE10+'IS(Q)'!BE18+'Revenue'!BE19-('Debt'!BE8)</f>
       </c>
       <c r="BF57" s="31">
-        <f>'Revenue'!BF14-'Opex'!BF10+'IS(Q)'!BF18+'Revenue'!BF19-(BF79*$D$73*100)</f>
+        <f>'Revenue'!BF14-'Opex'!BF10+'IS(Q)'!BF18+'Revenue'!BF19-('Debt'!BF8)</f>
       </c>
       <c r="BG57" s="31">
-        <f>'Revenue'!BG14-'Opex'!BG10+'IS(Q)'!BG18+'Revenue'!BG19-(BG79*$D$73*100)</f>
+        <f>'Revenue'!BG14-'Opex'!BG10+'IS(Q)'!BG18+'Revenue'!BG19-('Debt'!BG8)</f>
       </c>
       <c r="BH57" s="31">
-        <f>'Revenue'!BH14-'Opex'!BH10+'IS(Q)'!BH18+'Revenue'!BH19-(BH79*$D$73*100)</f>
+        <f>'Revenue'!BH14-'Opex'!BH10+'IS(Q)'!BH18+'Revenue'!BH19-('Debt'!BH8)</f>
       </c>
       <c r="BI57" s="31">
-        <f>'Revenue'!BI14-'Opex'!BI10+'IS(Q)'!BI18+'Revenue'!BI19-(BI79*$D$73*100)</f>
+        <f>'Revenue'!BI14-'Opex'!BI10+'IS(Q)'!BI18+'Revenue'!BI19-('Debt'!BI8)</f>
       </c>
       <c r="BJ57" s="31">
-        <f>'Revenue'!BJ14-'Opex'!BJ10+'IS(Q)'!BJ18+'Revenue'!BJ19-(BJ79*$D$73*100)</f>
+        <f>'Revenue'!BJ14-'Opex'!BJ10+'IS(Q)'!BJ18+'Revenue'!BJ19-('Debt'!BJ8)</f>
       </c>
       <c r="BK57" s="31">
-        <f>'Revenue'!BK14-'Opex'!BK10+'IS(Q)'!BK18+'Revenue'!BK19-(BK79*$D$73*100)</f>
+        <f>'Revenue'!BK14-'Opex'!BK10+'IS(Q)'!BK18+'Revenue'!BK19-('Debt'!BK8)</f>
       </c>
       <c r="BL57" s="31">
-        <f>'Revenue'!BL14-'Opex'!BL10+'IS(Q)'!BL18+'Revenue'!BL19-(BL79*$D$73*100)</f>
+        <f>'Revenue'!BL14-'Opex'!BL10+'IS(Q)'!BL18+'Revenue'!BL19-('Debt'!BL8)</f>
       </c>
       <c r="BM57" s="31">
-        <f>'Revenue'!BM14-'Opex'!BM10+'IS(Q)'!BM18+'Revenue'!BM19-(BM79*$D$73*100)</f>
+        <f>'Revenue'!BM14-'Opex'!BM10+'IS(Q)'!BM18+'Revenue'!BM19-('Debt'!BM8)</f>
       </c>
       <c r="BN57" s="31">
-        <f>'Revenue'!BN14-'Opex'!BN10+'IS(Q)'!BN18+'Revenue'!BN19-(BN79*$D$73*100)</f>
+        <f>'Revenue'!BN14-'Opex'!BN10+'IS(Q)'!BN18+'Revenue'!BN19-('Debt'!BN8)</f>
       </c>
       <c r="BO57" s="31">
-        <f>'Revenue'!BO14-'Opex'!BO10+'IS(Q)'!BO18+'Revenue'!BO19-(BO79*$D$73*100)</f>
+        <f>'Revenue'!BO14-'Opex'!BO10+'IS(Q)'!BO18+'Revenue'!BO19-('Debt'!BO8)</f>
       </c>
       <c r="BP57" s="31">
-        <f>'Revenue'!BP14-'Opex'!BP10+'IS(Q)'!BP18+'Revenue'!BP19-(BP79*$D$73*100)</f>
+        <f>'Revenue'!BP14-'Opex'!BP10+'IS(Q)'!BP18+'Revenue'!BP19-('Debt'!BP8)</f>
       </c>
       <c r="BQ57" s="31">
-        <f>'Revenue'!BQ14-'Opex'!BQ10+'IS(Q)'!BQ18+'Revenue'!BQ19-(BQ79*$D$73*100)</f>
+        <f>'Revenue'!BQ14-'Opex'!BQ10+'IS(Q)'!BQ18+'Revenue'!BQ19-('Debt'!BQ8)</f>
       </c>
       <c r="BR57" s="31">
-        <f>'Revenue'!BR14-'Opex'!BR10+'IS(Q)'!BR18+'Revenue'!BR19-(BR79*$D$73*100)</f>
+        <f>'Revenue'!BR14-'Opex'!BR10+'IS(Q)'!BR18+'Revenue'!BR19-('Debt'!BR8)</f>
       </c>
       <c r="BS57" s="31">
-        <f>'Revenue'!BS14-'Opex'!BS10+'IS(Q)'!BS18+'Revenue'!BS19-(BS79*$D$73*100)</f>
+        <f>'Revenue'!BS14-'Opex'!BS10+'IS(Q)'!BS18+'Revenue'!BS19-('Debt'!BS8)</f>
       </c>
       <c r="BT57" s="31">
-        <f>'Revenue'!BT14-'Opex'!BT10+'IS(Q)'!BT18+'Revenue'!BT19-(BT79*$D$73*100)</f>
+        <f>'Revenue'!BT14-'Opex'!BT10+'IS(Q)'!BT18+'Revenue'!BT19-('Debt'!BT8)</f>
       </c>
       <c r="BU57" s="31">
-        <f>'Revenue'!BU14-'Opex'!BU10+'IS(Q)'!BU18+'Revenue'!BU19-(BU79*$D$73*100)</f>
+        <f>'Revenue'!BU14-'Opex'!BU10+'IS(Q)'!BU18+'Revenue'!BU19-('Debt'!BU8)</f>
       </c>
       <c r="BV57" s="31">
-        <f>'Revenue'!BV14-'Opex'!BV10+'IS(Q)'!BV18+'Revenue'!BV19-(BV79*$D$73*100)</f>
+        <f>'Revenue'!BV14-'Opex'!BV10+'IS(Q)'!BV18+'Revenue'!BV19-('Debt'!BV8)</f>
       </c>
       <c r="BW57" s="31">
-        <f>'Revenue'!BW14-'Opex'!BW10+'IS(Q)'!BW18+'Revenue'!BW19-(BW79*$D$73*100)</f>
+        <f>'Revenue'!BW14-'Opex'!BW10+'IS(Q)'!BW18+'Revenue'!BW19-('Debt'!BW8)</f>
       </c>
       <c r="BX57" s="31">
-        <f>'Revenue'!BX14-'Opex'!BX10+'IS(Q)'!BX18+'Revenue'!BX19-(BX79*$D$73*100)</f>
+        <f>'Revenue'!BX14-'Opex'!BX10+'IS(Q)'!BX18+'Revenue'!BX19-('Debt'!BX8)</f>
       </c>
       <c r="BY57" s="31">
-        <f>'Revenue'!BY14-'Opex'!BY10+'IS(Q)'!BY18+'Revenue'!BY19-(BY79*$D$73*100)</f>
+        <f>'Revenue'!BY14-'Opex'!BY10+'IS(Q)'!BY18+'Revenue'!BY19-('Debt'!BY8)</f>
       </c>
       <c r="BZ57" s="31">
-        <f>'Revenue'!BZ14-'Opex'!BZ10+'IS(Q)'!BZ18+'Revenue'!BZ19-(BZ79*$D$73*100)</f>
+        <f>'Revenue'!BZ14-'Opex'!BZ10+'IS(Q)'!BZ18+'Revenue'!BZ19-('Debt'!BZ8)</f>
       </c>
       <c r="CA57" s="31">
-        <f>'Revenue'!CA14-'Opex'!CA10+'IS(Q)'!CA18+'Revenue'!CA19-(CA79*$D$73*100)</f>
+        <f>'Revenue'!CA14-'Opex'!CA10+'IS(Q)'!CA18+'Revenue'!CA19-('Debt'!CA8)</f>
       </c>
       <c r="CB57" s="31">
-        <f>'Revenue'!CB14-'Opex'!CB10+'IS(Q)'!CB18+'Revenue'!CB19-(CB79*$D$73*100)</f>
+        <f>'Revenue'!CB14-'Opex'!CB10+'IS(Q)'!CB18+'Revenue'!CB19-('Debt'!CB8)</f>
       </c>
       <c r="CC57" s="31">
-        <f>'Revenue'!CC14-'Opex'!CC10+'IS(Q)'!CC18+'Revenue'!CC19-(CC79*$D$73*100)</f>
+        <f>'Revenue'!CC14-'Opex'!CC10+'IS(Q)'!CC18+'Revenue'!CC19-('Debt'!CC8)</f>
       </c>
       <c r="CD57" s="31">
-        <f>'Revenue'!CD14-'Opex'!CD10+'IS(Q)'!CD18+'Revenue'!CD19-(CD79*$D$73*100)</f>
+        <f>'Revenue'!CD14-'Opex'!CD10+'IS(Q)'!CD18+'Revenue'!CD19-('Debt'!CD8)</f>
       </c>
       <c r="CE57" s="31">
-        <f>'Revenue'!CE14-'Opex'!CE10+'IS(Q)'!CE18+'Revenue'!CE19-(CE79*$D$73*100)</f>
+        <f>'Revenue'!CE14-'Opex'!CE10+'IS(Q)'!CE18+'Revenue'!CE19-('Debt'!CE8)</f>
       </c>
       <c r="CF57" s="31">
-        <f>'Revenue'!CF14-'Opex'!CF10+'IS(Q)'!CF18+'Revenue'!CF19-(CF79*$D$73*100)</f>
+        <f>'Revenue'!CF14-'Opex'!CF10+'IS(Q)'!CF18+'Revenue'!CF19-('Debt'!CF8)</f>
       </c>
       <c r="CG57" s="31">
-        <f>'Revenue'!CG14-'Opex'!CG10+'IS(Q)'!CG18+'Revenue'!CG19-(CG79*$D$73*100)</f>
+        <f>'Revenue'!CG14-'Opex'!CG10+'IS(Q)'!CG18+'Revenue'!CG19-('Debt'!CG8)</f>
       </c>
       <c r="CH57" s="31">
-        <f>'Revenue'!CH14-'Opex'!CH10+'IS(Q)'!CH18+'Revenue'!CH19-(CH79*$D$73*100)</f>
+        <f>'Revenue'!CH14-'Opex'!CH10+'IS(Q)'!CH18+'Revenue'!CH19-('Debt'!CH8)</f>
       </c>
       <c r="CI57" s="31">
-        <f>'Revenue'!CI14-'Opex'!CI10+'IS(Q)'!CI18+'Revenue'!CI19-(CI79*$D$73*100)</f>
+        <f>'Revenue'!CI14-'Opex'!CI10+'IS(Q)'!CI18+'Revenue'!CI19-('Debt'!CI8)</f>
       </c>
       <c r="CJ57" s="31">
-        <f>'Revenue'!CJ14-'Opex'!CJ10+'IS(Q)'!CJ18+'Revenue'!CJ19-(CJ79*$D$73*100)</f>
+        <f>'Revenue'!CJ14-'Opex'!CJ10+'IS(Q)'!CJ18+'Revenue'!CJ19-('Debt'!CJ8)</f>
       </c>
       <c r="CK57" s="31">
-        <f>'Revenue'!CK14-'Opex'!CK10+'IS(Q)'!CK18+'Revenue'!CK19-(CK79*$D$73*100)</f>
+        <f>'Revenue'!CK14-'Opex'!CK10+'IS(Q)'!CK18+'Revenue'!CK19-('Debt'!CK8)</f>
       </c>
       <c r="CL57" s="31">
-        <f>'Revenue'!CL14-'Opex'!CL10-$D$74*100+'IS(Q)'!CL18+'Revenue'!CL19-(CL79*$D$73*100)</f>
+        <f>'Revenue'!CL14-'Opex'!CL10-$D$73*100+'IS(Q)'!CL18+'Revenue'!CL19-('Debt'!CL8)</f>
       </c>
     </row>
     <row r="58" spans="2:90" x14ac:dyDescent="0.25">
@@ -30709,334 +30469,57 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="33" t="s">
-        <v>205</v>
+        <v>328</v>
       </c>
       <c r="C73" s="44" t="s">
-        <v>206</v>
+        <v>329</v>
       </c>
       <c r="D73" s="45">
-        <f>'입력값'!C8</f>
+        <f>'입력값'!C17</f>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="33" t="s">
-        <v>328</v>
+        <v>397</v>
       </c>
       <c r="C74" s="44" t="s">
-        <v>329</v>
+        <v>398</v>
       </c>
       <c r="D74" s="45">
-        <f>'입력값'!C17</f>
+        <f>'입력값'!C25</f>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="33" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C75" s="44" t="s">
-        <v>398</v>
-      </c>
-      <c r="D75" s="45">
-        <f>'입력값'!C25</f>
+        <v>400</v>
+      </c>
+      <c r="D75" s="65">
+        <f>'입력값'!C26</f>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C76" s="44" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D76" s="65">
-        <f>'입력값'!C26</f>
+        <f>'입력값'!C27</f>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="33" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C77" s="44" t="s">
-        <v>402</v>
-      </c>
-      <c r="D77" s="65">
-        <f>'입력값'!C27</f>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B78" s="33" t="s">
-        <v>403</v>
-      </c>
-      <c r="C78" s="44" t="s">
         <v>404</v>
       </c>
-      <c r="D78" s="66">
+      <c r="D77" s="66">
         <f>'입력값'!C28</f>
-      </c>
-    </row>
-    <row r="79" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B79" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="C79" s="44" t="s">
-        <v>247</v>
-      </c>
-      <c r="E79" s="52">
-        <f>'입력값'!E49</f>
-      </c>
-      <c r="F79" s="52">
-        <f>'입력값'!F49</f>
-      </c>
-      <c r="G79" s="52">
-        <f>'입력값'!G49</f>
-      </c>
-      <c r="H79" s="52">
-        <f>'입력값'!H49</f>
-      </c>
-      <c r="I79" s="52">
-        <f>'입력값'!I49</f>
-      </c>
-      <c r="J79" s="52">
-        <f>'입력값'!J49</f>
-      </c>
-      <c r="K79" s="45">
-        <f>'입력값'!K49</f>
-      </c>
-      <c r="L79" s="45">
-        <f>'입력값'!L49</f>
-      </c>
-      <c r="M79" s="45">
-        <f>'입력값'!M49</f>
-      </c>
-      <c r="N79" s="45">
-        <f>'입력값'!N49</f>
-      </c>
-      <c r="O79" s="45">
-        <f>'입력값'!O49</f>
-      </c>
-      <c r="P79" s="45">
-        <f>'입력값'!P49</f>
-      </c>
-      <c r="Q79" s="45">
-        <f>'입력값'!Q49</f>
-      </c>
-      <c r="R79" s="45">
-        <f>'입력값'!R49</f>
-      </c>
-      <c r="S79" s="45">
-        <f>'입력값'!S49</f>
-      </c>
-      <c r="T79" s="45">
-        <f>'입력값'!T49</f>
-      </c>
-      <c r="U79" s="45">
-        <f>'입력값'!U49</f>
-      </c>
-      <c r="V79" s="45">
-        <f>'입력값'!V49</f>
-      </c>
-      <c r="W79" s="45">
-        <f>'입력값'!W49</f>
-      </c>
-      <c r="X79" s="45">
-        <f>'입력값'!X49</f>
-      </c>
-      <c r="Y79" s="45">
-        <f>'입력값'!Y49</f>
-      </c>
-      <c r="Z79" s="45">
-        <f>'입력값'!Z49</f>
-      </c>
-      <c r="AA79" s="45">
-        <f>'입력값'!AA49</f>
-      </c>
-      <c r="AB79" s="45">
-        <f>'입력값'!AB49</f>
-      </c>
-      <c r="AC79" s="45">
-        <f>'입력값'!AC49</f>
-      </c>
-      <c r="AD79" s="45">
-        <f>'입력값'!AD49</f>
-      </c>
-      <c r="AE79" s="45">
-        <f>'입력값'!AE49</f>
-      </c>
-      <c r="AF79" s="45">
-        <f>'입력값'!AF49</f>
-      </c>
-      <c r="AG79" s="45">
-        <f>'입력값'!AG49</f>
-      </c>
-      <c r="AH79" s="45">
-        <f>'입력값'!AH49</f>
-      </c>
-      <c r="AI79" s="45">
-        <f>'입력값'!AI49</f>
-      </c>
-      <c r="AJ79" s="45">
-        <f>'입력값'!AJ49</f>
-      </c>
-      <c r="AK79" s="45">
-        <f>'입력값'!AK49</f>
-      </c>
-      <c r="AL79" s="45">
-        <f>'입력값'!AL49</f>
-      </c>
-      <c r="AM79" s="45">
-        <f>'입력값'!AM49</f>
-      </c>
-      <c r="AN79" s="45">
-        <f>'입력값'!AN49</f>
-      </c>
-      <c r="AO79" s="45">
-        <f>'입력값'!AO49</f>
-      </c>
-      <c r="AP79" s="45">
-        <f>'입력값'!AP49</f>
-      </c>
-      <c r="AQ79" s="45">
-        <f>'입력값'!AQ49</f>
-      </c>
-      <c r="AR79" s="45">
-        <f>'입력값'!AR49</f>
-      </c>
-      <c r="AS79" s="45">
-        <f>'입력값'!AS49</f>
-      </c>
-      <c r="AT79" s="45">
-        <f>'입력값'!AT49</f>
-      </c>
-      <c r="AU79" s="45">
-        <f>'입력값'!AU49</f>
-      </c>
-      <c r="AV79" s="45">
-        <f>'입력값'!AV49</f>
-      </c>
-      <c r="AW79" s="45">
-        <f>'입력값'!AW49</f>
-      </c>
-      <c r="AX79" s="45">
-        <f>'입력값'!AX49</f>
-      </c>
-      <c r="AY79" s="45">
-        <f>'입력값'!AY49</f>
-      </c>
-      <c r="AZ79" s="45">
-        <f>'입력값'!AZ49</f>
-      </c>
-      <c r="BA79" s="45">
-        <f>'입력값'!BA49</f>
-      </c>
-      <c r="BB79" s="45">
-        <f>'입력값'!BB49</f>
-      </c>
-      <c r="BC79" s="45">
-        <f>'입력값'!BC49</f>
-      </c>
-      <c r="BD79" s="45">
-        <f>'입력값'!BD49</f>
-      </c>
-      <c r="BE79" s="45">
-        <f>'입력값'!BE49</f>
-      </c>
-      <c r="BF79" s="45">
-        <f>'입력값'!BF49</f>
-      </c>
-      <c r="BG79" s="45">
-        <f>'입력값'!BG49</f>
-      </c>
-      <c r="BH79" s="45">
-        <f>'입력값'!BH49</f>
-      </c>
-      <c r="BI79" s="45">
-        <f>'입력값'!BI49</f>
-      </c>
-      <c r="BJ79" s="45">
-        <f>'입력값'!BJ49</f>
-      </c>
-      <c r="BK79" s="45">
-        <f>'입력값'!BK49</f>
-      </c>
-      <c r="BL79" s="45">
-        <f>'입력값'!BL49</f>
-      </c>
-      <c r="BM79" s="45">
-        <f>'입력값'!BM49</f>
-      </c>
-      <c r="BN79" s="45">
-        <f>'입력값'!BN49</f>
-      </c>
-      <c r="BO79" s="45">
-        <f>'입력값'!BO49</f>
-      </c>
-      <c r="BP79" s="45">
-        <f>'입력값'!BP49</f>
-      </c>
-      <c r="BQ79" s="45">
-        <f>'입력값'!BQ49</f>
-      </c>
-      <c r="BR79" s="45">
-        <f>'입력값'!BR49</f>
-      </c>
-      <c r="BS79" s="45">
-        <f>'입력값'!BS49</f>
-      </c>
-      <c r="BT79" s="45">
-        <f>'입력값'!BT49</f>
-      </c>
-      <c r="BU79" s="45">
-        <f>'입력값'!BU49</f>
-      </c>
-      <c r="BV79" s="45">
-        <f>'입력값'!BV49</f>
-      </c>
-      <c r="BW79" s="45">
-        <f>'입력값'!BW49</f>
-      </c>
-      <c r="BX79" s="45">
-        <f>'입력값'!BX49</f>
-      </c>
-      <c r="BY79" s="45">
-        <f>'입력값'!BY49</f>
-      </c>
-      <c r="BZ79" s="45">
-        <f>'입력값'!BZ49</f>
-      </c>
-      <c r="CA79" s="45">
-        <f>'입력값'!CA49</f>
-      </c>
-      <c r="CB79" s="45">
-        <f>'입력값'!CB49</f>
-      </c>
-      <c r="CC79" s="45">
-        <f>'입력값'!CC49</f>
-      </c>
-      <c r="CD79" s="45">
-        <f>'입력값'!CD49</f>
-      </c>
-      <c r="CE79" s="45">
-        <f>'입력값'!CE49</f>
-      </c>
-      <c r="CF79" s="45">
-        <f>'입력값'!CF49</f>
-      </c>
-      <c r="CG79" s="45">
-        <f>'입력값'!CG49</f>
-      </c>
-      <c r="CH79" s="45">
-        <f>'입력값'!CH49</f>
-      </c>
-      <c r="CI79" s="45">
-        <f>'입력값'!CI49</f>
-      </c>
-      <c r="CJ79" s="45">
-        <f>'입력값'!CJ49</f>
-      </c>
-      <c r="CK79" s="45">
-        <f>'입력값'!CK49</f>
-      </c>
-      <c r="CL79" s="45">
-        <f>'입력값'!CL49</f>
       </c>
     </row>
   </sheetData>

--- a/contract/sample-output.xlsx
+++ b/contract/sample-output.xlsx
@@ -24,7 +24,7 @@
     <t>샘플 태양광 100MW</t>
   </si>
   <si>
-    <t>재무모델 v2 (분기·5트랜치) — 재생E AI Agent 자동생성 · 2026-09-21</t>
+    <t>재무모델 v2 (분기·5트랜치) — 재생E AI Agent 자동생성 · 2026-09-22</t>
   </si>
   <si>
     <t>시트</t>
@@ -81,7 +81,7 @@
     <t>분기 현금흐름 · DSCR · 배당</t>
   </si>
   <si>
-    <t>※ Funding 시트의 트랜치 조건·총사업비 항목·사업자 지분은 "입력값" 시트를 참조하는 수식입니다(입력값 시트를 고치면 같이 바뀝니다). 그 외 계산 결과(세금·DSCR·배당 등)는 값(baked) 기준이라 가정을 바꾸려면 생성기에서 다시 뽑아야 합니다.</t>
+    <t>※ 입력값 시트(노란 탭) 외의 모든 값은 수식입니다. 노란 셀을 고치면 세금·DSCR·배당·IRR 까지 전부 다시 계산됩니다. 회색 셀(거치·상환·방식·투입순서, DSRA 적립기준)은 스케줄의 모양을 정하는 값이라 화면에서 다시 생성해야 합니다. 각 계산 시트 맨 아래 "가정" 블록이 입력값 시트를 참조하는 유일한 곳입니다.</t>
   </si>
   <si>
     <t>Executive Summary (v2 · 분기 · 5트랜치)</t>
@@ -861,7 +861,7 @@
     <t>영업비용 합계</t>
   </si>
   <si>
-    <t>※ 실측 오버라이드가 적용된 분기(있다면)는 값(baked)이고, 그 외 분기는 "입력값" 시트의 운영비 총액/에스컬레이션/후순위 비중을 참조하는 수식입니다.</t>
+    <t>※ 실측 오버라이드가 적용된 분기(예시 불러오기)는 "입력값" 시트의 실측 표를, 그 외 분기는 운영비 총액/에스컬레이션/후순위 비중(또는 운영비 항목)을 참조하는 수식입니다.</t>
   </si>
   <si>
     <t xml:space="preserve">  운영비 총액[억원/yr]</t>

--- a/contract/sample-output.xlsx
+++ b/contract/sample-output.xlsx
@@ -19,12 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="419">
   <si>
     <t>샘플 태양광 100MW</t>
   </si>
   <si>
-    <t>재무모델 v2 (분기·5트랜치) — 재생E AI Agent 자동생성 · 2026-09-23</t>
+    <t>재무모델 v2 (분기·5트랜치) — 재생E AI Agent 자동생성 · 2026-10-02</t>
   </si>
   <si>
     <t>시트</t>
@@ -636,6 +636,15 @@
     <t>총사업비(건설이자 제외)[KRWm]</t>
   </si>
   <si>
+    <t>총조달 소요액[KRWm] (= 총사업비 + DSRA + 건설이자)</t>
+  </si>
+  <si>
+    <t>조달 약정 합계[KRWm] (= 자본금 + 트랜치 약정)</t>
+  </si>
+  <si>
+    <t>조달 과부족[KRWm] (조달 − 소요, 0 이상이어야 함)</t>
+  </si>
+  <si>
     <t>사업자 구성 (지분)</t>
   </si>
   <si>
@@ -663,6 +672,30 @@
     <t>C8</t>
   </si>
   <si>
+    <t xml:space="preserve">  자기자본[억원]</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  DSRA 최초 적립액[억원]</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  선순위A · 금액[억원]</t>
+  </si>
+  <si>
+    <t>C41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  선순위B · 금액[억원]</t>
+  </si>
+  <si>
+    <t>C42</t>
+  </si>
+  <si>
     <t>차입금 상환 스케줄 — 건설기간 인출 + 트랜치별 상환</t>
   </si>
   <si>
@@ -738,18 +771,6 @@
     <t>DSRA 기말잔액</t>
   </si>
   <si>
-    <t xml:space="preserve">  자기자본[억원]</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  선순위A · 금액[억원]</t>
-  </si>
-  <si>
-    <t>C41</t>
-  </si>
-  <si>
     <t xml:space="preserve">  선순위A · 건설금리[%]</t>
   </si>
   <si>
@@ -760,12 +781,6 @@
   </si>
   <si>
     <t>E41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  선순위B · 금액[억원]</t>
-  </si>
-  <si>
-    <t>C42</t>
   </si>
   <si>
     <t xml:space="preserve">  선순위B · 건설금리[%]</t>
@@ -3012,7 +3027,7 @@
   <sheetPr>
     <tabColor rgb="FF14483A"/>
   </sheetPr>
-  <dimension ref="A1:CM27"/>
+  <dimension ref="A1:CM34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -3349,7 +3364,7 @@
         <v>203</v>
       </c>
       <c r="C15" s="32">
-        <f>$D$27*100+'Debt'!D12</f>
+        <f>$D$30*100+'Debt'!D12</f>
         <v>144794.2771314259</v>
       </c>
     </row>
@@ -3362,257 +3377,336 @@
         <v>141069</v>
       </c>
     </row>
-    <row r="18" spans="2:91" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
-      <c r="AC18" s="10"/>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
-      <c r="AF18" s="10"/>
-      <c r="AG18" s="10"/>
-      <c r="AH18" s="10"/>
-      <c r="AI18" s="10"/>
-      <c r="AJ18" s="10"/>
-      <c r="AK18" s="10"/>
-      <c r="AL18" s="10"/>
-      <c r="AM18" s="10"/>
-      <c r="AN18" s="10"/>
-      <c r="AO18" s="10"/>
-      <c r="AP18" s="10"/>
-      <c r="AQ18" s="10"/>
-      <c r="AR18" s="10"/>
-      <c r="AS18" s="10"/>
-      <c r="AT18" s="10"/>
-      <c r="AU18" s="10"/>
-      <c r="AV18" s="10"/>
-      <c r="AW18" s="10"/>
-      <c r="AX18" s="10"/>
-      <c r="AY18" s="10"/>
-      <c r="AZ18" s="10"/>
-      <c r="BA18" s="10"/>
-      <c r="BB18" s="10"/>
-      <c r="BC18" s="10"/>
-      <c r="BD18" s="10"/>
-      <c r="BE18" s="10"/>
-      <c r="BF18" s="10"/>
-      <c r="BG18" s="10"/>
-      <c r="BH18" s="10"/>
-      <c r="BI18" s="10"/>
-      <c r="BJ18" s="10"/>
-      <c r="BK18" s="10"/>
-      <c r="BL18" s="10"/>
-      <c r="BM18" s="10"/>
-      <c r="BN18" s="10"/>
-      <c r="BO18" s="10"/>
-      <c r="BP18" s="10"/>
-      <c r="BQ18" s="10"/>
-      <c r="BR18" s="10"/>
-      <c r="BS18" s="10"/>
-      <c r="BT18" s="10"/>
-      <c r="BU18" s="10"/>
-      <c r="BV18" s="10"/>
-      <c r="BW18" s="10"/>
-      <c r="BX18" s="10"/>
-      <c r="BY18" s="10"/>
-      <c r="BZ18" s="10"/>
-      <c r="CA18" s="10"/>
-      <c r="CB18" s="10"/>
-      <c r="CC18" s="10"/>
-      <c r="CD18" s="10"/>
-      <c r="CE18" s="10"/>
-      <c r="CF18" s="10"/>
-      <c r="CG18" s="10"/>
-      <c r="CH18" s="10"/>
-      <c r="CI18" s="10"/>
-      <c r="CJ18" s="10"/>
-      <c r="CK18" s="10"/>
-      <c r="CL18" s="10"/>
-      <c r="CM18" s="10"/>
+      <c r="C17" s="32">
+        <f>$D$30*100+$D$32*100+'Debt'!D12</f>
+        <v>149794.2771314259</v>
+      </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="32">
+        <f>$D$31*100+$D$33*100+$D$34*100</f>
+        <v>141069</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="14">
+        <f>C18-C17</f>
+        <v>-8725.277131425886</v>
+      </c>
+      <c r="E19" s="31" t="str">
+        <f>IF(C18-C17&gt;=-1,"조달 충족 (OK)","경고: 조달 부족 — 못 빌린 돈이 공짜로 조달된 셈이 되어 이자가 과소계상됩니다")</f>
+        <v>경고: 조달 부족 — 못 빌린 돈이 공짜로 조달된 셈이 되어 이자가 과소계상됩니다</v>
+      </c>
+    </row>
+    <row r="21" spans="2:91" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+      <c r="AD21" s="10"/>
+      <c r="AE21" s="10"/>
+      <c r="AF21" s="10"/>
+      <c r="AG21" s="10"/>
+      <c r="AH21" s="10"/>
+      <c r="AI21" s="10"/>
+      <c r="AJ21" s="10"/>
+      <c r="AK21" s="10"/>
+      <c r="AL21" s="10"/>
+      <c r="AM21" s="10"/>
+      <c r="AN21" s="10"/>
+      <c r="AO21" s="10"/>
+      <c r="AP21" s="10"/>
+      <c r="AQ21" s="10"/>
+      <c r="AR21" s="10"/>
+      <c r="AS21" s="10"/>
+      <c r="AT21" s="10"/>
+      <c r="AU21" s="10"/>
+      <c r="AV21" s="10"/>
+      <c r="AW21" s="10"/>
+      <c r="AX21" s="10"/>
+      <c r="AY21" s="10"/>
+      <c r="AZ21" s="10"/>
+      <c r="BA21" s="10"/>
+      <c r="BB21" s="10"/>
+      <c r="BC21" s="10"/>
+      <c r="BD21" s="10"/>
+      <c r="BE21" s="10"/>
+      <c r="BF21" s="10"/>
+      <c r="BG21" s="10"/>
+      <c r="BH21" s="10"/>
+      <c r="BI21" s="10"/>
+      <c r="BJ21" s="10"/>
+      <c r="BK21" s="10"/>
+      <c r="BL21" s="10"/>
+      <c r="BM21" s="10"/>
+      <c r="BN21" s="10"/>
+      <c r="BO21" s="10"/>
+      <c r="BP21" s="10"/>
+      <c r="BQ21" s="10"/>
+      <c r="BR21" s="10"/>
+      <c r="BS21" s="10"/>
+      <c r="BT21" s="10"/>
+      <c r="BU21" s="10"/>
+      <c r="BV21" s="10"/>
+      <c r="BW21" s="10"/>
+      <c r="BX21" s="10"/>
+      <c r="BY21" s="10"/>
+      <c r="BZ21" s="10"/>
+      <c r="CA21" s="10"/>
+      <c r="CB21" s="10"/>
+      <c r="CC21" s="10"/>
+      <c r="CD21" s="10"/>
+      <c r="CE21" s="10"/>
+      <c r="CF21" s="10"/>
+      <c r="CG21" s="10"/>
+      <c r="CH21" s="10"/>
+      <c r="CI21" s="10"/>
+      <c r="CJ21" s="10"/>
+      <c r="CK21" s="10"/>
+      <c r="CL21" s="10"/>
+      <c r="CM21" s="10"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>208</v>
+      <c r="C23" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>211</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="31" t="str">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="31" t="str">
         <f>'입력값'!B54</f>
         <v>출자자1</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C24" s="40">
         <f>'입력값'!C54/100</f>
         <v>0.6</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D24" s="32">
         <v>9000</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E24" s="32">
         <v>55598.862959798455</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="str">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="31" t="str">
         <f>'입력값'!B55</f>
         <v>출자자2</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C25" s="40">
         <f>'입력값'!C55/100</f>
         <v>0.4</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D25" s="32">
         <v>6000</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E25" s="32">
         <v>37065.908639865636</v>
       </c>
     </row>
-    <row r="25" spans="2:91" x14ac:dyDescent="0.25">
-      <c r="B25" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="44" t="s">
-        <v>210</v>
-      </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10"/>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10"/>
-      <c r="AB25" s="10"/>
-      <c r="AC25" s="10"/>
-      <c r="AD25" s="10"/>
-      <c r="AE25" s="10"/>
-      <c r="AF25" s="10"/>
-      <c r="AG25" s="10"/>
-      <c r="AH25" s="10"/>
-      <c r="AI25" s="10"/>
-      <c r="AJ25" s="10"/>
-      <c r="AK25" s="10"/>
-      <c r="AL25" s="10"/>
-      <c r="AM25" s="10"/>
-      <c r="AN25" s="10"/>
-      <c r="AO25" s="10"/>
-      <c r="AP25" s="10"/>
-      <c r="AQ25" s="10"/>
-      <c r="AR25" s="10"/>
-      <c r="AS25" s="10"/>
-      <c r="AT25" s="10"/>
-      <c r="AU25" s="10"/>
-      <c r="AV25" s="10"/>
-      <c r="AW25" s="10"/>
-      <c r="AX25" s="10"/>
-      <c r="AY25" s="10"/>
-      <c r="AZ25" s="10"/>
-      <c r="BA25" s="10"/>
-      <c r="BB25" s="10"/>
-      <c r="BC25" s="10"/>
-      <c r="BD25" s="10"/>
-      <c r="BE25" s="10"/>
-      <c r="BF25" s="10"/>
-      <c r="BG25" s="10"/>
-      <c r="BH25" s="10"/>
-      <c r="BI25" s="10"/>
-      <c r="BJ25" s="10"/>
-      <c r="BK25" s="10"/>
-      <c r="BL25" s="10"/>
-      <c r="BM25" s="10"/>
-      <c r="BN25" s="10"/>
-      <c r="BO25" s="10"/>
-      <c r="BP25" s="10"/>
-      <c r="BQ25" s="10"/>
-      <c r="BR25" s="10"/>
-      <c r="BS25" s="10"/>
-      <c r="BT25" s="10"/>
-      <c r="BU25" s="10"/>
-      <c r="BV25" s="10"/>
-      <c r="BW25" s="10"/>
-      <c r="BX25" s="10"/>
-      <c r="BY25" s="10"/>
-      <c r="BZ25" s="10"/>
-      <c r="CA25" s="10"/>
-      <c r="CB25" s="10"/>
-      <c r="CC25" s="10"/>
-      <c r="CD25" s="10"/>
-      <c r="CE25" s="10"/>
-      <c r="CF25" s="10"/>
-      <c r="CG25" s="10"/>
-      <c r="CH25" s="10"/>
-      <c r="CI25" s="10"/>
-      <c r="CJ25" s="10"/>
-      <c r="CK25" s="10"/>
-      <c r="CL25" s="10"/>
-      <c r="CM25" s="10"/>
+    <row r="28" spans="2:91" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
+      <c r="Z28" s="10"/>
+      <c r="AA28" s="10"/>
+      <c r="AB28" s="10"/>
+      <c r="AC28" s="10"/>
+      <c r="AD28" s="10"/>
+      <c r="AE28" s="10"/>
+      <c r="AF28" s="10"/>
+      <c r="AG28" s="10"/>
+      <c r="AH28" s="10"/>
+      <c r="AI28" s="10"/>
+      <c r="AJ28" s="10"/>
+      <c r="AK28" s="10"/>
+      <c r="AL28" s="10"/>
+      <c r="AM28" s="10"/>
+      <c r="AN28" s="10"/>
+      <c r="AO28" s="10"/>
+      <c r="AP28" s="10"/>
+      <c r="AQ28" s="10"/>
+      <c r="AR28" s="10"/>
+      <c r="AS28" s="10"/>
+      <c r="AT28" s="10"/>
+      <c r="AU28" s="10"/>
+      <c r="AV28" s="10"/>
+      <c r="AW28" s="10"/>
+      <c r="AX28" s="10"/>
+      <c r="AY28" s="10"/>
+      <c r="AZ28" s="10"/>
+      <c r="BA28" s="10"/>
+      <c r="BB28" s="10"/>
+      <c r="BC28" s="10"/>
+      <c r="BD28" s="10"/>
+      <c r="BE28" s="10"/>
+      <c r="BF28" s="10"/>
+      <c r="BG28" s="10"/>
+      <c r="BH28" s="10"/>
+      <c r="BI28" s="10"/>
+      <c r="BJ28" s="10"/>
+      <c r="BK28" s="10"/>
+      <c r="BL28" s="10"/>
+      <c r="BM28" s="10"/>
+      <c r="BN28" s="10"/>
+      <c r="BO28" s="10"/>
+      <c r="BP28" s="10"/>
+      <c r="BQ28" s="10"/>
+      <c r="BR28" s="10"/>
+      <c r="BS28" s="10"/>
+      <c r="BT28" s="10"/>
+      <c r="BU28" s="10"/>
+      <c r="BV28" s="10"/>
+      <c r="BW28" s="10"/>
+      <c r="BX28" s="10"/>
+      <c r="BY28" s="10"/>
+      <c r="BZ28" s="10"/>
+      <c r="CA28" s="10"/>
+      <c r="CB28" s="10"/>
+      <c r="CC28" s="10"/>
+      <c r="CD28" s="10"/>
+      <c r="CE28" s="10"/>
+      <c r="CF28" s="10"/>
+      <c r="CG28" s="10"/>
+      <c r="CH28" s="10"/>
+      <c r="CI28" s="10"/>
+      <c r="CJ28" s="10"/>
+      <c r="CK28" s="10"/>
+      <c r="CL28" s="10"/>
+      <c r="CM28" s="10"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="38" t="s">
-        <v>211</v>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="38" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="C27" s="45" t="s">
-        <v>213</v>
-      </c>
-      <c r="D27" s="46">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="D30" s="46">
         <f>'입력값'!C8</f>
         <v>1410.69</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="D31" s="46">
+        <f>'입력값'!C9</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="D32" s="46">
+        <f>'입력값'!C23</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="D33" s="46">
+        <f>'입력값'!C41</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="D34" s="46">
+        <f>'입력값'!C42</f>
+        <v>460.69</v>
       </c>
     </row>
   </sheetData>
@@ -3642,12 +3736,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -4010,10 +4104,10 @@
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(E8:CL8)</f>
@@ -4286,10 +4380,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(E9:CL9)</f>
@@ -4557,10 +4651,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D10" s="32">
         <f>SUM(E10:CL10)</f>
@@ -4832,10 +4926,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="34" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D11" s="32">
         <f>SUM(E11:CL11)</f>
@@ -5107,10 +5201,10 @@
     </row>
     <row r="12" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B12" s="47" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D12" s="14">
         <f>SUM(E12:CL12)</f>
@@ -5463,10 +5557,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E13" s="32">
         <f>E8+E9+E12</f>
@@ -5815,10 +5909,10 @@
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E14" s="32">
         <f>MIN(MAX(E13-(0),0),$D$57*100)*($D$57*100)/IF(($D$57*100)=0,1,$D$57*100)</f>
@@ -6167,10 +6261,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E15" s="32">
         <f>MIN(MAX(E13-($D$57*100),0),$D$58*100+$D$61*100)*($D$58*100)/IF(($D$58*100+$D$61*100)=0,1,$D$58*100+$D$61*100)</f>
@@ -6519,10 +6613,10 @@
     </row>
     <row r="16" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E16" s="32">
         <f>MIN(MAX(E13-($D$57*100),0),$D$58*100+$D$61*100)*($D$61*100)/IF(($D$58*100+$D$61*100)=0,1,$D$58*100+$D$61*100)</f>
@@ -6871,7 +6965,7 @@
     </row>
     <row r="19" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -7328,10 +7422,10 @@
     </row>
     <row r="24" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E24" s="32">
         <v>0</v>
@@ -7679,10 +7773,10 @@
     </row>
     <row r="25" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25" s="35" t="s">
         <v>228</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>217</v>
       </c>
       <c r="D25" s="32">
         <f>SUM(E25:CL25)</f>
@@ -8038,7 +8132,7 @@
         <v>201</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D26" s="32">
         <f>SUM(E26:CL26)</f>
@@ -8391,10 +8485,10 @@
     </row>
     <row r="27" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D27" s="14">
         <f>SUM(E27:CL27)</f>
@@ -8741,10 +8835,10 @@
     </row>
     <row r="28" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D28" s="14">
         <f>SUM(E28:CL28)</f>
@@ -9075,10 +9169,10 @@
     </row>
     <row r="29" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B29" s="47" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E29" s="14">
         <f>E24+E25-E28</f>
@@ -9427,10 +9521,10 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D30" s="32">
         <f>CL29</f>
@@ -9443,7 +9537,7 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="F31" s="50" t="str">
         <f>IF(AND(E15&lt;1,F15&gt;1),"인출 시작 분기 일치 (OK)","경고: 첫 인출 분기가 생성 당시(2024-09-30)와 달라졌습니다. 상환 스케줄이 들어간 열은 고정이라 실제와 어긋납니다 — 화면(HTML)에서 다시 생성하세요.")</f>
@@ -9546,10 +9640,10 @@
     </row>
     <row r="34" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E34" s="32">
         <v>0</v>
@@ -9897,10 +9991,10 @@
     </row>
     <row r="35" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B35" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="35" t="s">
         <v>228</v>
-      </c>
-      <c r="C35" s="35" t="s">
-        <v>217</v>
       </c>
       <c r="D35" s="32">
         <f>SUM(E35:CL35)</f>
@@ -10256,7 +10350,7 @@
         <v>201</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D36" s="32">
         <f>SUM(E36:CL36)</f>
@@ -10609,10 +10703,10 @@
     </row>
     <row r="37" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D37" s="14">
         <f>SUM(E37:CL37)</f>
@@ -10959,10 +11053,10 @@
     </row>
     <row r="38" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D38" s="14">
         <f>SUM(E38:CL38)</f>
@@ -11293,10 +11387,10 @@
     </row>
     <row r="39" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B39" s="47" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E39" s="14">
         <f>E34+E35-E38</f>
@@ -11645,10 +11739,10 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D40" s="32">
         <f>CL39</f>
@@ -11661,7 +11755,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="F41" s="50" t="str">
         <f>IF(AND(E16&lt;1,F16&gt;1),"인출 시작 분기 일치 (OK)","경고: 첫 인출 분기가 생성 당시(2024-09-30)와 달라졌습니다. 상환 스케줄이 들어간 열은 고정이라 실제와 어긋납니다 — 화면(HTML)에서 다시 생성하세요.")</f>
@@ -11670,7 +11764,7 @@
     </row>
     <row r="43" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
@@ -11764,10 +11858,10 @@
     </row>
     <row r="44" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E44" s="32">
         <f>E24+E34</f>
@@ -12116,10 +12210,10 @@
     </row>
     <row r="45" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B45" s="34" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D45" s="14">
         <f>SUM(E45:CL45)</f>
@@ -12472,10 +12566,10 @@
     </row>
     <row r="46" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D46" s="14">
         <f>SUM(E46:CL46)</f>
@@ -12828,10 +12922,10 @@
     </row>
     <row r="47" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B47" s="48" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D47" s="43">
         <f>SUM(E47:CL47)</f>
@@ -13185,10 +13279,10 @@
     </row>
     <row r="48" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B48" s="34" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E48" s="32">
         <f>E29+E39</f>
@@ -13537,10 +13631,10 @@
     </row>
     <row r="50" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B50" s="34" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E50" s="32">
         <f>0</f>
@@ -13889,10 +13983,10 @@
     </row>
     <row r="51" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B51" s="34" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E51" s="32">
         <f>E50</f>
@@ -14241,11 +14335,11 @@
     </row>
     <row r="54" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B54" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="44" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -14337,15 +14431,15 @@
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="34" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D56" s="46">
         <f>'입력값'!C8</f>
@@ -14354,10 +14448,10 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="34" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="D57" s="46">
         <f>'입력값'!C9</f>
@@ -14366,10 +14460,10 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="D58" s="46">
         <f>'입력값'!C41</f>
@@ -14378,10 +14472,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D59" s="52">
         <f>'입력값'!D41</f>
@@ -14390,10 +14484,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D60" s="52">
         <f>'입력값'!E41</f>
@@ -14402,10 +14496,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="D61" s="46">
         <f>'입력값'!C42</f>
@@ -14414,10 +14508,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D62" s="52">
         <f>'입력값'!D42</f>
@@ -14426,10 +14520,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D63" s="52">
         <f>'입력값'!E42</f>
@@ -14438,10 +14532,10 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="34" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E64" s="53">
         <f>'입력값'!E49</f>
@@ -14495,12 +14589,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -14863,10 +14957,10 @@
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E8" s="54">
         <v>0</v>
@@ -15129,10 +15223,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E9" s="55">
         <v>0</v>
@@ -15395,10 +15489,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D11" s="56">
         <f>SUM(E11:CL11)</f>
@@ -15751,10 +15845,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="57"/>
@@ -16085,10 +16179,10 @@
     </row>
     <row r="14" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B14" s="48" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D14" s="43">
         <f>SUM(E14:CL14)</f>
@@ -16436,7 +16530,7 @@
     </row>
     <row r="16" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -16530,10 +16624,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E18" s="32">
         <f>MIN(1,3)/3*E14</f>
@@ -16881,10 +16975,10 @@
     </row>
     <row r="19" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B19" s="48" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D19" s="43">
         <f>SUM(E19:CL19)</f>
@@ -17238,16 +17332,16 @@
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="38" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="44" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -17339,15 +17433,15 @@
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D25" s="58">
         <f>'입력값'!C7</f>
@@ -17356,10 +17450,10 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D26" s="59">
         <f>'입력값'!C10</f>
@@ -17368,10 +17462,10 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D27" s="60">
         <f>'입력값'!C11</f>
@@ -17380,10 +17474,10 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D28" s="60">
         <f>'입력값'!C12</f>
@@ -17392,10 +17486,10 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="34" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D29" s="60">
         <f>'입력값'!C13</f>
@@ -17404,10 +17498,10 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D30" s="61">
         <f>'입력값'!C14</f>
@@ -17441,12 +17535,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -17809,10 +17903,10 @@
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(E8:CL8)</f>
@@ -18159,10 +18253,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(E9:CL9)</f>
@@ -18509,10 +18603,10 @@
     </row>
     <row r="10" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B10" s="48" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D10" s="43">
         <f>SUM(E10:CL10)</f>
@@ -18866,16 +18960,16 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="38" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="44" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -18967,15 +19061,15 @@
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D17" s="46">
         <f>'입력값'!C18</f>
@@ -18984,10 +19078,10 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D18" s="60">
         <f>'입력값'!C19</f>
@@ -18996,10 +19090,10 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D19" s="60">
         <f>'입력값'!C20</f>
@@ -19033,12 +19127,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -19401,10 +19495,10 @@
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="47" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D8" s="14">
         <f>SUM(E8:CL8)</f>
@@ -19757,10 +19851,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="47" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D10" s="14">
         <f>SUM(E10:CL10)</f>
@@ -20113,10 +20207,10 @@
     </row>
     <row r="12" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B12" s="48" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D12" s="43">
         <f>SUM(E12:CL12)</f>
@@ -20470,10 +20564,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E13" s="40" t="str">
         <f>IF(E8&lt;=0,"",E12/E8)</f>
@@ -20822,10 +20916,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D15" s="32">
         <f>SUM(E15:CL15)</f>
@@ -21172,10 +21266,10 @@
     </row>
     <row r="16" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D16" s="32">
         <f>SUM(E16:CL16)</f>
@@ -21522,10 +21616,10 @@
     </row>
     <row r="17" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D17" s="32">
         <f>SUM(E17:CL17)</f>
@@ -21872,10 +21966,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D18" s="32">
         <f>SUM(E18:CL18)</f>
@@ -22222,10 +22316,10 @@
     </row>
     <row r="19" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B19" s="47" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D19" s="14">
         <f>SUM(E19:CL19)</f>
@@ -22578,10 +22672,10 @@
     </row>
     <row r="20" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E20" s="40" t="str">
         <f>IF(E8&lt;=0,"",E19/E8)</f>
@@ -22930,15 +23024,15 @@
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="47" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D23" s="32">
         <f>SUM(E23:CL23)</f>
@@ -23291,10 +23385,10 @@
     </row>
     <row r="24" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D24" s="32">
         <f>SUM(E24:CL24)</f>
@@ -23647,10 +23741,10 @@
     </row>
     <row r="25" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B25" s="47" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D25" s="14">
         <f>SUM(E25:CL25)</f>
@@ -24003,10 +24097,10 @@
     </row>
     <row r="27" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B27" s="47" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D27" s="14">
         <f>SUM(E27:CL27)</f>
@@ -24359,10 +24453,10 @@
     </row>
     <row r="28" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D28" s="32">
         <f>SUM(E28:CL28)</f>
@@ -24715,10 +24809,10 @@
     </row>
     <row r="29" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B29" s="48" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D29" s="43">
         <f>SUM(E29:CL29)</f>
@@ -25072,7 +25166,7 @@
     </row>
     <row r="32" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -25166,10 +25260,10 @@
     </row>
     <row r="34" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D34" s="32">
         <f>SUM(E34:CL34)</f>
@@ -25522,7 +25616,7 @@
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E36" s="13">
         <v>2024</v>
@@ -25593,10 +25687,10 @@
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E37" s="32">
         <f>E34+F34+G34</f>
@@ -25689,10 +25783,10 @@
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E38" s="32">
         <f>0</f>
@@ -25785,10 +25879,10 @@
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" s="34" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E39" s="32">
         <f>IF(E37&lt;=0,0,MIN(E38,E37*$D$63/100))</f>
@@ -25881,10 +25975,10 @@
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E40" s="32">
         <f>IF(E37&lt;=0,E38-E37,E38-E39)</f>
@@ -25977,10 +26071,10 @@
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E41" s="32">
         <f>MAX(0,E37-E39)</f>
@@ -26073,10 +26167,10 @@
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E42" s="32">
         <f>IF(E37&lt;=0,0,MIN(MAX(E41,0),200)*0.09+MIN(MAX(E41-200,0),19800)*0.19+MIN(MAX(E41-20000,0),280000)*0.21+MAX(E41-300000,0)*0.24)</f>
@@ -26169,10 +26263,10 @@
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E43" s="32">
         <f>E41*$D$64/100</f>
@@ -26265,10 +26359,10 @@
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E44" s="32">
         <f>0</f>
@@ -26361,10 +26455,10 @@
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="34" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E45" s="32">
         <f>(0)*$D$65/100</f>
@@ -26457,10 +26551,10 @@
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E46" s="32">
         <f>MAX(0,E42-(E44+E45))</f>
@@ -26553,10 +26647,10 @@
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" s="34" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E47" s="32">
         <f>IF(E37&lt;=0,0,MAX(E43,E46))</f>
@@ -26649,10 +26743,10 @@
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" s="34" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E48" s="32">
         <f>E42-E47</f>
@@ -26745,10 +26839,10 @@
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" s="34" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E49" s="32">
         <f>E44+E45-E48</f>
@@ -26841,10 +26935,10 @@
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" s="47" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E50" s="14">
         <f>E47*(1+$D$66/100)+E48*$D$67/100</f>
@@ -26937,10 +27031,10 @@
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" s="34" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E51" s="32">
         <f>MAX(0,E27)+MAX(0,F27)+MAX(0,G27)</f>
@@ -27033,16 +27127,16 @@
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="38" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="44" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -27134,15 +27228,15 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D58" s="60">
         <f>'입력값'!C15</f>
@@ -27151,10 +27245,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D59" s="62">
         <f>'입력값'!C16</f>
@@ -27163,10 +27257,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D60" s="46">
         <f>'입력값'!C17</f>
@@ -27175,10 +27269,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D61" s="46">
         <f>'입력값'!C21</f>
@@ -27187,10 +27281,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D62" s="46">
         <f>'입력값'!C22</f>
@@ -27199,10 +27293,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D63" s="60">
         <f>'입력값'!C32</f>
@@ -27211,10 +27305,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="34" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D64" s="60">
         <f>'입력값'!C33</f>
@@ -27223,10 +27317,10 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="34" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D65" s="60">
         <f>'입력값'!C34</f>
@@ -27235,10 +27329,10 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="34" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C66" s="45" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D66" s="60">
         <f>'입력값'!C35</f>
@@ -27247,10 +27341,10 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="34" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D67" s="60">
         <f>'입력값'!C36</f>
@@ -27284,12 +27378,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -27652,10 +27746,10 @@
     </row>
     <row r="9" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B9" s="48" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D9" s="43">
         <f>SUM(E9:CL9)</f>
@@ -28009,10 +28103,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D10" s="32">
         <f>SUM(E10:CL10)</f>
@@ -28365,10 +28459,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -28663,10 +28757,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="47" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D13" s="14">
         <f>SUM(E13:CL13)</f>
@@ -29019,10 +29113,10 @@
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D14" s="32">
         <f>SUM(E14:CL14)</f>
@@ -29375,10 +29469,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E15" s="32">
         <f>0</f>
@@ -29727,10 +29821,10 @@
     </row>
     <row r="16" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B16" s="48" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D16" s="43">
         <f>SUM(E16:CL16)</f>
@@ -30084,10 +30178,10 @@
     </row>
     <row r="17" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E17" s="32">
         <f>E18-E16</f>
@@ -30436,10 +30530,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E18" s="32">
         <f>E15+E13</f>
@@ -30788,10 +30882,10 @@
     </row>
     <row r="19" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E19" s="32">
         <v>0</v>
@@ -31054,10 +31148,10 @@
     </row>
     <row r="20" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E20" s="32">
         <f>0</f>
@@ -31406,10 +31500,10 @@
     </row>
     <row r="21" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E21" s="32">
         <f>E20</f>
@@ -31758,10 +31852,10 @@
     </row>
     <row r="22" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E22" s="32">
         <f>0</f>
@@ -32110,10 +32204,10 @@
     </row>
     <row r="23" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E23" s="32">
         <f>0</f>
@@ -32462,10 +32556,10 @@
     </row>
     <row r="24" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="64">
@@ -32816,7 +32910,7 @@
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E26" s="13">
         <v>2025</v>
@@ -32875,10 +32969,10 @@
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E27" s="32">
         <f>K10</f>
@@ -32955,10 +33049,10 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E28" s="32">
         <f>K9</f>
@@ -33035,10 +33129,10 @@
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" s="34" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E29" s="65">
         <f>IF(E27=0,"",E28/E27)</f>
@@ -33115,10 +33209,10 @@
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E30" s="65">
         <f>IF(E27=0,"",(H15+H20+E28)/E27)</f>
@@ -33195,111 +33289,111 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="34" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="34" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="34" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="34" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -33393,10 +33487,10 @@
     </row>
     <row r="46" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E46" s="32">
         <f>0</f>
@@ -33745,10 +33839,10 @@
     </row>
     <row r="47" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B47" s="47" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D47" s="17">
         <f>MIN(E29:V29)</f>
@@ -34101,10 +34195,10 @@
     </row>
     <row r="48" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B48" s="47" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D48" s="17">
         <f>MIN(E30:V30)</f>
@@ -34439,10 +34533,10 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="47" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D49" s="14">
         <f>CL17</f>
@@ -34451,7 +34545,7 @@
     </row>
     <row r="51" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -34814,10 +34908,10 @@
     </row>
     <row r="55" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D55" s="32">
         <f>SUM(E55:CL55)</f>
@@ -35170,10 +35264,10 @@
     </row>
     <row r="56" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B56" s="34" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E56" s="32">
         <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E28+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
@@ -35522,10 +35616,10 @@
     </row>
     <row r="57" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B57" s="34" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E57" s="32">
         <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
@@ -35874,10 +35968,10 @@
     </row>
     <row r="58" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E58" s="32">
         <f>E13-E55</f>
@@ -36226,10 +36320,10 @@
     </row>
     <row r="59" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E59" s="32">
         <f>E13-'IS(Q)'!E28-E19-E55</f>
@@ -36578,10 +36672,10 @@
     </row>
     <row r="60" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E60" s="32">
         <f>E16-E55</f>
@@ -36930,10 +37024,10 @@
     </row>
     <row r="61" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E61" s="32">
         <f>-E55-('Debt'!E15+'Debt'!E16)+'Debt'!E45+'Debt'!E46+E16</f>
@@ -37282,10 +37376,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="47" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D63" s="15">
         <f>(1+IRR(E57:CL57,0.020547644500372275))^4-1</f>
@@ -37294,10 +37388,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="47" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D64" s="15">
         <f>(1+IRR(E56:CL56,0.01870763734289671))^4-1</f>
@@ -37306,10 +37400,10 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="47" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D65" s="15">
         <f>(1+IRR(E59:CL59,0.046036226027774685))^4-1</f>
@@ -37318,10 +37412,10 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="47" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D66" s="15">
         <f>(1+IRR(E58:CL58,0.0389500374863605))^4-1</f>
@@ -37330,10 +37424,10 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="47" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D67" s="15">
         <f>(1+IRR(E60:CL60,0.03510805448393617))^4-1</f>
@@ -37342,10 +37436,10 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="47" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D68" s="15">
         <f>(1+IRR(E61:CL61,0.019272787932702595))^4-1</f>
@@ -37354,16 +37448,16 @@
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" s="38" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="73" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="44" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
@@ -37455,15 +37549,15 @@
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" s="38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="34" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D75" s="46">
         <f>'입력값'!C17</f>
@@ -37472,10 +37566,10 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="34" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C76" s="45" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D76" s="46">
         <f>'입력값'!C25</f>
@@ -37484,10 +37578,10 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="34" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C77" s="45" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D77" s="66">
         <f>'입력값'!C26</f>
@@ -37496,10 +37590,10 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="34" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C78" s="45" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D78" s="66">
         <f>'입력값'!C27</f>
@@ -37508,10 +37602,10 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="34" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C79" s="45" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D79" s="67">
         <f>'입력값'!C28</f>

--- a/contract/sample-output.xlsx
+++ b/contract/sample-output.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="420">
   <si>
     <t>샘플 태양광 100MW</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>최소 누적DSCR [x]</t>
+  </si>
+  <si>
+    <t>운영 중 최저 보유현금 [KRWm]</t>
   </si>
   <si>
     <t>총영업수익(전체기간) [KRWm]</t>
@@ -1475,6 +1478,7 @@
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1490,7 +1494,6 @@
     </xf>
     <xf numFmtId="10" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1894,12 +1897,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -1996,189 +1999,189 @@
       <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="19">
+        <v>56</v>
+      </c>
+      <c r="C7" s="20">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="20">
+        <v>57</v>
+      </c>
+      <c r="C8" s="21">
         <v>1410.69</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="20">
+        <v>58</v>
+      </c>
+      <c r="C9" s="21">
         <v>150.03</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="21">
+        <v>59</v>
+      </c>
+      <c r="C10" s="22">
         <v>154.8</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="22">
+        <v>60</v>
+      </c>
+      <c r="C11" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="22">
+        <v>61</v>
+      </c>
+      <c r="C12" s="23">
         <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="22">
+        <v>62</v>
+      </c>
+      <c r="C13" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="23">
+        <v>63</v>
+      </c>
+      <c r="C14" s="24">
         <v>3.77</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="22">
+        <v>64</v>
+      </c>
+      <c r="C15" s="23">
         <v>95</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="24">
+        <v>65</v>
+      </c>
+      <c r="C16" s="25">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="20">
+        <v>66</v>
+      </c>
+      <c r="C17" s="21">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="20">
+        <v>67</v>
+      </c>
+      <c r="C18" s="21">
         <v>49.8</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="22">
+        <v>68</v>
+      </c>
+      <c r="C19" s="23">
         <v>0.7</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="22">
+        <v>69</v>
+      </c>
+      <c r="C20" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="20">
+        <v>70</v>
+      </c>
+      <c r="C21" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="20">
+        <v>71</v>
+      </c>
+      <c r="C22" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="20">
+        <v>72</v>
+      </c>
+      <c r="C23" s="21">
         <v>50</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="25">
+        <v>73</v>
+      </c>
+      <c r="C24" s="26">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="20">
+        <v>74</v>
+      </c>
+      <c r="C25" s="21">
         <v>10</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="26">
+        <v>75</v>
+      </c>
+      <c r="C26" s="27">
         <v>1.1</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="26">
+        <v>76</v>
+      </c>
+      <c r="C27" s="27">
         <v>1.15</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="27">
+        <v>77</v>
+      </c>
+      <c r="C28" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -2273,47 +2276,47 @@
     <row r="31" spans="2:2" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="22">
+        <v>79</v>
+      </c>
+      <c r="C32" s="23">
         <v>80</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="22">
+        <v>80</v>
+      </c>
+      <c r="C33" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="22">
+        <v>81</v>
+      </c>
+      <c r="C34" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="22">
+        <v>82</v>
+      </c>
+      <c r="C35" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="22">
+        <v>83</v>
+      </c>
+      <c r="C36" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -2406,98 +2409,98 @@
       <c r="CM38" s="10"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="28" t="s">
+      <c r="B40" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="C40" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="D40" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="E40" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="F40" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="H40" s="28" t="s">
+      <c r="G40" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="I40" s="28" t="s">
+      <c r="H40" s="29" t="s">
         <v>91</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="20">
+      <c r="B41" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="21">
         <v>855.35</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <v>0.055999999999999994</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="30">
         <v>0.055999999999999994</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="31">
         <v>2</v>
       </c>
-      <c r="G41" s="30">
+      <c r="G41" s="31">
         <v>16</v>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="26">
         <v>1</v>
       </c>
-      <c r="I41" s="25">
+      <c r="I41" s="26">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" s="20">
+      <c r="B42" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="21">
         <v>492.56</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="30">
         <v>0.055</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="30">
         <v>0.055</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="31">
         <v>2</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G42" s="31">
         <v>16</v>
       </c>
-      <c r="H42" s="25">
+      <c r="H42" s="26">
         <v>1</v>
       </c>
-      <c r="I42" s="25">
+      <c r="I42" s="26">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B43" s="31" t="s">
-        <v>94</v>
+      <c r="B43" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="C43" s="32">
         <f>C9</f>
         <v>150.03</v>
       </c>
-      <c r="I43" s="25">
+      <c r="I43" s="26">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -2590,280 +2593,280 @@
       <c r="CM45" s="10"/>
     </row>
     <row r="47" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B47" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="28" t="s">
+      <c r="B47" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D47" s="28" t="s">
+      <c r="C47" s="29" t="s">
         <v>98</v>
       </c>
+      <c r="D47" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="E47" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G47" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H47" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I47" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K47" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L47" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M47" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N47" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O47" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P47" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q47" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R47" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S47" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T47" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U47" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V47" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W47" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X47" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y47" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z47" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA47" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB47" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC47" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD47" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE47" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF47" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG47" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH47" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI47" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ47" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK47" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL47" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM47" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN47" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO47" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP47" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ47" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR47" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS47" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT47" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU47" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV47" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW47" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX47" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY47" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ47" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA47" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB47" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC47" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD47" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE47" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF47" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG47" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH47" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI47" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ47" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK47" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL47" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM47" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN47" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO47" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP47" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ47" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR47" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS47" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT47" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU47" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV47" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW47" s="33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX47" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY47" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ47" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA47" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB47" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC47" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="CD47" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE47" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CF47" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="CG47" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CH47" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="CI47" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="CJ47" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CK47" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CL47" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D49" s="36">
         <f>SUM(E49:CL49)</f>
@@ -2890,7 +2893,7 @@
     </row>
     <row r="51" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -2983,37 +2986,37 @@
       <c r="CM51" s="10"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="C53" s="28" t="s">
+      <c r="B53" s="29" t="s">
         <v>189</v>
+      </c>
+      <c r="C53" s="29" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C54" s="22">
+      <c r="B54" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C54" s="23">
         <v>60</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="C55" s="22">
+      <c r="B55" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="23">
         <v>40</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3042,12 +3045,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -3140,37 +3143,37 @@
       <c r="CM4" s="10"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="D6" s="28" t="s">
+      <c r="B6" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>198</v>
+      <c r="J6" s="29" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="32">
         <f>'입력값'!C9*100</f>
@@ -3179,14 +3182,14 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" s="32">
         <f>'입력값'!C41*100</f>
         <v>85535</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E8" s="40">
         <f>'입력값'!D41</f>
@@ -3208,20 +3211,20 @@
         <f>'입력값'!H41</f>
         <v>1</v>
       </c>
-      <c r="J8" s="31" t="s">
-        <v>109</v>
+      <c r="J8" s="18" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" s="32">
         <f>'입력값'!C42*100</f>
         <v>49256</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E9" s="40">
         <f>'입력값'!D42</f>
@@ -3243,13 +3246,13 @@
         <f>'입력값'!H42</f>
         <v>1</v>
       </c>
-      <c r="J9" s="31" t="s">
-        <v>109</v>
+      <c r="J9" s="18" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C10" s="43">
         <f>C8+C9</f>
@@ -3258,7 +3261,7 @@
     </row>
     <row r="12" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -3352,7 +3355,7 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C14" s="32">
         <f>'Debt'!D12</f>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C15" s="32">
         <f>$D$30*100+'Debt'!D12</f>
@@ -3370,7 +3373,7 @@
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C16" s="32">
         <f>'입력값'!C8*100</f>
@@ -3379,7 +3382,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C17" s="32">
         <f>$D$30*100+$D$32*100+'Debt'!D12</f>
@@ -3388,7 +3391,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="32">
         <f>$D$31*100+$D$33*100+$D$34*100</f>
@@ -3397,20 +3400,20 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C19" s="14">
         <f>C18-C17</f>
         <v>-0.10684055057936348</v>
       </c>
-      <c r="E19" s="31" t="str">
+      <c r="E19" s="18" t="str">
         <f>IF(C18-C17&gt;=-1,"조달 충족 (OK)","경고: 조달 부족 — 못 빌린 돈이 공짜로 조달된 셈이 되어 이자가 과소계상됩니다")</f>
         <v>조달 충족 (OK)</v>
       </c>
     </row>
     <row r="21" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -3503,21 +3506,21 @@
       <c r="CM21" s="10"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="D23" s="28" t="s">
+      <c r="B23" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="D23" s="29" t="s">
         <v>211</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="31" t="str">
+      <c r="B24" s="18" t="str">
         <f>'입력값'!B54</f>
         <v>출자자1</v>
       </c>
@@ -3533,7 +3536,7 @@
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="31" t="str">
+      <c r="B25" s="18" t="str">
         <f>'입력값'!B55</f>
         <v>출자자2</v>
       </c>
@@ -3550,11 +3553,11 @@
     </row>
     <row r="28" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -3646,15 +3649,15 @@
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D30" s="46">
         <f>'입력값'!C8</f>
@@ -3663,10 +3666,10 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D31" s="46">
         <f>'입력값'!C9</f>
@@ -3675,10 +3678,10 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="34" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D32" s="46">
         <f>'입력값'!C23</f>
@@ -3687,10 +3690,10 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D33" s="46">
         <f>'입력값'!C41</f>
@@ -3699,10 +3702,10 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D34" s="46">
         <f>'입력값'!C42</f>
@@ -3736,12 +3739,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -3834,280 +3837,280 @@
       <c r="CM4" s="10"/>
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="29" t="s">
         <v>98</v>
       </c>
+      <c r="D6" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="E6" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(E8:CL8)</f>
@@ -4380,10 +4383,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="35" t="s">
         <v>229</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>228</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(E9:CL9)</f>
@@ -4651,10 +4654,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D10" s="32">
         <f>SUM(E10:CL10)</f>
@@ -4926,10 +4929,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D11" s="32">
         <f>SUM(E11:CL11)</f>
@@ -5201,10 +5204,10 @@
     </row>
     <row r="12" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B12" s="47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D12" s="14">
         <f>SUM(E12:CL12)</f>
@@ -5557,10 +5560,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E13" s="32">
         <f>E8+E9+E12</f>
@@ -5909,10 +5912,10 @@
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E14" s="32">
         <f>MIN(MAX(E13-(0),0),$D$57*100)*($D$57*100)/IF(($D$57*100)=0,1,$D$57*100)</f>
@@ -6261,10 +6264,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E15" s="32">
         <f>MIN(MAX(E13-($D$57*100),0),$D$58*100+$D$61*100)*($D$58*100)/IF(($D$58*100+$D$61*100)=0,1,$D$58*100+$D$61*100)</f>
@@ -6613,10 +6616,10 @@
     </row>
     <row r="16" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E16" s="32">
         <f>MIN(MAX(E13-($D$57*100),0),$D$58*100+$D$61*100)*($D$61*100)/IF(($D$58*100+$D$61*100)=0,1,$D$58*100+$D$61*100)</f>
@@ -6965,7 +6968,7 @@
     </row>
     <row r="19" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -7058,277 +7061,277 @@
       <c r="CM19" s="10"/>
     </row>
     <row r="21" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B21" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="28" t="s">
+      <c r="B21" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="C21" s="29" t="s">
         <v>98</v>
       </c>
+      <c r="D21" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="E21" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F21" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H21" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L21" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M21" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O21" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P21" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q21" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R21" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S21" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T21" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U21" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V21" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W21" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X21" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y21" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z21" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA21" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB21" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC21" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD21" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE21" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF21" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG21" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH21" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI21" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK21" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL21" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM21" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN21" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO21" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP21" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ21" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR21" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS21" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT21" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU21" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV21" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW21" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX21" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY21" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ21" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA21" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB21" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC21" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD21" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE21" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF21" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG21" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH21" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI21" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ21" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK21" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL21" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM21" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN21" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO21" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP21" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ21" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR21" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS21" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT21" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU21" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV21" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW21" s="33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX21" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY21" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ21" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA21" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB21" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC21" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="CD21" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE21" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CF21" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="CG21" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CH21" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="CI21" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="CJ21" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CK21" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CL21" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B23" s="48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" s="49"/>
       <c r="D23" s="49"/>
@@ -7422,10 +7425,10 @@
     </row>
     <row r="24" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E24" s="32">
         <v>0</v>
@@ -7773,10 +7776,10 @@
     </row>
     <row r="25" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D25" s="32">
         <f>SUM(E25:CL25)</f>
@@ -8129,10 +8132,10 @@
     </row>
     <row r="26" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D26" s="32">
         <f>SUM(E26:CL26)</f>
@@ -8485,10 +8488,10 @@
     </row>
     <row r="27" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D27" s="14">
         <f>SUM(E27:CL27)</f>
@@ -8835,10 +8838,10 @@
     </row>
     <row r="28" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D28" s="14">
         <f>SUM(E28:CL28)</f>
@@ -9169,10 +9172,10 @@
     </row>
     <row r="29" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B29" s="47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E29" s="14">
         <f>E24+E25-E28</f>
@@ -9521,23 +9524,23 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D30" s="32">
         <f>CL29</f>
         <v>0</v>
       </c>
-      <c r="F30" s="31" t="str">
+      <c r="F30" s="18" t="str">
         <f>IF(ABS(D30)&lt;1,"완전상환 확인 (OK)","경고: 미상환 잔액")</f>
         <v>완전상환 확인 (OK)</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F31" s="50" t="str">
         <f>IF(AND(E15&lt;1,F15&gt;1),"인출 시작 분기 일치 (OK)","경고: 첫 인출 분기가 생성 당시(2024-09-30)와 달라졌습니다. 상환 스케줄이 들어간 열은 고정이라 실제와 어긋납니다 — 화면(HTML)에서 다시 생성하세요.")</f>
@@ -9546,7 +9549,7 @@
     </row>
     <row r="33" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B33" s="48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" s="49"/>
       <c r="D33" s="49"/>
@@ -9640,10 +9643,10 @@
     </row>
     <row r="34" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E34" s="32">
         <v>0</v>
@@ -9991,10 +9994,10 @@
     </row>
     <row r="35" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B35" s="34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D35" s="32">
         <f>SUM(E35:CL35)</f>
@@ -10347,10 +10350,10 @@
     </row>
     <row r="36" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D36" s="32">
         <f>SUM(E36:CL36)</f>
@@ -10703,10 +10706,10 @@
     </row>
     <row r="37" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D37" s="14">
         <f>SUM(E37:CL37)</f>
@@ -11053,10 +11056,10 @@
     </row>
     <row r="38" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D38" s="14">
         <f>SUM(E38:CL38)</f>
@@ -11387,10 +11390,10 @@
     </row>
     <row r="39" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B39" s="47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E39" s="14">
         <f>E34+E35-E38</f>
@@ -11739,23 +11742,23 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D40" s="32">
         <f>CL39</f>
         <v>0</v>
       </c>
-      <c r="F40" s="31" t="str">
+      <c r="F40" s="18" t="str">
         <f>IF(ABS(D40)&lt;1,"완전상환 확인 (OK)","경고: 미상환 잔액")</f>
         <v>완전상환 확인 (OK)</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F41" s="50" t="str">
         <f>IF(AND(E16&lt;1,F16&gt;1),"인출 시작 분기 일치 (OK)","경고: 첫 인출 분기가 생성 당시(2024-09-30)와 달라졌습니다. 상환 스케줄이 들어간 열은 고정이라 실제와 어긋납니다 — 화면(HTML)에서 다시 생성하세요.")</f>
@@ -11764,7 +11767,7 @@
     </row>
     <row r="43" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
@@ -11858,10 +11861,10 @@
     </row>
     <row r="44" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E44" s="32">
         <f>E24+E34</f>
@@ -12210,10 +12213,10 @@
     </row>
     <row r="45" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B45" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D45" s="14">
         <f>SUM(E45:CL45)</f>
@@ -12566,10 +12569,10 @@
     </row>
     <row r="46" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D46" s="14">
         <f>SUM(E46:CL46)</f>
@@ -12922,10 +12925,10 @@
     </row>
     <row r="47" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B47" s="48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D47" s="43">
         <f>SUM(E47:CL47)</f>
@@ -13279,10 +13282,10 @@
     </row>
     <row r="48" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B48" s="34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E48" s="32">
         <f>E29+E39</f>
@@ -13631,10 +13634,10 @@
     </row>
     <row r="50" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B50" s="34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E50" s="32">
         <f>0</f>
@@ -13983,10 +13986,10 @@
     </row>
     <row r="51" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B51" s="34" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E51" s="32">
         <f>E50</f>
@@ -14335,11 +14338,11 @@
     </row>
     <row r="54" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B54" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -14431,15 +14434,15 @@
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="34" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D56" s="46">
         <f>'입력값'!C8</f>
@@ -14448,10 +14451,10 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="34" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D57" s="46">
         <f>'입력값'!C9</f>
@@ -14460,10 +14463,10 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D58" s="46">
         <f>'입력값'!C41</f>
@@ -14472,10 +14475,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D59" s="52">
         <f>'입력값'!D41</f>
@@ -14484,10 +14487,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D60" s="52">
         <f>'입력값'!E41</f>
@@ -14496,10 +14499,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D61" s="46">
         <f>'입력값'!C42</f>
@@ -14508,10 +14511,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D62" s="52">
         <f>'입력값'!D42</f>
@@ -14520,10 +14523,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D63" s="52">
         <f>'입력값'!E42</f>
@@ -14532,10 +14535,10 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E64" s="53">
         <f>'입력값'!E49</f>
@@ -14589,12 +14592,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -14687,280 +14690,280 @@
       <c r="CM4" s="10"/>
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="29" t="s">
         <v>98</v>
       </c>
+      <c r="D6" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="E6" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E8" s="54">
         <v>0</v>
@@ -15223,10 +15226,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E9" s="55">
         <v>0</v>
@@ -15489,10 +15492,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D11" s="56">
         <f>SUM(E11:CL11)</f>
@@ -15845,10 +15848,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="57"/>
@@ -16179,10 +16182,10 @@
     </row>
     <row r="14" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B14" s="48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D14" s="43">
         <f>SUM(E14:CL14)</f>
@@ -16530,7 +16533,7 @@
     </row>
     <row r="16" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -16624,10 +16627,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E18" s="32">
         <f>MIN(1,3)/3*E14</f>
@@ -16975,10 +16978,10 @@
     </row>
     <row r="19" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B19" s="48" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D19" s="43">
         <f>SUM(E19:CL19)</f>
@@ -17332,16 +17335,16 @@
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -17433,15 +17436,15 @@
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D25" s="58">
         <f>'입력값'!C7</f>
@@ -17450,10 +17453,10 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D26" s="59">
         <f>'입력값'!C10</f>
@@ -17462,10 +17465,10 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D27" s="60">
         <f>'입력값'!C11</f>
@@ -17474,10 +17477,10 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D28" s="60">
         <f>'입력값'!C12</f>
@@ -17486,10 +17489,10 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="34" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D29" s="60">
         <f>'입력값'!C13</f>
@@ -17498,10 +17501,10 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D30" s="61">
         <f>'입력값'!C14</f>
@@ -17535,12 +17538,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -17633,280 +17636,280 @@
       <c r="CM4" s="10"/>
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="29" t="s">
         <v>98</v>
       </c>
+      <c r="D6" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="E6" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(E8:CL8)</f>
@@ -18253,10 +18256,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(E9:CL9)</f>
@@ -18603,10 +18606,10 @@
     </row>
     <row r="10" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B10" s="48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D10" s="43">
         <f>SUM(E10:CL10)</f>
@@ -18960,16 +18963,16 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -19061,15 +19064,15 @@
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D17" s="46">
         <f>'입력값'!C18</f>
@@ -19078,10 +19081,10 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D18" s="60">
         <f>'입력값'!C19</f>
@@ -19090,10 +19093,10 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D19" s="60">
         <f>'입력값'!C20</f>
@@ -19127,12 +19130,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -19225,280 +19228,280 @@
       <c r="CM4" s="10"/>
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="29" t="s">
         <v>98</v>
       </c>
+      <c r="D6" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="E6" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="47" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D8" s="14">
         <f>SUM(E8:CL8)</f>
@@ -19851,10 +19854,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="47" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D10" s="14">
         <f>SUM(E10:CL10)</f>
@@ -20207,10 +20210,10 @@
     </row>
     <row r="12" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B12" s="48" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D12" s="43">
         <f>SUM(E12:CL12)</f>
@@ -20564,10 +20567,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E13" s="40" t="str">
         <f>IF(E8&lt;=0,"",E12/E8)</f>
@@ -20916,10 +20919,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D15" s="32">
         <f>SUM(E15:CL15)</f>
@@ -21266,10 +21269,10 @@
     </row>
     <row r="16" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D16" s="32">
         <f>SUM(E16:CL16)</f>
@@ -21616,10 +21619,10 @@
     </row>
     <row r="17" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D17" s="32">
         <f>SUM(E17:CL17)</f>
@@ -21966,10 +21969,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D18" s="32">
         <f>SUM(E18:CL18)</f>
@@ -22316,10 +22319,10 @@
     </row>
     <row r="19" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B19" s="47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D19" s="14">
         <f>SUM(E19:CL19)</f>
@@ -22672,10 +22675,10 @@
     </row>
     <row r="20" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E20" s="40" t="str">
         <f>IF(E8&lt;=0,"",E19/E8)</f>
@@ -23024,15 +23027,15 @@
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D23" s="32">
         <f>SUM(E23:CL23)</f>
@@ -23385,10 +23388,10 @@
     </row>
     <row r="24" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D24" s="32">
         <f>SUM(E24:CL24)</f>
@@ -23741,10 +23744,10 @@
     </row>
     <row r="25" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B25" s="47" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D25" s="14">
         <f>SUM(E25:CL25)</f>
@@ -24097,10 +24100,10 @@
     </row>
     <row r="27" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B27" s="47" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D27" s="14">
         <f>SUM(E27:CL27)</f>
@@ -24453,10 +24456,10 @@
     </row>
     <row r="28" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D28" s="32">
         <f>SUM(E28:CL28)</f>
@@ -24809,10 +24812,10 @@
     </row>
     <row r="29" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B29" s="48" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D29" s="43">
         <f>SUM(E29:CL29)</f>
@@ -25166,7 +25169,7 @@
     </row>
     <row r="32" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -25260,10 +25263,10 @@
     </row>
     <row r="34" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D34" s="32">
         <f>SUM(E34:CL34)</f>
@@ -25616,7 +25619,7 @@
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E36" s="13">
         <v>2024</v>
@@ -25687,10 +25690,10 @@
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E37" s="32">
         <f>E34+F34+G34</f>
@@ -25783,10 +25786,10 @@
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E38" s="32">
         <f>0</f>
@@ -25879,10 +25882,10 @@
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E39" s="32">
         <f>IF(E37&lt;=0,0,MIN(E38,E37*$D$63/100))</f>
@@ -25975,10 +25978,10 @@
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E40" s="32">
         <f>IF(E37&lt;=0,E38-E37,E38-E39)</f>
@@ -26071,10 +26074,10 @@
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E41" s="32">
         <f>MAX(0,E37-E39)</f>
@@ -26167,10 +26170,10 @@
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E42" s="32">
         <f>IF(E37&lt;=0,0,MIN(MAX(E41,0),200)*0.09+MIN(MAX(E41-200,0),19800)*0.19+MIN(MAX(E41-20000,0),280000)*0.21+MAX(E41-300000,0)*0.24)</f>
@@ -26263,10 +26266,10 @@
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E43" s="32">
         <f>E41*$D$64/100</f>
@@ -26359,10 +26362,10 @@
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E44" s="32">
         <f>0</f>
@@ -26455,10 +26458,10 @@
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E45" s="32">
         <f>(0)*$D$65/100</f>
@@ -26551,10 +26554,10 @@
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E46" s="32">
         <f>MAX(0,E42-(E44+E45))</f>
@@ -26647,10 +26650,10 @@
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" s="34" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E47" s="32">
         <f>IF(E37&lt;=0,0,MAX(E43,E46))</f>
@@ -26743,10 +26746,10 @@
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" s="34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E48" s="32">
         <f>E42-E47</f>
@@ -26839,10 +26842,10 @@
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" s="34" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E49" s="32">
         <f>E44+E45-E48</f>
@@ -26935,10 +26938,10 @@
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" s="47" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E50" s="14">
         <f>E47*(1+$D$66/100)+E48*$D$67/100</f>
@@ -27031,10 +27034,10 @@
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" s="34" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E51" s="32">
         <f>MAX(0,E27)+MAX(0,F27)+MAX(0,G27)</f>
@@ -27127,16 +27130,16 @@
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="38" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -27228,15 +27231,15 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D58" s="60">
         <f>'입력값'!C15</f>
@@ -27245,10 +27248,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D59" s="62">
         <f>'입력값'!C16</f>
@@ -27257,10 +27260,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D60" s="46">
         <f>'입력값'!C17</f>
@@ -27269,10 +27272,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D61" s="46">
         <f>'입력값'!C21</f>
@@ -27281,10 +27284,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D62" s="46">
         <f>'입력값'!C22</f>
@@ -27293,10 +27296,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D63" s="60">
         <f>'입력값'!C32</f>
@@ -27305,10 +27308,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="34" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D64" s="60">
         <f>'입력값'!C33</f>
@@ -27317,10 +27320,10 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="34" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D65" s="60">
         <f>'입력값'!C34</f>
@@ -27329,10 +27332,10 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="34" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C66" s="45" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D66" s="60">
         <f>'입력값'!C35</f>
@@ -27341,10 +27344,10 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="34" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D67" s="60">
         <f>'입력값'!C36</f>
@@ -27378,12 +27381,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -27476,280 +27479,280 @@
       <c r="CM4" s="10"/>
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="29" t="s">
         <v>98</v>
       </c>
+      <c r="D6" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="E6" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B9" s="48" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D9" s="43">
         <f>SUM(E9:CL9)</f>
@@ -28103,10 +28106,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D10" s="32">
         <f>SUM(E10:CL10)</f>
@@ -28459,10 +28462,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -28757,10 +28760,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="47" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D13" s="14">
         <f>SUM(E13:CL13)</f>
@@ -29113,10 +29116,10 @@
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D14" s="32">
         <f>SUM(E14:CL14)</f>
@@ -29469,10 +29472,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E15" s="32">
         <f>0</f>
@@ -29821,10 +29824,10 @@
     </row>
     <row r="16" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B16" s="48" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D16" s="43">
         <f>SUM(E16:CL16)</f>
@@ -30178,10 +30181,10 @@
     </row>
     <row r="17" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E17" s="32">
         <f>E18-E16</f>
@@ -30530,10 +30533,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E18" s="32">
         <f>E15+E13</f>
@@ -30882,10 +30885,10 @@
     </row>
     <row r="19" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E19" s="32">
         <v>0</v>
@@ -31148,10 +31151,10 @@
     </row>
     <row r="20" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E20" s="32">
         <f>0</f>
@@ -31500,10 +31503,10 @@
     </row>
     <row r="21" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E21" s="32">
         <f>E20</f>
@@ -31852,10 +31855,10 @@
     </row>
     <row r="22" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E22" s="32">
         <f>0</f>
@@ -32204,10 +32207,10 @@
     </row>
     <row r="23" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E23" s="32">
         <f>0</f>
@@ -32556,10 +32559,10 @@
     </row>
     <row r="24" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="64">
@@ -32910,7 +32913,7 @@
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E26" s="13">
         <v>2025</v>
@@ -32969,10 +32972,10 @@
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E27" s="32">
         <f>K10</f>
@@ -33049,10 +33052,10 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E28" s="32">
         <f>K9</f>
@@ -33129,10 +33132,10 @@
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" s="34" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E29" s="65">
         <f>IF(E27=0,"",E28/E27)</f>
@@ -33209,10 +33212,10 @@
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E30" s="65">
         <f>IF(E27=0,"",(H15+H20+E28)/E27)</f>
@@ -33289,111 +33292,111 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="34" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="34" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="34" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="C36" s="35" t="s">
         <v>383</v>
-      </c>
-      <c r="C36" s="35" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="34" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -33487,10 +33490,10 @@
     </row>
     <row r="46" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E46" s="32">
         <f>0</f>
@@ -33839,10 +33842,10 @@
     </row>
     <row r="47" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B47" s="47" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D47" s="17">
         <f>MIN(E29:V29)</f>
@@ -34195,10 +34198,10 @@
     </row>
     <row r="48" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B48" s="47" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D48" s="17">
         <f>MIN(E30:V30)</f>
@@ -34533,10 +34536,10 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="47" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D49" s="14">
         <f>CL17</f>
@@ -34545,7 +34548,7 @@
     </row>
     <row r="51" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -34638,280 +34641,280 @@
       <c r="CM51" s="10"/>
     </row>
     <row r="53" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B53" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C53" s="28" t="s">
+      <c r="B53" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D53" s="28" t="s">
+      <c r="C53" s="29" t="s">
         <v>98</v>
       </c>
+      <c r="D53" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="E53" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G53" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H53" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I53" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L53" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M53" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N53" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O53" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P53" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q53" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R53" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S53" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T53" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U53" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V53" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W53" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X53" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y53" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z53" s="33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA53" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AB53" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC53" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD53" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AE53" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF53" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG53" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH53" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI53" s="33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AJ53" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK53" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL53" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM53" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AN53" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO53" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AP53" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ53" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AR53" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS53" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AT53" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AU53" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV53" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AW53" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AX53" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AY53" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ53" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BA53" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BB53" s="33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC53" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BD53" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BE53" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BF53" s="33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BG53" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BH53" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BI53" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BJ53" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BK53" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BL53" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BM53" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BN53" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BO53" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BP53" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BQ53" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BR53" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="BS53" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="BT53" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="BU53" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BV53" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BW53" s="33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BX53" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BY53" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BZ53" s="33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CA53" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="CB53" s="33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CC53" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="CD53" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CE53" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CF53" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="CG53" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CH53" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="CI53" s="33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="CJ53" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CK53" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CL53" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D55" s="32">
         <f>SUM(E55:CL55)</f>
@@ -35264,10 +35267,10 @@
     </row>
     <row r="56" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B56" s="34" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E56" s="32">
         <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E28+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
@@ -35616,10 +35619,10 @@
     </row>
     <row r="57" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B57" s="34" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E57" s="32">
         <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
@@ -35968,10 +35971,10 @@
     </row>
     <row r="58" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E58" s="32">
         <f>E13-E55</f>
@@ -36320,10 +36323,10 @@
     </row>
     <row r="59" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E59" s="32">
         <f>E13-'IS(Q)'!E28-E19-E55</f>
@@ -36672,10 +36675,10 @@
     </row>
     <row r="60" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E60" s="32">
         <f>E16-E55</f>
@@ -37024,10 +37027,10 @@
     </row>
     <row r="61" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E61" s="32">
         <f>-E55-('Debt'!E15+'Debt'!E16)+'Debt'!E45+'Debt'!E46+E16</f>
@@ -37376,10 +37379,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="47" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D63" s="15">
         <f>(1+IRR(E57:CL57,0.020547644500372275))^4-1</f>
@@ -37388,10 +37391,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="47" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D64" s="15">
         <f>(1+IRR(E56:CL56,0.018842248557486396))^4-1</f>
@@ -37400,10 +37403,10 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="47" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D65" s="15">
         <f>(1+IRR(E59:CL59,0.03784631241217884))^4-1</f>
@@ -37412,10 +37415,10 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="47" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D66" s="15">
         <f>(1+IRR(E58:CL58,0.03126734292077549))^4-1</f>
@@ -37424,10 +37427,10 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="47" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D67" s="15">
         <f>(1+IRR(E60:CL60,0.024425729620145553))^4-1</f>
@@ -37436,10 +37439,10 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="47" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D68" s="15">
         <f>(1+IRR(E61:CL61,0.01682783163204693))^4-1</f>
@@ -37448,16 +37451,16 @@
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" s="38" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="73" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
@@ -37549,15 +37552,15 @@
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" s="38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="34" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D75" s="46">
         <f>'입력값'!C17</f>
@@ -37566,10 +37569,10 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="34" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C76" s="45" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D76" s="46">
         <f>'입력값'!C25</f>
@@ -37578,10 +37581,10 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="34" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C77" s="45" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D77" s="66">
         <f>'입력값'!C26</f>
@@ -37590,10 +37593,10 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="34" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C78" s="45" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D78" s="66">
         <f>'입력값'!C27</f>
@@ -37602,10 +37605,10 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="34" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C79" s="45" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D79" s="67">
         <f>'입력값'!C28</f>
@@ -37623,7 +37626,7 @@
   <sheetPr>
     <tabColor rgb="FF14483A"/>
   </sheetPr>
-  <dimension ref="A1:CM32"/>
+  <dimension ref="A1:CM33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -38084,13 +38087,17 @@
         <v>1.187143523658971</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="14">
-        <f>'Revenue'!D14</f>
-        <v>405788.8886999999</v>
+        <f>MIN('CF(Q)'!E17:CL17)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="18" t="str">
+        <f>IF(D28&gt;=-1,"운영자금 충족 (OK)","경고: 운영 중 현금 부족 — 추가 출자·브리지가 필요하고 위 Equity IRR 은 과대평가된 값입니다")</f>
+        <v>운영자금 충족 (OK)</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
@@ -38098,8 +38105,8 @@
         <v>49</v>
       </c>
       <c r="D29" s="14">
-        <f>'Opex'!D10</f>
-        <v>106510.04740942549</v>
+        <f>'Revenue'!D14</f>
+        <v>405788.8886999999</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
@@ -38107,8 +38114,8 @@
         <v>50</v>
       </c>
       <c r="D30" s="14">
-        <f>'Debt'!D45</f>
-        <v>68428.74</v>
+        <f>'Opex'!D10</f>
+        <v>106510.04740942549</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
@@ -38116,8 +38123,8 @@
         <v>51</v>
       </c>
       <c r="D31" s="14">
-        <f>-'IS(Q)'!D28</f>
-        <v>18618.801256538776</v>
+        <f>'Debt'!D45</f>
+        <v>68428.74</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
@@ -38125,6 +38132,15 @@
         <v>52</v>
       </c>
       <c r="D32" s="14">
+        <f>-'IS(Q)'!D28</f>
+        <v>18618.801256538776</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="14">
         <f>'CF(Q)'!D16</f>
         <v>80440.30003403581</v>
       </c>

--- a/contract/sample-output.xlsx
+++ b/contract/sample-output.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="423">
   <si>
     <t>샘플 태양광 100MW</t>
   </si>
@@ -150,7 +150,7 @@
     <t>Project IRR 세후 [%]</t>
   </si>
   <si>
-    <t>위와 같되 법인세 후</t>
+    <t>실제 납부 법인세 기준 — 이자 손금(차입으로 줄어든 세금)이 반영돼 있어 Equity IRR 세후와 직접 비교하면 안 됩니다. 레버리지 효과는 세전끼리 비교하세요</t>
   </si>
   <si>
     <t>Investor IRR [%]</t>
@@ -165,9 +165,15 @@
     <t>최소 누적DSCR [x]</t>
   </si>
   <si>
+    <t>운전자금 추가 출자 합계 [KRWm]</t>
+  </si>
+  <si>
     <t>운영 중 최저 보유현금 [KRWm]</t>
   </si>
   <si>
+    <t>추가 출자를 반영한 뒤의 최저 잔액 — 0 이상이어야 정상</t>
+  </si>
+  <si>
     <t>총영업수익(전체기간) [KRWm]</t>
   </si>
   <si>
@@ -1141,6 +1147,9 @@
   </si>
   <si>
     <t>연도별 DSCR · 배당 게이트</t>
+  </si>
+  <si>
+    <t>추가 출자(운전자금 부족분)</t>
   </si>
   <si>
     <t>원리금 합(연간)</t>
@@ -1459,7 +1468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1535,6 +1544,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1897,12 +1907,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2005,7 +2015,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" s="20">
         <v>100</v>
@@ -2013,7 +2023,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="21">
         <v>1410.69</v>
@@ -2021,7 +2031,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9" s="21">
         <v>150.03</v>
@@ -2029,7 +2039,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C10" s="22">
         <v>154.8</v>
@@ -2037,7 +2047,7 @@
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" s="23">
         <v>0</v>
@@ -2045,7 +2055,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12" s="23">
         <v>0.5</v>
@@ -2053,7 +2063,7 @@
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" s="23">
         <v>0</v>
@@ -2061,7 +2071,7 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" s="24">
         <v>3.77</v>
@@ -2069,7 +2079,7 @@
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" s="23">
         <v>95</v>
@@ -2077,7 +2087,7 @@
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16" s="25">
         <v>20</v>
@@ -2085,7 +2095,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C17" s="21">
         <v>20</v>
@@ -2093,7 +2103,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C18" s="21">
         <v>49.8</v>
@@ -2101,7 +2111,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" s="23">
         <v>0.7</v>
@@ -2109,7 +2119,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C20" s="23">
         <v>0</v>
@@ -2117,7 +2127,7 @@
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C21" s="21">
         <v>0</v>
@@ -2125,7 +2135,7 @@
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C22" s="21">
         <v>0</v>
@@ -2133,7 +2143,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" s="21">
         <v>50</v>
@@ -2141,7 +2151,7 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" s="26">
         <v>6</v>
@@ -2149,7 +2159,7 @@
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C25" s="21">
         <v>10</v>
@@ -2157,7 +2167,7 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C26" s="27">
         <v>1.1</v>
@@ -2165,7 +2175,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C27" s="27">
         <v>1.15</v>
@@ -2173,7 +2183,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C28" s="28">
         <v>2</v>
@@ -2181,7 +2191,7 @@
     </row>
     <row r="30" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -2276,7 +2286,7 @@
     <row r="31" spans="2:2" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C32" s="23">
         <v>80</v>
@@ -2284,7 +2294,7 @@
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" s="23">
         <v>0</v>
@@ -2292,7 +2302,7 @@
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C34" s="23">
         <v>0</v>
@@ -2300,7 +2310,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C35" s="23">
         <v>10</v>
@@ -2308,7 +2318,7 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="23">
         <v>0</v>
@@ -2316,7 +2326,7 @@
     </row>
     <row r="38" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -2410,33 +2420,33 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G40" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H40" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I40" s="29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C41" s="21">
         <v>855.35</v>
@@ -2462,7 +2472,7 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" s="21">
         <v>492.56</v>
@@ -2488,7 +2498,7 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C43" s="32">
         <f>C9</f>
@@ -2500,7 +2510,7 @@
     </row>
     <row r="45" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -2594,279 +2604,279 @@
     </row>
     <row r="47" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B47" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G47" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H47" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I47" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K47" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L47" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M47" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N47" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O47" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P47" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q47" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R47" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S47" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T47" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U47" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V47" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W47" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X47" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y47" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z47" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA47" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB47" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC47" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD47" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE47" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AF47" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG47" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AH47" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AI47" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ47" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK47" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AL47" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM47" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN47" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO47" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AP47" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ47" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR47" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AS47" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AT47" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AU47" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AV47" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AW47" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AX47" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AY47" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ47" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BA47" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BB47" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BC47" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BD47" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BE47" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BF47" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BG47" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH47" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BI47" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BJ47" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK47" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BL47" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BM47" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN47" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BO47" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BP47" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ47" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BR47" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BS47" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BT47" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU47" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BV47" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BW47" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BX47" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BY47" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BZ47" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="CA47" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CB47" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CC47" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD47" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CE47" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CF47" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CG47" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CH47" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CI47" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CJ47" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CK47" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CL47" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="34" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D49" s="36">
         <f>SUM(E49:CL49)</f>
@@ -2893,7 +2903,7 @@
     </row>
     <row r="51" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -2987,15 +2997,15 @@
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C54" s="23">
         <v>60</v>
@@ -3003,7 +3013,7 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C55" s="23">
         <v>40</v>
@@ -3011,12 +3021,12 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3045,12 +3055,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -3144,36 +3154,36 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D6" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>90</v>
-      </c>
       <c r="I6" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C7" s="32">
         <f>'입력값'!C9*100</f>
@@ -3182,14 +3192,14 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C8" s="32">
         <f>'입력값'!C41*100</f>
         <v>85535</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E8" s="40">
         <f>'입력값'!D41</f>
@@ -3212,19 +3222,19 @@
         <v>1</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" s="32">
         <f>'입력값'!C42*100</f>
         <v>49256</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E9" s="40">
         <f>'입력값'!D42</f>
@@ -3247,12 +3257,12 @@
         <v>1</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="42" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C10" s="43">
         <f>C8+C9</f>
@@ -3261,7 +3271,7 @@
     </row>
     <row r="12" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -3355,7 +3365,7 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="32" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C14" s="32">
         <f>'Debt'!D12</f>
@@ -3364,7 +3374,7 @@
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="32" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C15" s="32">
         <f>$D$30*100+'Debt'!D12</f>
@@ -3373,7 +3383,7 @@
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="32" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C16" s="32">
         <f>'입력값'!C8*100</f>
@@ -3382,7 +3392,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C17" s="32">
         <f>$D$30*100+$D$32*100+'Debt'!D12</f>
@@ -3391,7 +3401,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C18" s="32">
         <f>$D$31*100+$D$33*100+$D$34*100</f>
@@ -3400,7 +3410,7 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C19" s="14">
         <f>C18-C17</f>
@@ -3413,7 +3423,7 @@
     </row>
     <row r="21" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -3507,16 +3517,16 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
@@ -3553,11 +3563,11 @@
     </row>
     <row r="28" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -3649,15 +3659,15 @@
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D30" s="46">
         <f>'입력값'!C8</f>
@@ -3666,10 +3676,10 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D31" s="46">
         <f>'입력값'!C9</f>
@@ -3678,10 +3688,10 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D32" s="46">
         <f>'입력값'!C23</f>
@@ -3690,10 +3700,10 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="34" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D33" s="46">
         <f>'입력값'!C41</f>
@@ -3702,10 +3712,10 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D34" s="46">
         <f>'입력값'!C42</f>
@@ -3739,12 +3749,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -3838,279 +3848,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(E8:CL8)</f>
@@ -4383,10 +4393,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(E9:CL9)</f>
@@ -4654,10 +4664,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>231</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>229</v>
       </c>
       <c r="D10" s="32">
         <f>SUM(E10:CL10)</f>
@@ -4929,10 +4939,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="34" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D11" s="32">
         <f>SUM(E11:CL11)</f>
@@ -5204,10 +5214,10 @@
     </row>
     <row r="12" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B12" s="47" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D12" s="14">
         <f>SUM(E12:CL12)</f>
@@ -5560,10 +5570,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E13" s="32">
         <f>E8+E9+E12</f>
@@ -5912,10 +5922,10 @@
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E14" s="32">
         <f>MIN(MAX(E13-(0),0),$D$57*100)*($D$57*100)/IF(($D$57*100)=0,1,$D$57*100)</f>
@@ -6264,10 +6274,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E15" s="32">
         <f>MIN(MAX(E13-($D$57*100),0),$D$58*100+$D$61*100)*($D$58*100)/IF(($D$58*100+$D$61*100)=0,1,$D$58*100+$D$61*100)</f>
@@ -6616,10 +6626,10 @@
     </row>
     <row r="16" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E16" s="32">
         <f>MIN(MAX(E13-($D$57*100),0),$D$58*100+$D$61*100)*($D$61*100)/IF(($D$58*100+$D$61*100)=0,1,$D$58*100+$D$61*100)</f>
@@ -6968,7 +6978,7 @@
     </row>
     <row r="19" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -7062,276 +7072,276 @@
     </row>
     <row r="21" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B21" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F21" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H21" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L21" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M21" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O21" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P21" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q21" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R21" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S21" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T21" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U21" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V21" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W21" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X21" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y21" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z21" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA21" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB21" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC21" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD21" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE21" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AF21" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG21" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AH21" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AI21" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK21" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AL21" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM21" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN21" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO21" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AP21" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ21" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR21" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AS21" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AT21" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AU21" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AV21" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AW21" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AX21" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AY21" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ21" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BA21" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BB21" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BC21" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BD21" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BE21" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BF21" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BG21" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH21" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BI21" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BJ21" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK21" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BL21" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BM21" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN21" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BO21" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BP21" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ21" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BR21" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BS21" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BT21" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU21" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BV21" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BW21" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BX21" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BY21" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BZ21" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="CA21" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CB21" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CC21" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD21" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CE21" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CF21" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CG21" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CH21" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CI21" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CJ21" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CK21" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CL21" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B23" s="48" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C23" s="49"/>
       <c r="D23" s="49"/>
@@ -7425,10 +7435,10 @@
     </row>
     <row r="24" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E24" s="32">
         <v>0</v>
@@ -7776,10 +7786,10 @@
     </row>
     <row r="25" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D25" s="32">
         <f>SUM(E25:CL25)</f>
@@ -8132,10 +8142,10 @@
     </row>
     <row r="26" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D26" s="32">
         <f>SUM(E26:CL26)</f>
@@ -8488,10 +8498,10 @@
     </row>
     <row r="27" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D27" s="14">
         <f>SUM(E27:CL27)</f>
@@ -8838,10 +8848,10 @@
     </row>
     <row r="28" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D28" s="14">
         <f>SUM(E28:CL28)</f>
@@ -9172,10 +9182,10 @@
     </row>
     <row r="29" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B29" s="47" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E29" s="14">
         <f>E24+E25-E28</f>
@@ -9524,10 +9534,10 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D30" s="32">
         <f>CL29</f>
@@ -9540,7 +9550,7 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F31" s="50" t="str">
         <f>IF(AND(E15&lt;1,F15&gt;1),"인출 시작 분기 일치 (OK)","경고: 첫 인출 분기가 생성 당시(2024-09-30)와 달라졌습니다. 상환 스케줄이 들어간 열은 고정이라 실제와 어긋납니다 — 화면(HTML)에서 다시 생성하세요.")</f>
@@ -9549,7 +9559,7 @@
     </row>
     <row r="33" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B33" s="48" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C33" s="49"/>
       <c r="D33" s="49"/>
@@ -9643,10 +9653,10 @@
     </row>
     <row r="34" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E34" s="32">
         <v>0</v>
@@ -9994,10 +10004,10 @@
     </row>
     <row r="35" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B35" s="34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D35" s="32">
         <f>SUM(E35:CL35)</f>
@@ -10350,10 +10360,10 @@
     </row>
     <row r="36" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D36" s="32">
         <f>SUM(E36:CL36)</f>
@@ -10706,10 +10716,10 @@
     </row>
     <row r="37" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D37" s="14">
         <f>SUM(E37:CL37)</f>
@@ -11056,10 +11066,10 @@
     </row>
     <row r="38" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D38" s="14">
         <f>SUM(E38:CL38)</f>
@@ -11390,10 +11400,10 @@
     </row>
     <row r="39" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B39" s="47" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E39" s="14">
         <f>E34+E35-E38</f>
@@ -11742,10 +11752,10 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D40" s="32">
         <f>CL39</f>
@@ -11758,7 +11768,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F41" s="50" t="str">
         <f>IF(AND(E16&lt;1,F16&gt;1),"인출 시작 분기 일치 (OK)","경고: 첫 인출 분기가 생성 당시(2024-09-30)와 달라졌습니다. 상환 스케줄이 들어간 열은 고정이라 실제와 어긋납니다 — 화면(HTML)에서 다시 생성하세요.")</f>
@@ -11767,7 +11777,7 @@
     </row>
     <row r="43" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
@@ -11861,10 +11871,10 @@
     </row>
     <row r="44" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E44" s="32">
         <f>E24+E34</f>
@@ -12213,10 +12223,10 @@
     </row>
     <row r="45" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B45" s="34" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D45" s="14">
         <f>SUM(E45:CL45)</f>
@@ -12569,10 +12579,10 @@
     </row>
     <row r="46" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D46" s="14">
         <f>SUM(E46:CL46)</f>
@@ -12925,10 +12935,10 @@
     </row>
     <row r="47" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B47" s="48" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D47" s="43">
         <f>SUM(E47:CL47)</f>
@@ -13282,10 +13292,10 @@
     </row>
     <row r="48" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B48" s="34" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E48" s="32">
         <f>E29+E39</f>
@@ -13634,10 +13644,10 @@
     </row>
     <row r="50" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B50" s="34" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E50" s="32">
         <f>0</f>
@@ -13986,10 +13996,10 @@
     </row>
     <row r="51" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B51" s="34" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E51" s="32">
         <f>E50</f>
@@ -14338,11 +14348,11 @@
     </row>
     <row r="54" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B54" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -14434,15 +14444,15 @@
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="34" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D56" s="46">
         <f>'입력값'!C8</f>
@@ -14451,10 +14461,10 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="34" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D57" s="46">
         <f>'입력값'!C9</f>
@@ -14463,10 +14473,10 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D58" s="46">
         <f>'입력값'!C41</f>
@@ -14475,10 +14485,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D59" s="52">
         <f>'입력값'!D41</f>
@@ -14487,10 +14497,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D60" s="52">
         <f>'입력값'!E41</f>
@@ -14499,10 +14509,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D61" s="46">
         <f>'입력값'!C42</f>
@@ -14511,10 +14521,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D62" s="52">
         <f>'입력값'!D42</f>
@@ -14523,10 +14533,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D63" s="52">
         <f>'입력값'!E42</f>
@@ -14535,10 +14545,10 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E64" s="53">
         <f>'입력값'!E49</f>
@@ -14592,12 +14602,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -14691,279 +14701,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E8" s="54">
         <v>0</v>
@@ -15226,10 +15236,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E9" s="55">
         <v>0</v>
@@ -15492,10 +15502,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D11" s="56">
         <f>SUM(E11:CL11)</f>
@@ -15848,10 +15858,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="57"/>
@@ -16182,10 +16192,10 @@
     </row>
     <row r="14" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B14" s="48" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D14" s="43">
         <f>SUM(E14:CL14)</f>
@@ -16533,7 +16543,7 @@
     </row>
     <row r="16" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -16627,10 +16637,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E18" s="32">
         <f>MIN(1,3)/3*E14</f>
@@ -16978,10 +16988,10 @@
     </row>
     <row r="19" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B19" s="48" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D19" s="43">
         <f>SUM(E19:CL19)</f>
@@ -17335,16 +17345,16 @@
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="38" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -17436,15 +17446,15 @@
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D25" s="58">
         <f>'입력값'!C7</f>
@@ -17453,10 +17463,10 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D26" s="59">
         <f>'입력값'!C10</f>
@@ -17465,10 +17475,10 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D27" s="60">
         <f>'입력값'!C11</f>
@@ -17477,10 +17487,10 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D28" s="60">
         <f>'입력값'!C12</f>
@@ -17489,10 +17499,10 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="34" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D29" s="60">
         <f>'입력값'!C13</f>
@@ -17501,10 +17511,10 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D30" s="61">
         <f>'입력값'!C14</f>
@@ -17538,12 +17548,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -17637,279 +17647,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(E8:CL8)</f>
@@ -18256,10 +18266,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(E9:CL9)</f>
@@ -18606,10 +18616,10 @@
     </row>
     <row r="10" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B10" s="48" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D10" s="43">
         <f>SUM(E10:CL10)</f>
@@ -18963,16 +18973,16 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="38" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -19064,15 +19074,15 @@
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D17" s="46">
         <f>'입력값'!C18</f>
@@ -19081,10 +19091,10 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D18" s="60">
         <f>'입력값'!C19</f>
@@ -19093,10 +19103,10 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D19" s="60">
         <f>'입력값'!C20</f>
@@ -19130,12 +19140,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -19229,279 +19239,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="47" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D8" s="14">
         <f>SUM(E8:CL8)</f>
@@ -19854,10 +19864,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="47" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D10" s="14">
         <f>SUM(E10:CL10)</f>
@@ -20210,10 +20220,10 @@
     </row>
     <row r="12" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B12" s="48" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D12" s="43">
         <f>SUM(E12:CL12)</f>
@@ -20567,10 +20577,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E13" s="40" t="str">
         <f>IF(E8&lt;=0,"",E12/E8)</f>
@@ -20919,10 +20929,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D15" s="32">
         <f>SUM(E15:CL15)</f>
@@ -21269,10 +21279,10 @@
     </row>
     <row r="16" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D16" s="32">
         <f>SUM(E16:CL16)</f>
@@ -21619,10 +21629,10 @@
     </row>
     <row r="17" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D17" s="32">
         <f>SUM(E17:CL17)</f>
@@ -21969,10 +21979,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D18" s="32">
         <f>SUM(E18:CL18)</f>
@@ -22319,10 +22329,10 @@
     </row>
     <row r="19" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B19" s="47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D19" s="14">
         <f>SUM(E19:CL19)</f>
@@ -22675,10 +22685,10 @@
     </row>
     <row r="20" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E20" s="40" t="str">
         <f>IF(E8&lt;=0,"",E19/E8)</f>
@@ -23027,15 +23037,15 @@
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D23" s="32">
         <f>SUM(E23:CL23)</f>
@@ -23388,10 +23398,10 @@
     </row>
     <row r="24" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D24" s="32">
         <f>SUM(E24:CL24)</f>
@@ -23744,10 +23754,10 @@
     </row>
     <row r="25" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B25" s="47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D25" s="14">
         <f>SUM(E25:CL25)</f>
@@ -24100,10 +24110,10 @@
     </row>
     <row r="27" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B27" s="47" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D27" s="14">
         <f>SUM(E27:CL27)</f>
@@ -24456,10 +24466,10 @@
     </row>
     <row r="28" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D28" s="32">
         <f>SUM(E28:CL28)</f>
@@ -24812,10 +24822,10 @@
     </row>
     <row r="29" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B29" s="48" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D29" s="43">
         <f>SUM(E29:CL29)</f>
@@ -25169,7 +25179,7 @@
     </row>
     <row r="32" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -25263,10 +25273,10 @@
     </row>
     <row r="34" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D34" s="32">
         <f>SUM(E34:CL34)</f>
@@ -25619,7 +25629,7 @@
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E36" s="13">
         <v>2024</v>
@@ -25690,10 +25700,10 @@
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E37" s="32">
         <f>E34+F34+G34</f>
@@ -25786,10 +25796,10 @@
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E38" s="32">
         <f>0</f>
@@ -25882,10 +25892,10 @@
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" s="34" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E39" s="32">
         <f>IF(E37&lt;=0,0,MIN(E38,E37*$D$63/100))</f>
@@ -25978,10 +25988,10 @@
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E40" s="32">
         <f>IF(E37&lt;=0,E38-E37,E38-E39)</f>
@@ -26074,10 +26084,10 @@
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E41" s="32">
         <f>MAX(0,E37-E39)</f>
@@ -26170,10 +26180,10 @@
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E42" s="32">
         <f>IF(E37&lt;=0,0,MIN(MAX(E41,0),200)*0.09+MIN(MAX(E41-200,0),19800)*0.19+MIN(MAX(E41-20000,0),280000)*0.21+MAX(E41-300000,0)*0.24)</f>
@@ -26266,10 +26276,10 @@
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E43" s="32">
         <f>E41*$D$64/100</f>
@@ -26362,10 +26372,10 @@
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E44" s="32">
         <f>0</f>
@@ -26458,10 +26468,10 @@
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="34" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E45" s="32">
         <f>(0)*$D$65/100</f>
@@ -26554,10 +26564,10 @@
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E46" s="32">
         <f>MAX(0,E42-(E44+E45))</f>
@@ -26650,10 +26660,10 @@
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" s="34" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E47" s="32">
         <f>IF(E37&lt;=0,0,MAX(E43,E46))</f>
@@ -26746,10 +26756,10 @@
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" s="34" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E48" s="32">
         <f>E42-E47</f>
@@ -26842,10 +26852,10 @@
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" s="34" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E49" s="32">
         <f>E44+E45-E48</f>
@@ -26938,10 +26948,10 @@
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" s="47" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E50" s="14">
         <f>E47*(1+$D$66/100)+E48*$D$67/100</f>
@@ -27034,10 +27044,10 @@
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" s="34" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E51" s="32">
         <f>MAX(0,E27)+MAX(0,F27)+MAX(0,G27)</f>
@@ -27130,16 +27140,16 @@
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="38" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -27231,15 +27241,15 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D58" s="60">
         <f>'입력값'!C15</f>
@@ -27248,10 +27258,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D59" s="62">
         <f>'입력값'!C16</f>
@@ -27260,10 +27270,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D60" s="46">
         <f>'입력값'!C17</f>
@@ -27272,10 +27282,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D61" s="46">
         <f>'입력값'!C21</f>
@@ -27284,10 +27294,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D62" s="46">
         <f>'입력값'!C22</f>
@@ -27296,10 +27306,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D63" s="60">
         <f>'입력값'!C32</f>
@@ -27308,10 +27318,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="34" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D64" s="60">
         <f>'입력값'!C33</f>
@@ -27320,10 +27330,10 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="34" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D65" s="60">
         <f>'입력값'!C34</f>
@@ -27332,10 +27342,10 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="34" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C66" s="45" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D66" s="60">
         <f>'입력값'!C35</f>
@@ -27344,10 +27354,10 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="34" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D67" s="60">
         <f>'입력값'!C36</f>
@@ -27381,12 +27391,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -27480,279 +27490,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B9" s="48" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D9" s="43">
         <f>SUM(E9:CL9)</f>
@@ -28106,10 +28116,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D10" s="32">
         <f>SUM(E10:CL10)</f>
@@ -28462,10 +28472,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -28760,10 +28770,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="47" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D13" s="14">
         <f>SUM(E13:CL13)</f>
@@ -29116,10 +29126,10 @@
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D14" s="32">
         <f>SUM(E14:CL14)</f>
@@ -29472,10 +29482,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E15" s="32">
         <f>0</f>
@@ -29824,10 +29834,10 @@
     </row>
     <row r="16" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B16" s="48" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D16" s="43">
         <f>SUM(E16:CL16)</f>
@@ -30181,362 +30191,362 @@
     </row>
     <row r="17" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E17" s="32">
-        <f>E18-E16</f>
+        <f>E18-E16+E25</f>
         <v>0</v>
       </c>
       <c r="F17" s="32">
-        <f>F18-F16</f>
+        <f>F18-F16+F25</f>
         <v>0</v>
       </c>
       <c r="G17" s="32">
-        <f>G18-G16</f>
+        <f>G18-G16+G25</f>
         <v>0</v>
       </c>
       <c r="H17" s="32">
-        <f>H18-H16</f>
+        <f>H18-H16+H25</f>
         <v>0</v>
       </c>
       <c r="I17" s="32">
-        <f>I18-I16</f>
+        <f>I18-I16+I25</f>
         <v>0</v>
       </c>
       <c r="J17" s="32">
-        <f>J18-J16</f>
+        <f>J18-J16+J25</f>
         <v>0</v>
       </c>
       <c r="K17" s="32">
-        <f>K18-K16</f>
+        <f>K18-K16+K25</f>
         <v>1601.3291924148925</v>
       </c>
       <c r="L17" s="32">
-        <f>L18-L16</f>
+        <f>L18-L16+L25</f>
         <v>3710.788256920765</v>
       </c>
       <c r="M17" s="32">
-        <f>M18-M16</f>
+        <f>M18-M16+M25</f>
         <v>3714.1379464266374</v>
       </c>
       <c r="N17" s="32">
-        <f>N18-N16</f>
+        <f>N18-N16+N25</f>
         <v>3746.780760932509</v>
       </c>
       <c r="O17" s="32">
-        <f>O18-O16</f>
+        <f>O18-O16+O25</f>
         <v>3789.6155546819596</v>
       </c>
       <c r="P17" s="32">
-        <f>P18-P16</f>
+        <f>P18-P16+P25</f>
         <v>3846.742117840529</v>
       </c>
       <c r="Q17" s="32">
-        <f>Q18-Q16</f>
+        <f>Q18-Q16+Q25</f>
         <v>3927.0559773899104</v>
       </c>
       <c r="R17" s="32">
-        <f>R18-R16</f>
+        <f>R18-R16+R25</f>
         <v>4030.5571333301045</v>
       </c>
       <c r="S17" s="32">
-        <f>S18-S16</f>
+        <f>S18-S16+S25</f>
         <v>4138.097811174028</v>
       </c>
       <c r="T17" s="32">
-        <f>T18-T16</f>
+        <f>T18-T16+T25</f>
         <v>4259.907208476275</v>
       </c>
       <c r="U17" s="32">
-        <f>U18-U16</f>
+        <f>U18-U16+U25</f>
         <v>4404.901552889836</v>
       </c>
       <c r="V17" s="32">
-        <f>V18-V16</f>
+        <f>V18-V16+V25</f>
         <v>4573.0808444147115</v>
       </c>
       <c r="W17" s="32">
-        <f>W18-W16</f>
+        <f>W18-W16+W25</f>
         <v>4745.251525536414</v>
       </c>
       <c r="X17" s="32">
-        <f>X18-X16</f>
+        <f>X18-X16+X25</f>
         <v>4931.694457134355</v>
       </c>
       <c r="Y17" s="32">
-        <f>Y18-Y16</f>
+        <f>Y18-Y16+Y25</f>
         <v>5141.3205753707425</v>
       </c>
       <c r="Z17" s="32">
-        <f>Z18-Z16</f>
+        <f>Z18-Z16+Z25</f>
         <v>5374.12988024558</v>
       </c>
       <c r="AA17" s="32">
-        <f>AA18-AA16</f>
+        <f>AA18-AA16+AA25</f>
         <v>5610.881986661196</v>
       </c>
       <c r="AB17" s="32">
-        <f>AB18-AB16</f>
+        <f>AB18-AB16+AB25</f>
         <v>5861.909048782064</v>
       </c>
       <c r="AC17" s="32">
-        <f>AC18-AC16</f>
+        <f>AC18-AC16+AC25</f>
         <v>6136.117929172212</v>
       </c>
       <c r="AD17" s="32">
-        <f>AD18-AD16</f>
+        <f>AD18-AD16+AD25</f>
         <v>6433.508627831639</v>
       </c>
       <c r="AE17" s="32">
-        <f>AE18-AE16</f>
+        <f>AE18-AE16+AE25</f>
         <v>6734.793120462703</v>
       </c>
       <c r="AF17" s="32">
-        <f>AF18-AF16</f>
+        <f>AF18-AF16+AF25</f>
         <v>7050.354708350055</v>
       </c>
       <c r="AG17" s="32">
-        <f>AG18-AG16</f>
+        <f>AG18-AG16+AG25</f>
         <v>7389.097020376081</v>
       </c>
       <c r="AH17" s="32">
-        <f>AH18-AH16</f>
+        <f>AH18-AH16+AH25</f>
         <v>7751.0200565407795</v>
       </c>
       <c r="AI17" s="32">
-        <f>AI18-AI16</f>
+        <f>AI18-AI16+AI25</f>
         <v>8116.78748033666</v>
       </c>
       <c r="AJ17" s="32">
-        <f>AJ18-AJ16</f>
+        <f>AJ18-AJ16+AJ25</f>
         <v>8496.833734288071</v>
       </c>
       <c r="AK17" s="32">
-        <f>AK18-AK16</f>
+        <f>AK18-AK16+AK25</f>
         <v>8900.05981755857</v>
       </c>
       <c r="AL17" s="32">
-        <f>AL18-AL16</f>
+        <f>AL18-AL16+AL25</f>
         <v>9326.465730148157</v>
       </c>
       <c r="AM17" s="32">
-        <f>AM18-AM16</f>
+        <f>AM18-AM16+AM25</f>
         <v>9756.666237552567</v>
       </c>
       <c r="AN17" s="32">
-        <f>AN18-AN16</f>
+        <f>AN18-AN16+AN25</f>
         <v>10201.147010461404</v>
       </c>
       <c r="AO17" s="32">
-        <f>AO18-AO16</f>
+        <f>AO18-AO16+AO25</f>
         <v>10668.806867270494</v>
       </c>
       <c r="AP17" s="32">
-        <f>AP18-AP16</f>
+        <f>AP18-AP16+AP25</f>
         <v>11159.64580797984</v>
       </c>
       <c r="AQ17" s="32">
-        <f>AQ18-AQ16</f>
+        <f>AQ18-AQ16+AQ25</f>
         <v>11654.229171578805</v>
       </c>
       <c r="AR17" s="32">
-        <f>AR18-AR16</f>
+        <f>AR18-AR16+AR25</f>
         <v>12163.094008032082</v>
       </c>
       <c r="AS17" s="32">
-        <f>AS18-AS16</f>
+        <f>AS18-AS16+AS25</f>
         <v>12695.137297837768</v>
       </c>
       <c r="AT17" s="32">
-        <f>AT18-AT16</f>
+        <f>AT18-AT16+AT25</f>
         <v>13250.359040995862</v>
       </c>
       <c r="AU17" s="32">
-        <f>AU18-AU16</f>
+        <f>AU18-AU16+AU25</f>
         <v>13809.274660340036</v>
       </c>
       <c r="AV17" s="32">
-        <f>AV18-AV16</f>
+        <f>AV18-AV16+AV25</f>
         <v>14382.472782305313</v>
       </c>
       <c r="AW17" s="32">
-        <f>AW18-AW16</f>
+        <f>AW18-AW16+AW25</f>
         <v>14978.848817296046</v>
       </c>
       <c r="AX17" s="32">
-        <f>AX18-AX16</f>
+        <f>AX18-AX16+AX25</f>
         <v>15598.402765312236</v>
       </c>
       <c r="AY17" s="32">
-        <f>AY18-AY16</f>
+        <f>AY18-AY16+AY25</f>
         <v>16221.599670406398</v>
       </c>
       <c r="AZ17" s="32">
-        <f>AZ18-AZ16</f>
+        <f>AZ18-AZ16+AZ25</f>
         <v>16859.079966861675</v>
       </c>
       <c r="BA17" s="32">
-        <f>BA18-BA16</f>
+        <f>BA18-BA16+BA25</f>
         <v>17519.73770816833</v>
       </c>
       <c r="BB17" s="32">
-        <f>BB18-BB16</f>
+        <f>BB18-BB16+BB25</f>
         <v>18203.572894326368</v>
       </c>
       <c r="BC17" s="32">
-        <f>BC18-BC16</f>
+        <f>BC18-BC16+BC25</f>
         <v>18890.999747114016</v>
       </c>
       <c r="BD17" s="32">
-        <f>BD18-BD16</f>
+        <f>BD18-BD16+BD25</f>
         <v>19592.71076613362</v>
       </c>
       <c r="BE17" s="32">
-        <f>BE18-BE16</f>
+        <f>BE18-BE16+BE25</f>
         <v>20317.598820438005</v>
       </c>
       <c r="BF17" s="32">
-        <f>BF18-BF16</f>
+        <f>BF18-BF16+BF25</f>
         <v>21065.663910027175</v>
       </c>
       <c r="BG17" s="32">
-        <f>BG18-BG16</f>
+        <f>BG18-BG16+BG25</f>
         <v>21817.269004616366</v>
       </c>
       <c r="BH17" s="32">
-        <f>BH18-BH16</f>
+        <f>BH18-BH16+BH25</f>
         <v>22583.158947038763</v>
       </c>
       <c r="BI17" s="32">
-        <f>BI18-BI16</f>
+        <f>BI18-BI16+BI25</f>
         <v>23372.22556343231</v>
       </c>
       <c r="BJ17" s="32">
-        <f>BJ18-BJ16</f>
+        <f>BJ18-BJ16+BJ25</f>
         <v>24184.468853797003</v>
       </c>
       <c r="BK17" s="32">
-        <f>BK18-BK16</f>
+        <f>BK18-BK16+BK25</f>
         <v>25000.200115866006</v>
       </c>
       <c r="BL17" s="32">
-        <f>BL18-BL16</f>
+        <f>BL18-BL16+BL25</f>
         <v>1000</v>
       </c>
       <c r="BM17" s="32">
-        <f>BM18-BM16</f>
+        <f>BM18-BM16+BM25</f>
         <v>1000</v>
       </c>
       <c r="BN17" s="32">
-        <f>BN18-BN16</f>
+        <f>BN18-BN16+BN25</f>
         <v>1000</v>
       </c>
       <c r="BO17" s="32">
-        <f>BO18-BO16</f>
+        <f>BO18-BO16+BO25</f>
         <v>1000</v>
       </c>
       <c r="BP17" s="32">
-        <f>BP18-BP16</f>
+        <f>BP18-BP16+BP25</f>
         <v>1000</v>
       </c>
       <c r="BQ17" s="32">
-        <f>BQ18-BQ16</f>
+        <f>BQ18-BQ16+BQ25</f>
         <v>1000</v>
       </c>
       <c r="BR17" s="32">
-        <f>BR18-BR16</f>
+        <f>BR18-BR16+BR25</f>
         <v>1000</v>
       </c>
       <c r="BS17" s="32">
-        <f>BS18-BS16</f>
+        <f>BS18-BS16+BS25</f>
         <v>1000</v>
       </c>
       <c r="BT17" s="32">
-        <f>BT18-BT16</f>
+        <f>BT18-BT16+BT25</f>
         <v>1000</v>
       </c>
       <c r="BU17" s="32">
-        <f>BU18-BU16</f>
+        <f>BU18-BU16+BU25</f>
         <v>1000</v>
       </c>
       <c r="BV17" s="32">
-        <f>BV18-BV16</f>
+        <f>BV18-BV16+BV25</f>
         <v>1000</v>
       </c>
       <c r="BW17" s="32">
-        <f>BW18-BW16</f>
+        <f>BW18-BW16+BW25</f>
         <v>1000</v>
       </c>
       <c r="BX17" s="32">
-        <f>BX18-BX16</f>
+        <f>BX18-BX16+BX25</f>
         <v>1000</v>
       </c>
       <c r="BY17" s="32">
-        <f>BY18-BY16</f>
+        <f>BY18-BY16+BY25</f>
         <v>1000</v>
       </c>
       <c r="BZ17" s="32">
-        <f>BZ18-BZ16</f>
+        <f>BZ18-BZ16+BZ25</f>
         <v>1000</v>
       </c>
       <c r="CA17" s="32">
-        <f>CA18-CA16</f>
+        <f>CA18-CA16+CA25</f>
         <v>1000</v>
       </c>
       <c r="CB17" s="32">
-        <f>CB18-CB16</f>
+        <f>CB18-CB16+CB25</f>
         <v>1000</v>
       </c>
       <c r="CC17" s="32">
-        <f>CC18-CC16</f>
+        <f>CC18-CC16+CC25</f>
         <v>1000</v>
       </c>
       <c r="CD17" s="32">
-        <f>CD18-CD16</f>
+        <f>CD18-CD16+CD25</f>
         <v>1000</v>
       </c>
       <c r="CE17" s="32">
-        <f>CE18-CE16</f>
+        <f>CE18-CE16+CE25</f>
         <v>1000</v>
       </c>
       <c r="CF17" s="32">
-        <f>CF18-CF16</f>
+        <f>CF18-CF16+CF25</f>
         <v>1000</v>
       </c>
       <c r="CG17" s="32">
-        <f>CG18-CG16</f>
+        <f>CG18-CG16+CG25</f>
         <v>1000</v>
       </c>
       <c r="CH17" s="32">
-        <f>CH18-CH16</f>
+        <f>CH18-CH16+CH25</f>
         <v>1000</v>
       </c>
       <c r="CI17" s="32">
-        <f>CI18-CI16</f>
+        <f>CI18-CI16+CI25</f>
         <v>1000</v>
       </c>
       <c r="CJ17" s="32">
-        <f>CJ18-CJ16</f>
+        <f>CJ18-CJ16+CJ25</f>
         <v>1000</v>
       </c>
       <c r="CK17" s="32">
-        <f>CK18-CK16</f>
+        <f>CK18-CK16+CK25</f>
         <v>1000</v>
       </c>
       <c r="CL17" s="32">
-        <f>CL18-CL16</f>
+        <f>CL18-CL16+CL25</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E18" s="32">
         <f>E15+E13</f>
@@ -30885,10 +30895,10 @@
     </row>
     <row r="19" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E19" s="32">
         <v>0</v>
@@ -31151,10 +31161,10 @@
     </row>
     <row r="20" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E20" s="32">
         <f>0</f>
@@ -31503,10 +31513,10 @@
     </row>
     <row r="21" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E21" s="32">
         <f>E20</f>
@@ -31855,10 +31865,10 @@
     </row>
     <row r="22" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E22" s="32">
         <f>0</f>
@@ -32207,10 +32217,10 @@
     </row>
     <row r="23" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E23" s="32">
         <f>0</f>
@@ -32559,10 +32569,10 @@
     </row>
     <row r="24" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="64">
@@ -32911,9 +32921,366 @@
       </c>
       <c r="CM24" s="10"/>
     </row>
+    <row r="25" spans="2:91" x14ac:dyDescent="0.25">
+      <c r="B25" s="48" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="D25" s="43">
+        <f>SUM(E25:CL25)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="65">
+        <f>MAX(0,-(E18-E16))</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="65">
+        <f>MAX(0,-(F18-F16))</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="65">
+        <f>MAX(0,-(G18-G16))</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="65">
+        <f>MAX(0,-(H18-H16))</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="65">
+        <f>MAX(0,-(I18-I16))</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="65">
+        <f>MAX(0,-(J18-J16))</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="65">
+        <f>MAX(0,-(K18-K16))</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="65">
+        <f>MAX(0,-(L18-L16))</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="65">
+        <f>MAX(0,-(M18-M16))</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="65">
+        <f>MAX(0,-(N18-N16))</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="65">
+        <f>MAX(0,-(O18-O16))</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="65">
+        <f>MAX(0,-(P18-P16))</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="65">
+        <f>MAX(0,-(Q18-Q16))</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="65">
+        <f>MAX(0,-(R18-R16))</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="65">
+        <f>MAX(0,-(S18-S16))</f>
+        <v>0</v>
+      </c>
+      <c r="T25" s="65">
+        <f>MAX(0,-(T18-T16))</f>
+        <v>0</v>
+      </c>
+      <c r="U25" s="65">
+        <f>MAX(0,-(U18-U16))</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="65">
+        <f>MAX(0,-(V18-V16))</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="65">
+        <f>MAX(0,-(W18-W16))</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="65">
+        <f>MAX(0,-(X18-X16))</f>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="65">
+        <f>MAX(0,-(Y18-Y16))</f>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="65">
+        <f>MAX(0,-(Z18-Z16))</f>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="65">
+        <f>MAX(0,-(AA18-AA16))</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="65">
+        <f>MAX(0,-(AB18-AB16))</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="65">
+        <f>MAX(0,-(AC18-AC16))</f>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="65">
+        <f>MAX(0,-(AD18-AD16))</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="65">
+        <f>MAX(0,-(AE18-AE16))</f>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="65">
+        <f>MAX(0,-(AF18-AF16))</f>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="65">
+        <f>MAX(0,-(AG18-AG16))</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="65">
+        <f>MAX(0,-(AH18-AH16))</f>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="65">
+        <f>MAX(0,-(AI18-AI16))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="65">
+        <f>MAX(0,-(AJ18-AJ16))</f>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="65">
+        <f>MAX(0,-(AK18-AK16))</f>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="65">
+        <f>MAX(0,-(AL18-AL16))</f>
+        <v>0</v>
+      </c>
+      <c r="AM25" s="65">
+        <f>MAX(0,-(AM18-AM16))</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="65">
+        <f>MAX(0,-(AN18-AN16))</f>
+        <v>0</v>
+      </c>
+      <c r="AO25" s="65">
+        <f>MAX(0,-(AO18-AO16))</f>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="65">
+        <f>MAX(0,-(AP18-AP16))</f>
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="65">
+        <f>MAX(0,-(AQ18-AQ16))</f>
+        <v>0</v>
+      </c>
+      <c r="AR25" s="65">
+        <f>MAX(0,-(AR18-AR16))</f>
+        <v>0</v>
+      </c>
+      <c r="AS25" s="65">
+        <f>MAX(0,-(AS18-AS16))</f>
+        <v>0</v>
+      </c>
+      <c r="AT25" s="65">
+        <f>MAX(0,-(AT18-AT16))</f>
+        <v>0</v>
+      </c>
+      <c r="AU25" s="65">
+        <f>MAX(0,-(AU18-AU16))</f>
+        <v>0</v>
+      </c>
+      <c r="AV25" s="65">
+        <f>MAX(0,-(AV18-AV16))</f>
+        <v>0</v>
+      </c>
+      <c r="AW25" s="65">
+        <f>MAX(0,-(AW18-AW16))</f>
+        <v>0</v>
+      </c>
+      <c r="AX25" s="65">
+        <f>MAX(0,-(AX18-AX16))</f>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="65">
+        <f>MAX(0,-(AY18-AY16))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ25" s="65">
+        <f>MAX(0,-(AZ18-AZ16))</f>
+        <v>0</v>
+      </c>
+      <c r="BA25" s="65">
+        <f>MAX(0,-(BA18-BA16))</f>
+        <v>0</v>
+      </c>
+      <c r="BB25" s="65">
+        <f>MAX(0,-(BB18-BB16))</f>
+        <v>0</v>
+      </c>
+      <c r="BC25" s="65">
+        <f>MAX(0,-(BC18-BC16))</f>
+        <v>0</v>
+      </c>
+      <c r="BD25" s="65">
+        <f>MAX(0,-(BD18-BD16))</f>
+        <v>0</v>
+      </c>
+      <c r="BE25" s="65">
+        <f>MAX(0,-(BE18-BE16))</f>
+        <v>0</v>
+      </c>
+      <c r="BF25" s="65">
+        <f>MAX(0,-(BF18-BF16))</f>
+        <v>0</v>
+      </c>
+      <c r="BG25" s="65">
+        <f>MAX(0,-(BG18-BG16))</f>
+        <v>0</v>
+      </c>
+      <c r="BH25" s="65">
+        <f>MAX(0,-(BH18-BH16))</f>
+        <v>0</v>
+      </c>
+      <c r="BI25" s="65">
+        <f>MAX(0,-(BI18-BI16))</f>
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="65">
+        <f>MAX(0,-(BJ18-BJ16))</f>
+        <v>0</v>
+      </c>
+      <c r="BK25" s="65">
+        <f>MAX(0,-(BK18-BK16))</f>
+        <v>0</v>
+      </c>
+      <c r="BL25" s="65">
+        <f>MAX(0,-(BL18-BL16))</f>
+        <v>0</v>
+      </c>
+      <c r="BM25" s="65">
+        <f>MAX(0,-(BM18-BM16))</f>
+        <v>0</v>
+      </c>
+      <c r="BN25" s="65">
+        <f>MAX(0,-(BN18-BN16))</f>
+        <v>0</v>
+      </c>
+      <c r="BO25" s="65">
+        <f>MAX(0,-(BO18-BO16))</f>
+        <v>0</v>
+      </c>
+      <c r="BP25" s="65">
+        <f>MAX(0,-(BP18-BP16))</f>
+        <v>0</v>
+      </c>
+      <c r="BQ25" s="65">
+        <f>MAX(0,-(BQ18-BQ16))</f>
+        <v>0</v>
+      </c>
+      <c r="BR25" s="65">
+        <f>MAX(0,-(BR18-BR16))</f>
+        <v>0</v>
+      </c>
+      <c r="BS25" s="65">
+        <f>MAX(0,-(BS18-BS16))</f>
+        <v>0</v>
+      </c>
+      <c r="BT25" s="65">
+        <f>MAX(0,-(BT18-BT16))</f>
+        <v>0</v>
+      </c>
+      <c r="BU25" s="65">
+        <f>MAX(0,-(BU18-BU16))</f>
+        <v>0</v>
+      </c>
+      <c r="BV25" s="65">
+        <f>MAX(0,-(BV18-BV16))</f>
+        <v>0</v>
+      </c>
+      <c r="BW25" s="65">
+        <f>MAX(0,-(BW18-BW16))</f>
+        <v>0</v>
+      </c>
+      <c r="BX25" s="65">
+        <f>MAX(0,-(BX18-BX16))</f>
+        <v>0</v>
+      </c>
+      <c r="BY25" s="65">
+        <f>MAX(0,-(BY18-BY16))</f>
+        <v>0</v>
+      </c>
+      <c r="BZ25" s="65">
+        <f>MAX(0,-(BZ18-BZ16))</f>
+        <v>0</v>
+      </c>
+      <c r="CA25" s="65">
+        <f>MAX(0,-(CA18-CA16))</f>
+        <v>0</v>
+      </c>
+      <c r="CB25" s="65">
+        <f>MAX(0,-(CB18-CB16))</f>
+        <v>0</v>
+      </c>
+      <c r="CC25" s="65">
+        <f>MAX(0,-(CC18-CC16))</f>
+        <v>0</v>
+      </c>
+      <c r="CD25" s="65">
+        <f>MAX(0,-(CD18-CD16))</f>
+        <v>0</v>
+      </c>
+      <c r="CE25" s="65">
+        <f>MAX(0,-(CE18-CE16))</f>
+        <v>0</v>
+      </c>
+      <c r="CF25" s="65">
+        <f>MAX(0,-(CF18-CF16))</f>
+        <v>0</v>
+      </c>
+      <c r="CG25" s="65">
+        <f>MAX(0,-(CG18-CG16))</f>
+        <v>0</v>
+      </c>
+      <c r="CH25" s="65">
+        <f>MAX(0,-(CH18-CH16))</f>
+        <v>0</v>
+      </c>
+      <c r="CI25" s="65">
+        <f>MAX(0,-(CI18-CI16))</f>
+        <v>0</v>
+      </c>
+      <c r="CJ25" s="65">
+        <f>MAX(0,-(CJ18-CJ16))</f>
+        <v>0</v>
+      </c>
+      <c r="CK25" s="65">
+        <f>MAX(0,-(CK18-CK16))</f>
+        <v>0</v>
+      </c>
+      <c r="CL25" s="65">
+        <f>MAX(0,-(CL18-CL16))</f>
+        <v>0</v>
+      </c>
+      <c r="CM25" s="49"/>
+    </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E26" s="13">
         <v>2025</v>
@@ -32972,10 +33339,10 @@
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E27" s="32">
         <f>K10</f>
@@ -33052,10 +33419,10 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E28" s="32">
         <f>K9</f>
@@ -33132,271 +33499,271 @@
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" s="34" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="E29" s="65">
+        <v>363</v>
+      </c>
+      <c r="E29" s="66">
         <f>IF(E27=0,"",E28/E27)</f>
         <v>1.187143523658971</v>
       </c>
-      <c r="F29" s="65">
+      <c r="F29" s="66">
         <f>IF(F27=0,"",F28/F27)</f>
         <v>1.6572126565462255</v>
       </c>
-      <c r="G29" s="65">
+      <c r="G29" s="66">
         <f>IF(G27=0,"",G28/G27)</f>
         <v>1.0073021924292676</v>
       </c>
-      <c r="H29" s="65">
+      <c r="H29" s="66">
         <f>IF(H27=0,"",H28/H27)</f>
         <v>1.0245885931257517</v>
       </c>
-      <c r="I29" s="65">
+      <c r="I29" s="66">
         <f>IF(I27=0,"",I28/I27)</f>
         <v>1.0429645625989417</v>
       </c>
-      <c r="J29" s="65">
+      <c r="J29" s="66">
         <f>IF(J27=0,"",J28/J27)</f>
         <v>1.0625377074113014</v>
       </c>
-      <c r="K29" s="65">
+      <c r="K29" s="66">
         <f>IF(K27=0,"",K28/K27)</f>
         <v>1.083430299004098</v>
       </c>
-      <c r="L29" s="65">
+      <c r="L29" s="66">
         <f>IF(L27=0,"",L28/L27)</f>
         <v>1.1057818601423848</v>
       </c>
-      <c r="M29" s="65">
+      <c r="M29" s="66">
         <f>IF(M27=0,"",M28/M27)</f>
         <v>1.129752318781926</v>
       </c>
-      <c r="N29" s="65">
+      <c r="N29" s="66">
         <f>IF(N27=0,"",N28/N27)</f>
         <v>1.1555258800995714</v>
       </c>
-      <c r="O29" s="65">
+      <c r="O29" s="66">
         <f>IF(O27=0,"",O28/O27)</f>
         <v>1.183315815000944</v>
       </c>
-      <c r="P29" s="65">
+      <c r="P29" s="66">
         <f>IF(P27=0,"",P28/P27)</f>
         <v>1.2133704285752722</v>
       </c>
-      <c r="Q29" s="65">
+      <c r="Q29" s="66">
         <f>IF(Q27=0,"",Q28/Q27)</f>
         <v>1.2459805622374127</v>
       </c>
-      <c r="R29" s="65">
+      <c r="R29" s="66">
         <f>IF(R27=0,"",R28/R27)</f>
         <v>1.2814891099186823</v>
       </c>
-      <c r="S29" s="65">
+      <c r="S29" s="66">
         <f>IF(S27=0,"",S28/S27)</f>
         <v>1.320303208667883</v>
       </c>
-      <c r="T29" s="65">
+      <c r="T29" s="66">
         <f>IF(T27=0,"",T28/T27)</f>
         <v>1.362910023632631</v>
       </c>
-      <c r="U29" s="65">
+      <c r="U29" s="66">
         <f>IF(U27=0,"",U28/U27)</f>
         <v>1.409897427751645</v>
       </c>
-      <c r="V29" s="65">
+      <c r="V29" s="66">
         <f>IF(V27=0,"",V28/V27)</f>
         <v>1.4558007324858961</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="E30" s="65">
+        <v>363</v>
+      </c>
+      <c r="E30" s="66">
         <f>IF(E27=0,"",(H15+H20+E28)/E27)</f>
         <v>1.187143523658971</v>
       </c>
-      <c r="F30" s="65">
+      <c r="F30" s="66">
         <f>IF(F27=0,"",(L15+L20+F28)/F27)</f>
         <v>2.214293966113563</v>
       </c>
-      <c r="G30" s="65">
+      <c r="G30" s="66">
         <f>IF(G27=0,"",(P15+P20+G28)/G27)</f>
         <v>1.7534997176553586</v>
       </c>
-      <c r="H30" s="65">
+      <c r="H30" s="66">
         <f>IF(H27=0,"",(T15+T20+H28)/H27)</f>
         <v>1.8013808270037128</v>
       </c>
-      <c r="I30" s="65">
+      <c r="I30" s="66">
         <f>IF(I27=0,"",(X15+X20+I28)/I27)</f>
         <v>1.8699082378967293</v>
       </c>
-      <c r="J30" s="65">
+      <c r="J30" s="66">
         <f>IF(J27=0,"",(AB15+AB20+J28)/J27)</f>
         <v>1.9611090246969691</v>
       </c>
-      <c r="K30" s="65">
+      <c r="K30" s="66">
         <f>IF(K27=0,"",(AF15+AF20+K28)/K27)</f>
         <v>2.077286429580618</v>
       </c>
-      <c r="L30" s="65">
+      <c r="L30" s="66">
         <f>IF(L27=0,"",(AJ15+AJ20+L28)/L27)</f>
         <v>2.2210685696321772</v>
       </c>
-      <c r="M30" s="65">
+      <c r="M30" s="66">
         <f>IF(M27=0,"",(AN15+AN20+M28)/M27)</f>
         <v>2.3954678294408716</v>
       </c>
-      <c r="N30" s="65">
+      <c r="N30" s="66">
         <f>IF(N27=0,"",(AR15+AR20+N28)/N27)</f>
         <v>2.603953777912916</v>
       </c>
-      <c r="O30" s="65">
+      <c r="O30" s="66">
         <f>IF(O27=0,"",(AV15+AV20+O28)/O27)</f>
         <v>2.850543343880449</v>
       </c>
-      <c r="P30" s="65">
+      <c r="P30" s="66">
         <f>IF(P27=0,"",(AZ15+AZ20+P28)/P27)</f>
         <v>3.13991321208346</v>
       </c>
-      <c r="Q30" s="65">
+      <c r="Q30" s="66">
         <f>IF(Q27=0,"",(BD15+BD20+Q28)/Q27)</f>
         <v>3.4775411010399186</v>
       </c>
-      <c r="R30" s="65">
+      <c r="R30" s="66">
         <f>IF(R27=0,"",(BH15+BH20+R28)/R27)</f>
         <v>3.8698849688146435</v>
       </c>
-      <c r="S30" s="65">
+      <c r="S30" s="66">
         <f>IF(S27=0,"",(BL15+BL20+S28)/S27)</f>
         <v>4.324612582393173</v>
       </c>
-      <c r="T30" s="65">
+      <c r="T30" s="66">
         <f>IF(T27=0,"",(BP15+BP20+T28)/T27)</f>
         <v>1.9739011415280188</v>
       </c>
-      <c r="U30" s="65">
+      <c r="U30" s="66">
         <f>IF(U27=0,"",(BT15+BT20+U28)/U27)</f>
         <v>2.0266246884998984</v>
       </c>
-      <c r="V30" s="65">
+      <c r="V30" s="66">
         <f>IF(V27=0,"",(BX15+BX20+V28)/V27)</f>
         <v>2.2809643741410595</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="34" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="34" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="34" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="34" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -33490,10 +33857,10 @@
     </row>
     <row r="46" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E46" s="32">
         <f>0</f>
@@ -33842,10 +34209,10 @@
     </row>
     <row r="47" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B47" s="47" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D47" s="17">
         <f>MIN(E29:V29)</f>
@@ -34198,348 +34565,348 @@
     </row>
     <row r="48" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B48" s="47" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D48" s="17">
         <f>MIN(E30:V30)</f>
         <v>1.187143523658971</v>
       </c>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="65"/>
-      <c r="K48" s="65">
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="66"/>
+      <c r="K48" s="66">
         <f>IF(K47&gt;0,K46/K47,"")</f>
         <v>1.187143523658971</v>
       </c>
-      <c r="L48" s="65">
+      <c r="L48" s="66">
         <f>IF(L47&gt;0,L46/L47,"")</f>
         <v>1.6561661911180003</v>
       </c>
-      <c r="M48" s="65">
+      <c r="M48" s="66">
         <f>IF(M47&gt;0,M46/M47,"")</f>
         <v>1.8125070802710104</v>
       </c>
-      <c r="N48" s="65">
+      <c r="N48" s="66">
         <f>IF(N47&gt;0,N46/N47,"")</f>
         <v>1.8906775248475154</v>
       </c>
-      <c r="O48" s="65">
+      <c r="O48" s="66">
         <f>IF(O47&gt;0,O46/O47,"")</f>
         <v>1.5804466491863713</v>
       </c>
-      <c r="P48" s="65">
+      <c r="P48" s="66">
         <f>IF(P47&gt;0,P46/P47,"")</f>
         <v>1.431715740450008</v>
       </c>
-      <c r="Q48" s="65">
+      <c r="Q48" s="66">
         <f>IF(Q47&gt;0,Q46/Q47,"")</f>
         <v>1.3453458051879383</v>
       </c>
-      <c r="R48" s="65">
+      <c r="R48" s="66">
         <f>IF(R47&gt;0,R46/R47,"")</f>
         <v>1.2894449858877683</v>
       </c>
-      <c r="S48" s="65">
+      <c r="S48" s="66">
         <f>IF(S47&gt;0,S46/S47,"")</f>
         <v>1.2499999365530408</v>
       </c>
-      <c r="T48" s="65">
+      <c r="T48" s="66">
         <f>IF(T47&gt;0,T46/T47,"")</f>
         <v>1.2210653230178483</v>
       </c>
-      <c r="U48" s="65">
+      <c r="U48" s="66">
         <f>IF(U47&gt;0,U46/U47,"")</f>
         <v>1.1993453067122024</v>
       </c>
-      <c r="V48" s="65">
+      <c r="V48" s="66">
         <f>IF(V47&gt;0,V46/V47,"")</f>
         <v>1.1826526315500938</v>
       </c>
-      <c r="W48" s="65">
+      <c r="W48" s="66">
         <f>IF(W47&gt;0,W46/W47,"")</f>
         <v>1.1691514039184878</v>
       </c>
-      <c r="X48" s="65">
+      <c r="X48" s="66">
         <f>IF(X47&gt;0,X46/X47,"")</f>
         <v>1.1582594017590462</v>
       </c>
-      <c r="Y48" s="65">
+      <c r="Y48" s="66">
         <f>IF(Y47&gt;0,Y46/Y47,"")</f>
         <v>1.1495510090977237</v>
       </c>
-      <c r="Z48" s="65">
+      <c r="Z48" s="66">
         <f>IF(Z47&gt;0,Z46/Z47,"")</f>
         <v>1.1425589190637102</v>
       </c>
-      <c r="AA48" s="65">
+      <c r="AA48" s="66">
         <f>IF(AA47&gt;0,AA46/AA47,"")</f>
         <v>1.1366038979710784</v>
       </c>
-      <c r="AB48" s="65">
+      <c r="AB48" s="66">
         <f>IF(AB47&gt;0,AB46/AB47,"")</f>
         <v>1.1316614626935406</v>
       </c>
-      <c r="AC48" s="65">
+      <c r="AC48" s="66">
         <f>IF(AC47&gt;0,AC46/AC47,"")</f>
         <v>1.1276932015869205</v>
       </c>
-      <c r="AD48" s="65">
+      <c r="AD48" s="66">
         <f>IF(AD47&gt;0,AD46/AD47,"")</f>
         <v>1.1245397658659972</v>
       </c>
-      <c r="AE48" s="65">
+      <c r="AE48" s="66">
         <f>IF(AE47&gt;0,AE46/AE47,"")</f>
         <v>1.1218047205057322</v>
       </c>
-      <c r="AF48" s="65">
+      <c r="AF48" s="66">
         <f>IF(AF47&gt;0,AF46/AF47,"")</f>
         <v>1.1195648613153326</v>
       </c>
-      <c r="AG48" s="65">
+      <c r="AG48" s="66">
         <f>IF(AG47&gt;0,AG46/AG47,"")</f>
         <v>1.1178654067948686</v>
       </c>
-      <c r="AH48" s="65">
+      <c r="AH48" s="66">
         <f>IF(AH47&gt;0,AH46/AH47,"")</f>
         <v>1.1166358687918094</v>
       </c>
-      <c r="AI48" s="65">
+      <c r="AI48" s="66">
         <f>IF(AI47&gt;0,AI46/AI47,"")</f>
         <v>1.1155905144047553</v>
       </c>
-      <c r="AJ48" s="65">
+      <c r="AJ48" s="66">
         <f>IF(AJ47&gt;0,AJ46/AJ47,"")</f>
         <v>1.1148252164009056</v>
       </c>
-      <c r="AK48" s="65">
+      <c r="AK48" s="66">
         <f>IF(AK47&gt;0,AK46/AK47,"")</f>
         <v>1.114405507957043</v>
       </c>
-      <c r="AL48" s="65">
+      <c r="AL48" s="66">
         <f>IF(AL47&gt;0,AL46/AL47,"")</f>
         <v>1.1142945718436283</v>
       </c>
-      <c r="AM48" s="65">
+      <c r="AM48" s="66">
         <f>IF(AM47&gt;0,AM46/AM47,"")</f>
         <v>1.1142637835740765</v>
       </c>
-      <c r="AN48" s="65">
+      <c r="AN48" s="66">
         <f>IF(AN47&gt;0,AN46/AN47,"")</f>
         <v>1.114408676251522</v>
       </c>
-      <c r="AO48" s="65">
+      <c r="AO48" s="66">
         <f>IF(AO47&gt;0,AO46/AO47,"")</f>
         <v>1.1147980119390213</v>
       </c>
-      <c r="AP48" s="65">
+      <c r="AP48" s="66">
         <f>IF(AP47&gt;0,AP46/AP47,"")</f>
         <v>1.115410226626987</v>
       </c>
-      <c r="AQ48" s="65">
+      <c r="AQ48" s="66">
         <f>IF(AQ47&gt;0,AQ46/AQ47,"")</f>
         <v>1.116051591895035</v>
       </c>
-      <c r="AR48" s="65">
+      <c r="AR48" s="66">
         <f>IF(AR47&gt;0,AR46/AR47,"")</f>
         <v>1.116812463071292</v>
       </c>
-      <c r="AS48" s="65">
+      <c r="AS48" s="66">
         <f>IF(AS47&gt;0,AS46/AS47,"")</f>
         <v>1.1177596962334726</v>
       </c>
-      <c r="AT48" s="65">
+      <c r="AT48" s="66">
         <f>IF(AT47&gt;0,AT46/AT47,"")</f>
         <v>1.11887957320801</v>
       </c>
-      <c r="AU48" s="65">
+      <c r="AU48" s="66">
         <f>IF(AU47&gt;0,AU46/AU47,"")</f>
         <v>1.1200020981225862</v>
       </c>
-      <c r="AV48" s="65">
+      <c r="AV48" s="66">
         <f>IF(AV47&gt;0,AV46/AV47,"")</f>
         <v>1.1212116208024905</v>
       </c>
-      <c r="AW48" s="65">
+      <c r="AW48" s="66">
         <f>IF(AW47&gt;0,AW46/AW47,"")</f>
         <v>1.1225716266708885</v>
       </c>
-      <c r="AX48" s="65">
+      <c r="AX48" s="66">
         <f>IF(AX47&gt;0,AX46/AX47,"")</f>
         <v>1.1240728375701872</v>
       </c>
-      <c r="AY48" s="65">
+      <c r="AY48" s="66">
         <f>IF(AY47&gt;0,AY46/AY47,"")</f>
         <v>1.1255625718895965</v>
       </c>
-      <c r="AZ48" s="65">
+      <c r="AZ48" s="66">
         <f>IF(AZ47&gt;0,AZ46/AZ47,"")</f>
         <v>1.1271195109250776</v>
       </c>
-      <c r="BA48" s="65">
+      <c r="BA48" s="66">
         <f>IF(BA47&gt;0,BA46/BA47,"")</f>
         <v>1.1288035411748498</v>
       </c>
-      <c r="BB48" s="65">
+      <c r="BB48" s="66">
         <f>IF(BB47&gt;0,BB46/BB47,"")</f>
         <v>1.1306080921318415</v>
       </c>
-      <c r="BC48" s="65">
+      <c r="BC48" s="66">
         <f>IF(BC47&gt;0,BC46/BC47,"")</f>
         <v>1.1323937346304598</v>
       </c>
-      <c r="BD48" s="65">
+      <c r="BD48" s="66">
         <f>IF(BD47&gt;0,BD46/BD47,"")</f>
         <v>1.134234118655096</v>
       </c>
-      <c r="BE48" s="65">
+      <c r="BE48" s="66">
         <f>IF(BE47&gt;0,BE46/BE47,"")</f>
         <v>1.1361857270182436</v>
       </c>
-      <c r="BF48" s="65">
+      <c r="BF48" s="66">
         <f>IF(BF47&gt;0,BF46/BF47,"")</f>
         <v>1.138243743326328</v>
       </c>
-      <c r="BG48" s="65">
+      <c r="BG48" s="66">
         <f>IF(BG47&gt;0,BG46/BG47,"")</f>
         <v>1.1402792337571965</v>
       </c>
-      <c r="BH48" s="65">
+      <c r="BH48" s="66">
         <f>IF(BH47&gt;0,BH46/BH47,"")</f>
         <v>1.142361478365299</v>
       </c>
-      <c r="BI48" s="65">
+      <c r="BI48" s="66">
         <f>IF(BI47&gt;0,BI46/BI47,"")</f>
         <v>1.144543881208073</v>
       </c>
-      <c r="BJ48" s="65">
+      <c r="BJ48" s="66">
         <f>IF(BJ47&gt;0,BJ46/BJ47,"")</f>
         <v>1.1468228208987932</v>
       </c>
-      <c r="BK48" s="65">
+      <c r="BK48" s="66">
         <f>IF(BK47&gt;0,BK46/BK47,"")</f>
         <v>1.1490778866886036</v>
       </c>
-      <c r="BL48" s="65">
+      <c r="BL48" s="66">
         <f>IF(BL47&gt;0,BL46/BL47,"")</f>
         <v>1.1513745899361703</v>
       </c>
-      <c r="BM48" s="65">
+      <c r="BM48" s="66">
         <f>IF(BM47&gt;0,BM46/BM47,"")</f>
         <v>1.1537636006946481</v>
       </c>
-      <c r="BN48" s="65">
+      <c r="BN48" s="66">
         <f>IF(BN47&gt;0,BN46/BN47,"")</f>
         <v>1.1562421474337792</v>
       </c>
-      <c r="BO48" s="65">
+      <c r="BO48" s="66">
         <f>IF(BO47&gt;0,BO46/BO47,"")</f>
         <v>1.1586968735841465</v>
       </c>
-      <c r="BP48" s="65">
+      <c r="BP48" s="66">
         <f>IF(BP47&gt;0,BP46/BP47,"")</f>
         <v>1.1611900440361098</v>
       </c>
-      <c r="BQ48" s="65">
+      <c r="BQ48" s="66">
         <f>IF(BQ47&gt;0,BQ46/BQ47,"")</f>
         <v>1.163769919360351</v>
       </c>
-      <c r="BR48" s="65">
+      <c r="BR48" s="66">
         <f>IF(BR47&gt;0,BR46/BR47,"")</f>
         <v>1.1664343556133794</v>
       </c>
-      <c r="BS48" s="65">
+      <c r="BS48" s="66">
         <f>IF(BS47&gt;0,BS46/BS47,"")</f>
         <v>1.169075921045502</v>
       </c>
-      <c r="BT48" s="65">
+      <c r="BT48" s="66">
         <f>IF(BT47&gt;0,BT46/BT47,"")</f>
         <v>1.1717540805015896</v>
       </c>
-      <c r="BU48" s="65">
+      <c r="BU48" s="66">
         <f>IF(BU47&gt;0,BU46/BU47,"")</f>
         <v>1.174514976876541</v>
       </c>
-      <c r="BV48" s="65">
+      <c r="BV48" s="66">
         <f>IF(BV47&gt;0,BV46/BV47,"")</f>
         <v>1.1773569456232162</v>
       </c>
-      <c r="BW48" s="65">
+      <c r="BW48" s="66">
         <f>IF(BW47&gt;0,BW46/BW47,"")</f>
         <v>1.1801775888563795</v>
       </c>
-      <c r="BX48" s="65">
+      <c r="BX48" s="66">
         <f>IF(BX47&gt;0,BX46/BX47,"")</f>
         <v>1.1830339517068444</v>
       </c>
-      <c r="BY48" s="65">
+      <c r="BY48" s="66">
         <f>IF(BY47&gt;0,BY46/BY47,"")</f>
         <v>1.1859703169371685</v>
       </c>
-      <c r="BZ48" s="65">
+      <c r="BZ48" s="66">
         <f>IF(BZ47&gt;0,BZ46/BZ47,"")</f>
         <v>1.1889853977803093</v>
       </c>
-      <c r="CA48" s="65">
+      <c r="CA48" s="66">
         <f>IF(CA47&gt;0,CA46/CA47,"")</f>
         <v>1.2043344524425832</v>
       </c>
-      <c r="CB48" s="65">
+      <c r="CB48" s="66">
         <f>IF(CB47&gt;0,CB46/CB47,"")</f>
         <v>1.2196398265865265</v>
       </c>
-      <c r="CC48" s="65">
+      <c r="CC48" s="66">
         <f>IF(CC47&gt;0,CC46/CC47,"")</f>
         <v>1.2349452007304698</v>
       </c>
-      <c r="CD48" s="65">
+      <c r="CD48" s="66">
         <f>IF(CD47&gt;0,CD46/CD47,"")</f>
         <v>1.2502505748744133</v>
       </c>
-      <c r="CE48" s="65">
+      <c r="CE48" s="66">
         <f>IF(CE47&gt;0,CE46/CE47,"")</f>
         <v>1.2654577626256145</v>
       </c>
-      <c r="CF48" s="65">
+      <c r="CF48" s="66">
         <f>IF(CF47&gt;0,CF46/CF47,"")</f>
         <v>1.2806213047488444</v>
       </c>
-      <c r="CG48" s="65">
+      <c r="CG48" s="66">
         <f>IF(CG47&gt;0,CG46/CG47,"")</f>
         <v>1.2957848468720743</v>
       </c>
-      <c r="CH48" s="65">
+      <c r="CH48" s="66">
         <f>IF(CH47&gt;0,CH46/CH47,"")</f>
         <v>1.3109483889953044</v>
       </c>
-      <c r="CI48" s="65">
+      <c r="CI48" s="66">
         <f>IF(CI47&gt;0,CI46/CI47,"")</f>
         <v>1.326013476699731</v>
       </c>
-      <c r="CJ48" s="65">
+      <c r="CJ48" s="66">
         <f>IF(CJ47&gt;0,CJ46/CJ47,"")</f>
         <v>1.3417295623026362</v>
       </c>
-      <c r="CK48" s="65">
+      <c r="CK48" s="66">
         <f>IF(CK47&gt;0,CK46/CK47,"")</f>
         <v>1.3574456479055417</v>
       </c>
-      <c r="CL48" s="65">
+      <c r="CL48" s="66">
         <f>IF(CL47&gt;0,CL46/CL47,"")</f>
         <v>1.3810668197589262</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="47" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D49" s="14">
         <f>CL17</f>
@@ -34548,7 +34915,7 @@
     </row>
     <row r="51" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -34642,279 +35009,279 @@
     </row>
     <row r="53" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B53" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G53" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H53" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I53" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L53" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M53" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N53" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O53" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P53" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q53" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R53" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S53" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T53" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U53" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V53" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W53" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X53" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Y53" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Z53" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA53" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB53" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC53" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD53" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE53" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AF53" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG53" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AH53" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AI53" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ53" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK53" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AL53" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM53" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AN53" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO53" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AP53" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ53" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AR53" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AS53" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AT53" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AU53" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AV53" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AW53" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AX53" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AY53" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ53" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BA53" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BB53" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BC53" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BD53" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BE53" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BF53" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BG53" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH53" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BI53" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BJ53" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK53" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BL53" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BM53" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BN53" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BO53" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BP53" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ53" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BR53" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BS53" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BT53" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU53" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BV53" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BW53" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BX53" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BY53" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BZ53" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="CA53" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="CB53" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CC53" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD53" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CE53" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CF53" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CG53" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CH53" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CI53" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CJ53" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CK53" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CL53" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D55" s="32">
         <f>SUM(E55:CL55)</f>
@@ -35267,10 +35634,10 @@
     </row>
     <row r="56" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B56" s="34" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E56" s="32">
         <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E28+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
@@ -35619,10 +35986,10 @@
     </row>
     <row r="57" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B57" s="34" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E57" s="32">
         <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
@@ -35971,1418 +36338,1418 @@
     </row>
     <row r="58" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E58" s="32">
-        <f>E13-E55</f>
+        <f>E13-E55-E25</f>
         <v>-14106.900000000005</v>
       </c>
       <c r="F58" s="32">
-        <f>F13-F55</f>
+        <f>F13-F55-F25</f>
         <v>-896.0999999999949</v>
       </c>
       <c r="G58" s="32">
-        <f>G13-G55</f>
+        <f>G13-G55-G25</f>
         <v>0</v>
       </c>
       <c r="H58" s="32">
-        <f>H13-H55</f>
+        <f>H13-H55-H25</f>
         <v>0</v>
       </c>
       <c r="I58" s="32">
-        <f>I13-I55</f>
+        <f>I13-I55-I25</f>
         <v>0</v>
       </c>
       <c r="J58" s="32">
-        <f>J13-J55</f>
+        <f>J13-J55-J25</f>
         <v>0</v>
       </c>
       <c r="K58" s="32">
-        <f>K13-K55</f>
+        <f>K13-K55-K25</f>
         <v>1601.3291924148925</v>
       </c>
       <c r="L58" s="32">
-        <f>L13-L55</f>
+        <f>L13-L55-L25</f>
         <v>2109.4590645058724</v>
       </c>
       <c r="M58" s="32">
-        <f>M13-M55</f>
+        <f>M13-M55-M25</f>
         <v>3.3496895058724476</v>
       </c>
       <c r="N58" s="32">
-        <f>N13-N55</f>
+        <f>N13-N55-N25</f>
         <v>32.642814505871684</v>
       </c>
       <c r="O58" s="32">
-        <f>O13-O55</f>
+        <f>O13-O55-O25</f>
         <v>42.834793749450455</v>
       </c>
       <c r="P58" s="32">
-        <f>P13-P55</f>
+        <f>P13-P55-P25</f>
         <v>57.1265631585693</v>
       </c>
       <c r="Q58" s="32">
-        <f>Q13-Q55</f>
+        <f>Q13-Q55-Q25</f>
         <v>80.3138595493815</v>
       </c>
       <c r="R58" s="32">
-        <f>R13-R55</f>
+        <f>R13-R55-R25</f>
         <v>103.50115594019417</v>
       </c>
       <c r="S58" s="32">
-        <f>S13-S55</f>
+        <f>S13-S55-S25</f>
         <v>107.54067784392282</v>
       </c>
       <c r="T58" s="32">
-        <f>T13-T55</f>
+        <f>T13-T55-T25</f>
         <v>121.80939730224691</v>
       </c>
       <c r="U58" s="32">
-        <f>U13-U55</f>
+        <f>U13-U55-U25</f>
         <v>144.99434441356107</v>
       </c>
       <c r="V58" s="32">
-        <f>V13-V55</f>
+        <f>V13-V55-V25</f>
         <v>168.17929152487568</v>
       </c>
       <c r="W58" s="32">
-        <f>W13-W55</f>
+        <f>W13-W55-W25</f>
         <v>172.17068112170273</v>
       </c>
       <c r="X58" s="32">
-        <f>X13-X55</f>
+        <f>X13-X55-X25</f>
         <v>186.44293159794051</v>
       </c>
       <c r="Y58" s="32">
-        <f>Y13-Y55</f>
+        <f>Y13-Y55-Y25</f>
         <v>209.62611823638827</v>
       </c>
       <c r="Z58" s="32">
-        <f>Z13-Z55</f>
+        <f>Z13-Z55-Z25</f>
         <v>232.80930487483738</v>
       </c>
       <c r="AA58" s="32">
-        <f>AA13-AA55</f>
+        <f>AA13-AA55-AA25</f>
         <v>236.7521064156149</v>
       </c>
       <c r="AB58" s="32">
-        <f>AB13-AB55</f>
+        <f>AB13-AB55-AB25</f>
         <v>251.02706212086832</v>
       </c>
       <c r="AC58" s="32">
-        <f>AC13-AC55</f>
+        <f>AC13-AC55-AC25</f>
         <v>274.2088803901479</v>
       </c>
       <c r="AD58" s="32">
-        <f>AD13-AD55</f>
+        <f>AD13-AD55-AD25</f>
         <v>297.39069865942747</v>
       </c>
       <c r="AE58" s="32">
-        <f>AE13-AE55</f>
+        <f>AE13-AE55-AE25</f>
         <v>301.2844926310636</v>
       </c>
       <c r="AF58" s="32">
-        <f>AF13-AF55</f>
+        <f>AF13-AF55-AF25</f>
         <v>315.5615878873523</v>
       </c>
       <c r="AG58" s="32">
-        <f>AG13-AG55</f>
+        <f>AG13-AG55-AG25</f>
         <v>338.74231202602596</v>
       </c>
       <c r="AH58" s="32">
-        <f>AH13-AH55</f>
+        <f>AH13-AH55-AH25</f>
         <v>361.92303616469826</v>
       </c>
       <c r="AI58" s="32">
-        <f>AI13-AI55</f>
+        <f>AI13-AI55-AI25</f>
         <v>365.76742379588086</v>
       </c>
       <c r="AJ58" s="32">
-        <f>AJ13-AJ55</f>
+        <f>AJ13-AJ55-AJ25</f>
         <v>380.04625395141056</v>
       </c>
       <c r="AK58" s="32">
-        <f>AK13-AK55</f>
+        <f>AK13-AK55-AK25</f>
         <v>403.22608327049784</v>
       </c>
       <c r="AL58" s="32">
-        <f>AL13-AL55</f>
+        <f>AL13-AL55-AL25</f>
         <v>426.40591258958693</v>
       </c>
       <c r="AM58" s="32">
-        <f>AM13-AM55</f>
+        <f>AM13-AM55-AM25</f>
         <v>430.2005074044091</v>
       </c>
       <c r="AN58" s="32">
-        <f>AN13-AN55</f>
+        <f>AN13-AN55-AN25</f>
         <v>444.480772908837</v>
       </c>
       <c r="AO58" s="32">
-        <f>AO13-AO55</f>
+        <f>AO13-AO55-AO25</f>
         <v>467.65985680909034</v>
       </c>
       <c r="AP58" s="32">
-        <f>AP13-AP55</f>
+        <f>AP13-AP55-AP25</f>
         <v>490.83894070934457</v>
       </c>
       <c r="AQ58" s="32">
-        <f>AQ13-AQ55</f>
+        <f>AQ13-AQ55-AQ25</f>
         <v>494.58336359896475</v>
       </c>
       <c r="AR58" s="32">
-        <f>AR13-AR55</f>
+        <f>AR13-AR55-AR25</f>
         <v>508.86483645327644</v>
       </c>
       <c r="AS58" s="32">
-        <f>AS13-AS55</f>
+        <f>AS13-AS55-AS25</f>
         <v>532.0432898056856</v>
       </c>
       <c r="AT58" s="32">
-        <f>AT13-AT55</f>
+        <f>AT13-AT55-AT25</f>
         <v>555.2217431580934</v>
       </c>
       <c r="AU58" s="32">
-        <f>AU13-AU55</f>
+        <f>AU13-AU55-AU25</f>
         <v>558.915619344174</v>
       </c>
       <c r="AV58" s="32">
-        <f>AV13-AV55</f>
+        <f>AV13-AV55-AV25</f>
         <v>573.1981219652771</v>
       </c>
       <c r="AW58" s="32">
-        <f>AW13-AW55</f>
+        <f>AW13-AW55-AW25</f>
         <v>596.3760349907325</v>
       </c>
       <c r="AX58" s="32">
-        <f>AX13-AX55</f>
+        <f>AX13-AX55-AX25</f>
         <v>619.5539480161888</v>
       </c>
       <c r="AY58" s="32">
-        <f>AY13-AY55</f>
+        <f>AY13-AY55-AY25</f>
         <v>623.196905094162</v>
       </c>
       <c r="AZ58" s="32">
-        <f>AZ13-AZ55</f>
+        <f>AZ13-AZ55-AZ25</f>
         <v>637.4802964552769</v>
       </c>
       <c r="BA58" s="32">
-        <f>BA13-BA55</f>
+        <f>BA13-BA55-BA25</f>
         <v>660.6577413066566</v>
       </c>
       <c r="BB58" s="32">
-        <f>BB13-BB55</f>
+        <f>BB13-BB55-BB25</f>
         <v>683.8351861580368</v>
       </c>
       <c r="BC58" s="32">
-        <f>BC13-BC55</f>
+        <f>BC13-BC55-BC25</f>
         <v>687.4268527876466</v>
       </c>
       <c r="BD58" s="32">
-        <f>BD13-BD55</f>
+        <f>BD13-BD55-BD25</f>
         <v>701.7110190196031</v>
       </c>
       <c r="BE58" s="32">
-        <f>BE13-BE55</f>
+        <f>BE13-BE55-BE25</f>
         <v>724.8880543043856</v>
       </c>
       <c r="BF58" s="32">
-        <f>BF13-BF55</f>
+        <f>BF13-BF55-BF25</f>
         <v>748.0650895891695</v>
       </c>
       <c r="BG58" s="32">
-        <f>BG13-BG55</f>
+        <f>BG13-BG55-BG25</f>
         <v>751.6050945891925</v>
       </c>
       <c r="BH58" s="32">
-        <f>BH13-BH55</f>
+        <f>BH13-BH55-BH25</f>
         <v>765.8899424223969</v>
       </c>
       <c r="BI58" s="32">
-        <f>BI13-BI55</f>
+        <f>BI13-BI55-BI25</f>
         <v>789.0666163935462</v>
       </c>
       <c r="BJ58" s="32">
-        <f>BJ13-BJ55</f>
+        <f>BJ13-BJ55-BJ25</f>
         <v>812.243290364695</v>
       </c>
       <c r="BK58" s="32">
-        <f>BK13-BK55</f>
+        <f>BK13-BK55-BK25</f>
         <v>815.7312620690009</v>
       </c>
       <c r="BL58" s="32">
-        <f>BL13-BL55</f>
+        <f>BL13-BL55-BL25</f>
         <v>830.0167141437246</v>
       </c>
       <c r="BM58" s="32">
-        <f>BM13-BM55</f>
+        <f>BM13-BM55-BM25</f>
         <v>853.1930670032348</v>
       </c>
       <c r="BN58" s="32">
-        <f>BN13-BN55</f>
+        <f>BN13-BN55-BN25</f>
         <v>876.3694198627454</v>
       </c>
       <c r="BO58" s="32">
-        <f>BO13-BO55</f>
+        <f>BO13-BO55-BO25</f>
         <v>879.8049856504413</v>
       </c>
       <c r="BP58" s="32">
-        <f>BP13-BP55</f>
+        <f>BP13-BP55-BP25</f>
         <v>894.0909770907192</v>
       </c>
       <c r="BQ58" s="32">
-        <f>BQ13-BQ55</f>
+        <f>BQ13-BQ55-BQ25</f>
         <v>917.2670426863333</v>
       </c>
       <c r="BR58" s="32">
-        <f>BR13-BR55</f>
+        <f>BR13-BR55-BR25</f>
         <v>940.443108281946</v>
       </c>
       <c r="BS58" s="32">
-        <f>BS13-BS55</f>
+        <f>BS13-BS55-BS25</f>
         <v>943.8258942265188</v>
       </c>
       <c r="BT58" s="32">
-        <f>BT13-BT55</f>
+        <f>BT13-BT55-BT25</f>
         <v>958.1123700897415</v>
       </c>
       <c r="BU58" s="32">
-        <f>BU13-BU55</f>
+        <f>BU13-BU55-BU25</f>
         <v>981.2881771870607</v>
       </c>
       <c r="BV58" s="32">
-        <f>BV13-BV55</f>
+        <f>BV13-BV55-BV25</f>
         <v>1004.463984284379</v>
       </c>
       <c r="BW58" s="32">
-        <f>BW13-BW55</f>
+        <f>BW13-BW55-BW25</f>
         <v>1007.7936148860804</v>
       </c>
       <c r="BX58" s="32">
-        <f>BX13-BX55</f>
+        <f>BX13-BX55-BX25</f>
         <v>1022.080528232581</v>
       </c>
       <c r="BY58" s="32">
-        <f>BY13-BY55</f>
+        <f>BY13-BY55-BY25</f>
         <v>3151.3654764840153</v>
       </c>
       <c r="BZ58" s="32">
-        <f>BZ13-BZ55</f>
+        <f>BZ13-BZ55-BZ25</f>
         <v>3145.2479247354477</v>
       </c>
       <c r="CA58" s="32">
-        <f>CA13-CA55</f>
+        <f>CA13-CA55-CA25</f>
         <v>3119.230897713078</v>
       </c>
       <c r="CB58" s="32">
-        <f>CB13-CB55</f>
+        <f>CB13-CB55-CB25</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CC58" s="32">
-        <f>CC13-CC55</f>
+        <f>CC13-CC55-CC25</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CD58" s="32">
-        <f>CD13-CD55</f>
+        <f>CD13-CD55-CD25</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CE58" s="32">
-        <f>CE13-CE55</f>
+        <f>CE13-CE55-CE25</f>
         <v>3090.400740930274</v>
       </c>
       <c r="CF58" s="32">
-        <f>CF13-CF55</f>
+        <f>CF13-CF55-CF25</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CG58" s="32">
-        <f>CG13-CG55</f>
+        <f>CG13-CG55-CG25</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CH58" s="32">
-        <f>CH13-CH55</f>
+        <f>CH13-CH55-CH25</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CI58" s="32">
-        <f>CI13-CI55</f>
+        <f>CI13-CI55-CI25</f>
         <v>3061.5232063707645</v>
       </c>
       <c r="CJ58" s="32">
-        <f>CJ13-CJ55</f>
+        <f>CJ13-CJ55-CJ25</f>
         <v>3193.8188300401507</v>
       </c>
       <c r="CK58" s="32">
-        <f>CK13-CK55</f>
+        <f>CK13-CK55-CK25</f>
         <v>3193.8188300401507</v>
       </c>
       <c r="CL58" s="32">
-        <f>CL13-CL55</f>
+        <f>CL13-CL55-CL25</f>
         <v>2800.288402540151</v>
       </c>
     </row>
     <row r="59" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E59" s="32">
-        <f>E13-'IS(Q)'!E28-E19-E55</f>
+        <f>E13-'IS(Q)'!E28-E19-E55-E25</f>
         <v>-14106.900000000005</v>
       </c>
       <c r="F59" s="32">
-        <f>F13-'IS(Q)'!F28-F19-F55</f>
+        <f>F13-'IS(Q)'!F28-F19-F55-F25</f>
         <v>-896.0999999999949</v>
       </c>
       <c r="G59" s="32">
-        <f>G13-'IS(Q)'!G28-G19-G55</f>
+        <f>G13-'IS(Q)'!G28-G19-G55-G25</f>
         <v>0</v>
       </c>
       <c r="H59" s="32">
-        <f>H13-'IS(Q)'!H28-H19-H55</f>
+        <f>H13-'IS(Q)'!H28-H19-H55-H25</f>
         <v>0</v>
       </c>
       <c r="I59" s="32">
-        <f>I13-'IS(Q)'!I28-I19-I55</f>
+        <f>I13-'IS(Q)'!I28-I19-I55-I25</f>
         <v>0</v>
       </c>
       <c r="J59" s="32">
-        <f>J13-'IS(Q)'!J28-J19-J55</f>
+        <f>J13-'IS(Q)'!J28-J19-J55-J25</f>
         <v>0</v>
       </c>
       <c r="K59" s="32">
-        <f>K13-'IS(Q)'!K28-K19-K55</f>
+        <f>K13-'IS(Q)'!K28-K19-K55-K25</f>
         <v>1680.9290000000012</v>
       </c>
       <c r="L59" s="32">
-        <f>L13-'IS(Q)'!L28-L19-L55</f>
+        <f>L13-'IS(Q)'!L28-L19-L55-L25</f>
         <v>2205.5535000000004</v>
       </c>
       <c r="M59" s="32">
-        <f>M13-'IS(Q)'!M28-M19-M55</f>
+        <f>M13-'IS(Q)'!M28-M19-M55-M25</f>
         <v>99.44412500000061</v>
       </c>
       <c r="N59" s="32">
-        <f>N13-'IS(Q)'!N28-N19-N55</f>
+        <f>N13-'IS(Q)'!N28-N19-N55-N25</f>
         <v>128.73724999999985</v>
       </c>
       <c r="O59" s="32">
-        <f>O13-'IS(Q)'!O28-O19-O55</f>
+        <f>O13-'IS(Q)'!O28-O19-O55-O25</f>
         <v>131.56433000000075</v>
       </c>
       <c r="P59" s="32">
-        <f>P13-'IS(Q)'!P28-P19-P55</f>
+        <f>P13-'IS(Q)'!P28-P19-P55-P25</f>
         <v>151.98193250000077</v>
       </c>
       <c r="Q59" s="32">
-        <f>Q13-'IS(Q)'!Q28-Q19-Q55</f>
+        <f>Q13-'IS(Q)'!Q28-Q19-Q55-Q25</f>
         <v>181.2750575000008</v>
       </c>
       <c r="R59" s="32">
-        <f>R13-'IS(Q)'!R28-R19-R55</f>
+        <f>R13-'IS(Q)'!R28-R19-R55-R25</f>
         <v>210.56818250000123</v>
       </c>
       <c r="S59" s="32">
-        <f>S13-'IS(Q)'!S28-S19-S55</f>
+        <f>S13-'IS(Q)'!S28-S19-S55-S25</f>
         <v>213.33425749999992</v>
       </c>
       <c r="T59" s="32">
-        <f>T13-'IS(Q)'!T28-T19-T55</f>
+        <f>T13-'IS(Q)'!T28-T19-T55-T25</f>
         <v>233.75186000000176</v>
       </c>
       <c r="U59" s="32">
-        <f>U13-'IS(Q)'!U28-U19-U55</f>
+        <f>U13-'IS(Q)'!U28-U19-U55-U25</f>
         <v>263.0449850000015</v>
       </c>
       <c r="V59" s="32">
-        <f>V13-'IS(Q)'!V28-V19-V55</f>
+        <f>V13-'IS(Q)'!V28-V19-V55-V25</f>
         <v>292.3381100000017</v>
       </c>
       <c r="W59" s="32">
-        <f>W13-'IS(Q)'!W28-W19-W55</f>
+        <f>W13-'IS(Q)'!W28-W19-W55-W25</f>
         <v>295.0427529650019</v>
       </c>
       <c r="X59" s="32">
-        <f>X13-'IS(Q)'!X28-X19-X55</f>
+        <f>X13-'IS(Q)'!X28-X19-X55-X25</f>
         <v>315.46035546500144</v>
       </c>
       <c r="Y59" s="32">
-        <f>Y13-'IS(Q)'!Y28-Y19-Y55</f>
+        <f>Y13-'IS(Q)'!Y28-Y19-Y55-Y25</f>
         <v>344.75348046500073</v>
       </c>
       <c r="Z59" s="32">
-        <f>Z13-'IS(Q)'!Z28-Z19-Z55</f>
+        <f>Z13-'IS(Q)'!Z28-Z19-Z55-Z25</f>
         <v>374.04660546500133</v>
       </c>
       <c r="AA59" s="32">
-        <f>AA13-'IS(Q)'!AA28-AA19-AA55</f>
+        <f>AA13-'IS(Q)'!AA28-AA19-AA55-AA25</f>
         <v>376.68938637075564</v>
       </c>
       <c r="AB59" s="32">
-        <f>AB13-'IS(Q)'!AB28-AB19-AB55</f>
+        <f>AB13-'IS(Q)'!AB28-AB19-AB55-AB25</f>
         <v>397.1069888707565</v>
       </c>
       <c r="AC59" s="32">
-        <f>AC13-'IS(Q)'!AC28-AC19-AC55</f>
+        <f>AC13-'IS(Q)'!AC28-AC19-AC55-AC25</f>
         <v>426.4001138707564</v>
       </c>
       <c r="AD59" s="32">
-        <f>AD13-'IS(Q)'!AD28-AD19-AD55</f>
+        <f>AD13-'IS(Q)'!AD28-AD19-AD55-AD25</f>
         <v>455.6932388707563</v>
       </c>
       <c r="AE59" s="32">
-        <f>AE13-'IS(Q)'!AE28-AE19-AE55</f>
+        <f>AE13-'IS(Q)'!AE28-AE19-AE55-AE25</f>
         <v>458.27372468285256</v>
       </c>
       <c r="AF59" s="32">
-        <f>AF13-'IS(Q)'!AF28-AF19-AF55</f>
+        <f>AF13-'IS(Q)'!AF28-AF19-AF55-AF25</f>
         <v>478.6913271828506</v>
       </c>
       <c r="AG59" s="32">
-        <f>AG13-'IS(Q)'!AG28-AG19-AG55</f>
+        <f>AG13-'IS(Q)'!AG28-AG19-AG55-AG25</f>
         <v>507.984452182852</v>
       </c>
       <c r="AH59" s="32">
-        <f>AH13-'IS(Q)'!AH28-AH19-AH55</f>
+        <f>AH13-'IS(Q)'!AH28-AH19-AH55-AH25</f>
         <v>537.2775771828522</v>
       </c>
       <c r="AI59" s="32">
-        <f>AI13-'IS(Q)'!AI28-AI19-AI55</f>
+        <f>AI13-'IS(Q)'!AI28-AI19-AI55-AI25</f>
         <v>539.7953318356319</v>
       </c>
       <c r="AJ59" s="32">
-        <f>AJ13-'IS(Q)'!AJ28-AJ19-AJ55</f>
+        <f>AJ13-'IS(Q)'!AJ28-AJ19-AJ55-AJ25</f>
         <v>560.212934335632</v>
       </c>
       <c r="AK59" s="32">
-        <f>AK13-'IS(Q)'!AK28-AK19-AK55</f>
+        <f>AK13-'IS(Q)'!AK28-AK19-AK55-AK25</f>
         <v>589.506059335631</v>
       </c>
       <c r="AL59" s="32">
-        <f>AL13-'IS(Q)'!AL28-AL19-AL55</f>
+        <f>AL13-'IS(Q)'!AL28-AL19-AL55-AL25</f>
         <v>618.7991843356319</v>
       </c>
       <c r="AM59" s="32">
-        <f>AM13-'IS(Q)'!AM28-AM19-AM55</f>
+        <f>AM13-'IS(Q)'!AM28-AM19-AM55-AM25</f>
         <v>621.2537687109796</v>
       </c>
       <c r="AN59" s="32">
-        <f>AN13-'IS(Q)'!AN28-AN19-AN55</f>
+        <f>AN13-'IS(Q)'!AN28-AN19-AN55-AN25</f>
         <v>641.6713712109811</v>
       </c>
       <c r="AO59" s="32">
-        <f>AO13-'IS(Q)'!AO28-AO19-AO55</f>
+        <f>AO13-'IS(Q)'!AO28-AO19-AO55-AO25</f>
         <v>670.9644962109804</v>
       </c>
       <c r="AP59" s="32">
-        <f>AP13-'IS(Q)'!AP28-AP19-AP55</f>
+        <f>AP13-'IS(Q)'!AP28-AP19-AP55-AP25</f>
         <v>700.2576212109808</v>
       </c>
       <c r="AQ59" s="32">
-        <f>AQ13-'IS(Q)'!AQ28-AQ19-AQ55</f>
+        <f>AQ13-'IS(Q)'!AQ28-AQ19-AQ55-AQ25</f>
         <v>702.6485931169576</v>
       </c>
       <c r="AR59" s="32">
-        <f>AR13-'IS(Q)'!AR28-AR19-AR55</f>
+        <f>AR13-'IS(Q)'!AR28-AR19-AR55-AR25</f>
         <v>723.0661956169563</v>
       </c>
       <c r="AS59" s="32">
-        <f>AS13-'IS(Q)'!AS28-AS19-AS55</f>
+        <f>AS13-'IS(Q)'!AS28-AS19-AS55-AS25</f>
         <v>752.3593206169575</v>
       </c>
       <c r="AT59" s="32">
-        <f>AT13-'IS(Q)'!AT28-AT19-AT55</f>
+        <f>AT13-'IS(Q)'!AT28-AT19-AT55-AT25</f>
         <v>781.6524456169573</v>
       </c>
       <c r="AU59" s="32">
-        <f>AU13-'IS(Q)'!AU28-AU19-AU55</f>
+        <f>AU13-'IS(Q)'!AU28-AU19-AU55-AU25</f>
         <v>783.979359766277</v>
       </c>
       <c r="AV59" s="32">
-        <f>AV13-'IS(Q)'!AV28-AV19-AV55</f>
+        <f>AV13-'IS(Q)'!AV28-AV19-AV55-AV25</f>
         <v>804.3969622662771</v>
       </c>
       <c r="AW59" s="32">
-        <f>AW13-'IS(Q)'!AW28-AW19-AW55</f>
+        <f>AW13-'IS(Q)'!AW28-AW19-AW55-AW25</f>
         <v>833.6900872662766</v>
       </c>
       <c r="AX59" s="32">
-        <f>AX13-'IS(Q)'!AX28-AX19-AX55</f>
+        <f>AX13-'IS(Q)'!AX28-AX19-AX55-AX25</f>
         <v>862.9832122662767</v>
       </c>
       <c r="AY59" s="32">
-        <f>AY13-'IS(Q)'!AY28-AY19-AY55</f>
+        <f>AY13-'IS(Q)'!AY28-AY19-AY55-AY25</f>
         <v>865.2456202546398</v>
       </c>
       <c r="AZ59" s="32">
-        <f>AZ13-'IS(Q)'!AZ28-AZ19-AZ55</f>
+        <f>AZ13-'IS(Q)'!AZ28-AZ19-AZ55-AZ25</f>
         <v>885.6632227546409</v>
       </c>
       <c r="BA59" s="32">
-        <f>BA13-'IS(Q)'!BA28-BA19-BA55</f>
+        <f>BA13-'IS(Q)'!BA28-BA19-BA55-BA25</f>
         <v>914.9563477546407</v>
       </c>
       <c r="BB59" s="32">
-        <f>BB13-'IS(Q)'!BB28-BB19-BB55</f>
+        <f>BB13-'IS(Q)'!BB28-BB19-BB55-BB25</f>
         <v>944.2494727546409</v>
       </c>
       <c r="BC59" s="32">
-        <f>BC13-'IS(Q)'!BC28-BC19-BC55</f>
+        <f>BC13-'IS(Q)'!BC28-BC19-BC55-BC25</f>
         <v>946.4469230389234</v>
       </c>
       <c r="BD59" s="32">
-        <f>BD13-'IS(Q)'!BD28-BD19-BD55</f>
+        <f>BD13-'IS(Q)'!BD28-BD19-BD55-BD25</f>
         <v>966.864525538923</v>
       </c>
       <c r="BE59" s="32">
-        <f>BE13-'IS(Q)'!BE28-BE19-BE55</f>
+        <f>BE13-'IS(Q)'!BE28-BE19-BE55-BE25</f>
         <v>996.1576505389227</v>
       </c>
       <c r="BF59" s="32">
-        <f>BF13-'IS(Q)'!BF28-BF19-BF55</f>
+        <f>BF13-'IS(Q)'!BF28-BF19-BF55-BF25</f>
         <v>1025.4507755389238</v>
       </c>
       <c r="BG59" s="32">
-        <f>BG13-'IS(Q)'!BG28-BG19-BG55</f>
+        <f>BG13-'IS(Q)'!BG28-BG19-BG55-BG25</f>
         <v>1027.5828134151966</v>
       </c>
       <c r="BH59" s="32">
-        <f>BH13-'IS(Q)'!BH28-BH19-BH55</f>
+        <f>BH13-'IS(Q)'!BH28-BH19-BH55-BH25</f>
         <v>1048.0004159151968</v>
       </c>
       <c r="BI59" s="32">
-        <f>BI13-'IS(Q)'!BI28-BI19-BI55</f>
+        <f>BI13-'IS(Q)'!BI28-BI19-BI55-BI25</f>
         <v>1077.293540915197</v>
       </c>
       <c r="BJ59" s="32">
-        <f>BJ13-'IS(Q)'!BJ28-BJ19-BJ55</f>
+        <f>BJ13-'IS(Q)'!BJ28-BJ19-BJ55-BJ25</f>
         <v>1106.5866659151964</v>
       </c>
       <c r="BK59" s="32">
-        <f>BK13-'IS(Q)'!BK28-BK19-BK55</f>
+        <f>BK13-'IS(Q)'!BK28-BK19-BK55-BK25</f>
         <v>1108.6528334966015</v>
       </c>
       <c r="BL59" s="32">
-        <f>BL13-'IS(Q)'!BL28-BL19-BL55</f>
+        <f>BL13-'IS(Q)'!BL28-BL19-BL55-BL25</f>
         <v>1129.0704359966026</v>
       </c>
       <c r="BM59" s="32">
-        <f>BM13-'IS(Q)'!BM28-BM19-BM55</f>
+        <f>BM13-'IS(Q)'!BM28-BM19-BM55-BM25</f>
         <v>1158.3635609966022</v>
       </c>
       <c r="BN59" s="32">
-        <f>BN13-'IS(Q)'!BN28-BN19-BN55</f>
+        <f>BN13-'IS(Q)'!BN28-BN19-BN55-BN25</f>
         <v>1187.6566859966022</v>
       </c>
       <c r="BO59" s="32">
-        <f>BO13-'IS(Q)'!BO28-BO19-BO55</f>
+        <f>BO13-'IS(Q)'!BO28-BO19-BO55-BO25</f>
         <v>1189.6565221910787</v>
       </c>
       <c r="BP59" s="32">
-        <f>BP13-'IS(Q)'!BP28-BP19-BP55</f>
+        <f>BP13-'IS(Q)'!BP28-BP19-BP55-BP25</f>
         <v>1210.0741246910777</v>
       </c>
       <c r="BQ59" s="32">
-        <f>BQ13-'IS(Q)'!BQ28-BQ19-BQ55</f>
+        <f>BQ13-'IS(Q)'!BQ28-BQ19-BQ55-BQ25</f>
         <v>1239.3672496910785</v>
       </c>
       <c r="BR59" s="32">
-        <f>BR13-'IS(Q)'!BR28-BR19-BR55</f>
+        <f>BR13-'IS(Q)'!BR28-BR19-BR55-BR25</f>
         <v>1268.6603746910778</v>
       </c>
       <c r="BS59" s="32">
-        <f>BS13-'IS(Q)'!BS28-BS19-BS55</f>
+        <f>BS13-'IS(Q)'!BS28-BS19-BS55-BS25</f>
         <v>1270.5934151789172</v>
       </c>
       <c r="BT59" s="32">
-        <f>BT13-'IS(Q)'!BT28-BT19-BT55</f>
+        <f>BT13-'IS(Q)'!BT28-BT19-BT55-BT25</f>
         <v>1291.0110176789178</v>
       </c>
       <c r="BU59" s="32">
-        <f>BU13-'IS(Q)'!BU28-BU19-BU55</f>
+        <f>BU13-'IS(Q)'!BU28-BU19-BU55-BU25</f>
         <v>1320.304142678918</v>
       </c>
       <c r="BV59" s="32">
-        <f>BV13-'IS(Q)'!BV28-BV19-BV55</f>
+        <f>BV13-'IS(Q)'!BV28-BV19-BV55-BV25</f>
         <v>1349.597267678917</v>
       </c>
       <c r="BW59" s="32">
-        <f>BW13-'IS(Q)'!BW28-BW19-BW55</f>
+        <f>BW13-'IS(Q)'!BW28-BW19-BW55-BW25</f>
         <v>1351.4630448901698</v>
       </c>
       <c r="BX59" s="32">
-        <f>BX13-'IS(Q)'!BX28-BX19-BX55</f>
+        <f>BX13-'IS(Q)'!BX28-BX19-BX55-BX25</f>
         <v>1371.880647390169</v>
       </c>
       <c r="BY59" s="32">
-        <f>BY13-'IS(Q)'!BY28-BY19-BY55</f>
+        <f>BY13-'IS(Q)'!BY28-BY19-BY55-BY25</f>
         <v>3507.28314739017</v>
       </c>
       <c r="BZ59" s="32">
-        <f>BZ13-'IS(Q)'!BZ28-BZ19-BZ55</f>
+        <f>BZ13-'IS(Q)'!BZ28-BZ19-BZ55-BZ25</f>
         <v>3507.2831473901697</v>
       </c>
       <c r="CA59" s="32">
-        <f>CA13-'IS(Q)'!CA28-CA19-CA55</f>
+        <f>CA13-'IS(Q)'!CA28-CA19-CA55-CA25</f>
         <v>3479.788065481901</v>
       </c>
       <c r="CB59" s="32">
-        <f>CB13-'IS(Q)'!CB28-CB19-CB55</f>
+        <f>CB13-'IS(Q)'!CB28-CB19-CB55-CB25</f>
         <v>3470.9125429819014</v>
       </c>
       <c r="CC59" s="32">
-        <f>CC13-'IS(Q)'!CC28-CC19-CC55</f>
+        <f>CC13-'IS(Q)'!CC28-CC19-CC55-CC25</f>
         <v>3470.9125429819014</v>
       </c>
       <c r="CD59" s="32">
-        <f>CD13-'IS(Q)'!CD28-CD19-CD55</f>
+        <f>CD13-'IS(Q)'!CD28-CD19-CD55-CD25</f>
         <v>3470.9125429819014</v>
       </c>
       <c r="CE59" s="32">
-        <f>CE13-'IS(Q)'!CE28-CE19-CE55</f>
+        <f>CE13-'IS(Q)'!CE28-CE19-CE55-CE25</f>
         <v>3443.3492528152738</v>
       </c>
       <c r="CF59" s="32">
-        <f>CF13-'IS(Q)'!CF28-CF19-CF55</f>
+        <f>CF13-'IS(Q)'!CF28-CF19-CF55-CF25</f>
         <v>3434.4737303152733</v>
       </c>
       <c r="CG59" s="32">
-        <f>CG13-'IS(Q)'!CG28-CG19-CG55</f>
+        <f>CG13-'IS(Q)'!CG28-CG19-CG55-CG25</f>
         <v>3434.4737303152733</v>
       </c>
       <c r="CH59" s="32">
-        <f>CH13-'IS(Q)'!CH28-CH19-CH55</f>
+        <f>CH13-'IS(Q)'!CH28-CH19-CH55-CH25</f>
         <v>3434.4737303152733</v>
       </c>
       <c r="CI59" s="32">
-        <f>CI13-'IS(Q)'!CI28-CI19-CI55</f>
+        <f>CI13-'IS(Q)'!CI28-CI19-CI55-CI25</f>
         <v>3406.8417544324802</v>
       </c>
       <c r="CJ59" s="32">
-        <f>CJ13-'IS(Q)'!CJ28-CJ19-CJ55</f>
+        <f>CJ13-'IS(Q)'!CJ28-CJ19-CJ55-CJ25</f>
         <v>3397.966231932481</v>
       </c>
       <c r="CK59" s="32">
-        <f>CK13-'IS(Q)'!CK28-CK19-CK55</f>
+        <f>CK13-'IS(Q)'!CK28-CK19-CK55-CK25</f>
         <v>3397.966231932481</v>
       </c>
       <c r="CL59" s="32">
-        <f>CL13-'IS(Q)'!CL28-CL19-CL55</f>
+        <f>CL13-'IS(Q)'!CL28-CL19-CL55-CL25</f>
         <v>3004.4358044324813</v>
       </c>
     </row>
     <row r="60" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E60" s="32">
-        <f>E16-E55</f>
+        <f>E16-E55-E25</f>
         <v>-14106.900000000005</v>
       </c>
       <c r="F60" s="32">
-        <f>F16-F55</f>
+        <f>F16-F55-F25</f>
         <v>-896.0999999999949</v>
       </c>
       <c r="G60" s="32">
-        <f>G16-G55</f>
+        <f>G16-G55-G25</f>
         <v>0</v>
       </c>
       <c r="H60" s="32">
-        <f>H16-H55</f>
+        <f>H16-H55-H25</f>
         <v>0</v>
       </c>
       <c r="I60" s="32">
-        <f>I16-I55</f>
+        <f>I16-I55-I25</f>
         <v>0</v>
       </c>
       <c r="J60" s="32">
-        <f>J16-J55</f>
+        <f>J16-J55-J25</f>
         <v>0</v>
       </c>
       <c r="K60" s="32">
-        <f>K16-K55</f>
+        <f>K16-K55-K25</f>
         <v>0</v>
       </c>
       <c r="L60" s="32">
-        <f>L16-L55</f>
+        <f>L16-L55-L25</f>
         <v>0</v>
       </c>
       <c r="M60" s="32">
-        <f>M16-M55</f>
+        <f>M16-M55-M25</f>
         <v>0</v>
       </c>
       <c r="N60" s="32">
-        <f>N16-N55</f>
+        <f>N16-N55-N25</f>
         <v>0</v>
       </c>
       <c r="O60" s="32">
-        <f>O16-O55</f>
+        <f>O16-O55-O25</f>
         <v>0</v>
       </c>
       <c r="P60" s="32">
-        <f>P16-P55</f>
+        <f>P16-P55-P25</f>
         <v>0</v>
       </c>
       <c r="Q60" s="32">
-        <f>Q16-Q55</f>
+        <f>Q16-Q55-Q25</f>
         <v>0</v>
       </c>
       <c r="R60" s="32">
-        <f>R16-R55</f>
+        <f>R16-R55-R25</f>
         <v>0</v>
       </c>
       <c r="S60" s="32">
-        <f>S16-S55</f>
+        <f>S16-S55-S25</f>
         <v>0</v>
       </c>
       <c r="T60" s="32">
-        <f>T16-T55</f>
+        <f>T16-T55-T25</f>
         <v>0</v>
       </c>
       <c r="U60" s="32">
-        <f>U16-U55</f>
+        <f>U16-U55-U25</f>
         <v>0</v>
       </c>
       <c r="V60" s="32">
-        <f>V16-V55</f>
+        <f>V16-V55-V25</f>
         <v>0</v>
       </c>
       <c r="W60" s="32">
-        <f>W16-W55</f>
+        <f>W16-W55-W25</f>
         <v>0</v>
       </c>
       <c r="X60" s="32">
-        <f>X16-X55</f>
+        <f>X16-X55-X25</f>
         <v>0</v>
       </c>
       <c r="Y60" s="32">
-        <f>Y16-Y55</f>
+        <f>Y16-Y55-Y25</f>
         <v>0</v>
       </c>
       <c r="Z60" s="32">
-        <f>Z16-Z55</f>
+        <f>Z16-Z55-Z25</f>
         <v>0</v>
       </c>
       <c r="AA60" s="32">
-        <f>AA16-AA55</f>
+        <f>AA16-AA55-AA25</f>
         <v>0</v>
       </c>
       <c r="AB60" s="32">
-        <f>AB16-AB55</f>
+        <f>AB16-AB55-AB25</f>
         <v>0</v>
       </c>
       <c r="AC60" s="32">
-        <f>AC16-AC55</f>
+        <f>AC16-AC55-AC25</f>
         <v>0</v>
       </c>
       <c r="AD60" s="32">
-        <f>AD16-AD55</f>
+        <f>AD16-AD55-AD25</f>
         <v>0</v>
       </c>
       <c r="AE60" s="32">
-        <f>AE16-AE55</f>
+        <f>AE16-AE55-AE25</f>
         <v>0</v>
       </c>
       <c r="AF60" s="32">
-        <f>AF16-AF55</f>
+        <f>AF16-AF55-AF25</f>
         <v>0</v>
       </c>
       <c r="AG60" s="32">
-        <f>AG16-AG55</f>
+        <f>AG16-AG55-AG25</f>
         <v>0</v>
       </c>
       <c r="AH60" s="32">
-        <f>AH16-AH55</f>
+        <f>AH16-AH55-AH25</f>
         <v>0</v>
       </c>
       <c r="AI60" s="32">
-        <f>AI16-AI55</f>
+        <f>AI16-AI55-AI25</f>
         <v>0</v>
       </c>
       <c r="AJ60" s="32">
-        <f>AJ16-AJ55</f>
+        <f>AJ16-AJ55-AJ25</f>
         <v>0</v>
       </c>
       <c r="AK60" s="32">
-        <f>AK16-AK55</f>
+        <f>AK16-AK55-AK25</f>
         <v>0</v>
       </c>
       <c r="AL60" s="32">
-        <f>AL16-AL55</f>
+        <f>AL16-AL55-AL25</f>
         <v>0</v>
       </c>
       <c r="AM60" s="32">
-        <f>AM16-AM55</f>
+        <f>AM16-AM55-AM25</f>
         <v>0</v>
       </c>
       <c r="AN60" s="32">
-        <f>AN16-AN55</f>
+        <f>AN16-AN55-AN25</f>
         <v>0</v>
       </c>
       <c r="AO60" s="32">
-        <f>AO16-AO55</f>
+        <f>AO16-AO55-AO25</f>
         <v>0</v>
       </c>
       <c r="AP60" s="32">
-        <f>AP16-AP55</f>
+        <f>AP16-AP55-AP25</f>
         <v>0</v>
       </c>
       <c r="AQ60" s="32">
-        <f>AQ16-AQ55</f>
+        <f>AQ16-AQ55-AQ25</f>
         <v>0</v>
       </c>
       <c r="AR60" s="32">
-        <f>AR16-AR55</f>
+        <f>AR16-AR55-AR25</f>
         <v>0</v>
       </c>
       <c r="AS60" s="32">
-        <f>AS16-AS55</f>
+        <f>AS16-AS55-AS25</f>
         <v>0</v>
       </c>
       <c r="AT60" s="32">
-        <f>AT16-AT55</f>
+        <f>AT16-AT55-AT25</f>
         <v>0</v>
       </c>
       <c r="AU60" s="32">
-        <f>AU16-AU55</f>
+        <f>AU16-AU55-AU25</f>
         <v>0</v>
       </c>
       <c r="AV60" s="32">
-        <f>AV16-AV55</f>
+        <f>AV16-AV55-AV25</f>
         <v>0</v>
       </c>
       <c r="AW60" s="32">
-        <f>AW16-AW55</f>
+        <f>AW16-AW55-AW25</f>
         <v>0</v>
       </c>
       <c r="AX60" s="32">
-        <f>AX16-AX55</f>
+        <f>AX16-AX55-AX25</f>
         <v>0</v>
       </c>
       <c r="AY60" s="32">
-        <f>AY16-AY55</f>
+        <f>AY16-AY55-AY25</f>
         <v>0</v>
       </c>
       <c r="AZ60" s="32">
-        <f>AZ16-AZ55</f>
+        <f>AZ16-AZ55-AZ25</f>
         <v>0</v>
       </c>
       <c r="BA60" s="32">
-        <f>BA16-BA55</f>
+        <f>BA16-BA55-BA25</f>
         <v>0</v>
       </c>
       <c r="BB60" s="32">
-        <f>BB16-BB55</f>
+        <f>BB16-BB55-BB25</f>
         <v>0</v>
       </c>
       <c r="BC60" s="32">
-        <f>BC16-BC55</f>
+        <f>BC16-BC55-BC25</f>
         <v>0</v>
       </c>
       <c r="BD60" s="32">
-        <f>BD16-BD55</f>
+        <f>BD16-BD55-BD25</f>
         <v>0</v>
       </c>
       <c r="BE60" s="32">
-        <f>BE16-BE55</f>
+        <f>BE16-BE55-BE25</f>
         <v>0</v>
       </c>
       <c r="BF60" s="32">
-        <f>BF16-BF55</f>
+        <f>BF16-BF55-BF25</f>
         <v>0</v>
       </c>
       <c r="BG60" s="32">
-        <f>BG16-BG55</f>
+        <f>BG16-BG55-BG25</f>
         <v>0</v>
       </c>
       <c r="BH60" s="32">
-        <f>BH16-BH55</f>
+        <f>BH16-BH55-BH25</f>
         <v>0</v>
       </c>
       <c r="BI60" s="32">
-        <f>BI16-BI55</f>
+        <f>BI16-BI55-BI25</f>
         <v>0</v>
       </c>
       <c r="BJ60" s="32">
-        <f>BJ16-BJ55</f>
+        <f>BJ16-BJ55-BJ25</f>
         <v>0</v>
       </c>
       <c r="BK60" s="32">
-        <f>BK16-BK55</f>
+        <f>BK16-BK55-BK25</f>
         <v>0</v>
       </c>
       <c r="BL60" s="32">
-        <f>BL16-BL55</f>
+        <f>BL16-BL55-BL25</f>
         <v>24830.21683000973</v>
       </c>
       <c r="BM60" s="32">
-        <f>BM16-BM55</f>
+        <f>BM16-BM55-BM25</f>
         <v>853.1930670032348</v>
       </c>
       <c r="BN60" s="32">
-        <f>BN16-BN55</f>
+        <f>BN16-BN55-BN25</f>
         <v>876.3694198627454</v>
       </c>
       <c r="BO60" s="32">
-        <f>BO16-BO55</f>
+        <f>BO16-BO55-BO25</f>
         <v>879.8049856504413</v>
       </c>
       <c r="BP60" s="32">
-        <f>BP16-BP55</f>
+        <f>BP16-BP55-BP25</f>
         <v>894.0909770907192</v>
       </c>
       <c r="BQ60" s="32">
-        <f>BQ16-BQ55</f>
+        <f>BQ16-BQ55-BQ25</f>
         <v>917.2670426863333</v>
       </c>
       <c r="BR60" s="32">
-        <f>BR16-BR55</f>
+        <f>BR16-BR55-BR25</f>
         <v>940.443108281946</v>
       </c>
       <c r="BS60" s="32">
-        <f>BS16-BS55</f>
+        <f>BS16-BS55-BS25</f>
         <v>943.8258942265188</v>
       </c>
       <c r="BT60" s="32">
-        <f>BT16-BT55</f>
+        <f>BT16-BT55-BT25</f>
         <v>958.1123700897415</v>
       </c>
       <c r="BU60" s="32">
-        <f>BU16-BU55</f>
+        <f>BU16-BU55-BU25</f>
         <v>981.2881771870607</v>
       </c>
       <c r="BV60" s="32">
-        <f>BV16-BV55</f>
+        <f>BV16-BV55-BV25</f>
         <v>1004.463984284379</v>
       </c>
       <c r="BW60" s="32">
-        <f>BW16-BW55</f>
+        <f>BW16-BW55-BW25</f>
         <v>1007.7936148860804</v>
       </c>
       <c r="BX60" s="32">
-        <f>BX16-BX55</f>
+        <f>BX16-BX55-BX25</f>
         <v>1022.080528232581</v>
       </c>
       <c r="BY60" s="32">
-        <f>BY16-BY55</f>
+        <f>BY16-BY55-BY25</f>
         <v>3151.3654764840157</v>
       </c>
       <c r="BZ60" s="32">
-        <f>BZ16-BZ55</f>
+        <f>BZ16-BZ55-BZ25</f>
         <v>3145.2479247354477</v>
       </c>
       <c r="CA60" s="32">
-        <f>CA16-CA55</f>
+        <f>CA16-CA55-CA25</f>
         <v>3119.230897713078</v>
       </c>
       <c r="CB60" s="32">
-        <f>CB16-CB55</f>
+        <f>CB16-CB55-CB25</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CC60" s="32">
-        <f>CC16-CC55</f>
+        <f>CC16-CC55-CC25</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CD60" s="32">
-        <f>CD16-CD55</f>
+        <f>CD16-CD55-CD25</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CE60" s="32">
-        <f>CE16-CE55</f>
+        <f>CE16-CE55-CE25</f>
         <v>3090.400740930274</v>
       </c>
       <c r="CF60" s="32">
-        <f>CF16-CF55</f>
+        <f>CF16-CF55-CF25</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CG60" s="32">
-        <f>CG16-CG55</f>
+        <f>CG16-CG55-CG25</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CH60" s="32">
-        <f>CH16-CH55</f>
+        <f>CH16-CH55-CH25</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CI60" s="32">
-        <f>CI16-CI55</f>
+        <f>CI16-CI55-CI25</f>
         <v>3061.5232063707645</v>
       </c>
       <c r="CJ60" s="32">
-        <f>CJ16-CJ55</f>
+        <f>CJ16-CJ55-CJ25</f>
         <v>3193.8188300401507</v>
       </c>
       <c r="CK60" s="32">
-        <f>CK16-CK55</f>
+        <f>CK16-CK55-CK25</f>
         <v>3193.8188300401507</v>
       </c>
       <c r="CL60" s="32">
-        <f>CL16-CL55</f>
+        <f>CL16-CL55-CL25</f>
         <v>3800.288402540151</v>
       </c>
     </row>
     <row r="61" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E61" s="32">
-        <f>-E55-('Debt'!E15+'Debt'!E16)+'Debt'!E45+'Debt'!E46+E16</f>
+        <f>-E55-E25-('Debt'!E15+'Debt'!E16)+'Debt'!E45+'Debt'!E46+E16</f>
         <v>-14106.900000000005</v>
       </c>
       <c r="F61" s="32">
-        <f>-F55-('Debt'!F15-'Debt'!E15+'Debt'!F16-'Debt'!E16)+'Debt'!F45+'Debt'!F46+F16</f>
+        <f>-F55-F25-('Debt'!F15-'Debt'!E15+'Debt'!F16-'Debt'!E16)+'Debt'!F45+'Debt'!F46+F16</f>
         <v>-21160.35000000001</v>
       </c>
       <c r="G61" s="32">
-        <f>-G55-('Debt'!G15-'Debt'!F15+'Debt'!G16-'Debt'!F16)+'Debt'!G45+'Debt'!G46+G16</f>
+        <f>-G55-G25-('Debt'!G15-'Debt'!F15+'Debt'!G16-'Debt'!F16)+'Debt'!G45+'Debt'!G46+G16</f>
         <v>-28495.64823415511</v>
       </c>
       <c r="H61" s="32">
-        <f>-H55-('Debt'!H15-'Debt'!G15+'Debt'!H16-'Debt'!G16)+'Debt'!H45+'Debt'!H46+H16</f>
+        <f>-H55-H25-('Debt'!H15-'Debt'!G15+'Debt'!H16-'Debt'!G16)+'Debt'!H45+'Debt'!H46+H16</f>
         <v>-35945.4340539314</v>
       </c>
       <c r="I61" s="32">
-        <f>-I55-('Debt'!I15-'Debt'!H15+'Debt'!I16-'Debt'!H16)+'Debt'!I45+'Debt'!I46+I16</f>
+        <f>-I55-I25-('Debt'!I15-'Debt'!H15+'Debt'!I16-'Debt'!H16)+'Debt'!I45+'Debt'!I46+I16</f>
         <v>-29391.936290704965</v>
       </c>
       <c r="J61" s="32">
-        <f>-J55-('Debt'!J15-'Debt'!I15+'Debt'!J16-'Debt'!I16)+'Debt'!J45+'Debt'!J46+J16+'Debt'!D12</f>
+        <f>-J55-J25-('Debt'!J15-'Debt'!I15+'Debt'!J16-'Debt'!I16)+'Debt'!J45+'Debt'!J46+J16+'Debt'!D12</f>
         <v>-16968.624580657943</v>
       </c>
       <c r="K61" s="32">
-        <f>-K55-('Debt'!K15-'Debt'!J15+'Debt'!K16-'Debt'!J16)+'Debt'!K45+'Debt'!K46+K16</f>
+        <f>-K55-K25-('Debt'!K15-'Debt'!J15+'Debt'!K16-'Debt'!J16)+'Debt'!K45+'Debt'!K46+K16</f>
         <v>1874.7599999999998</v>
       </c>
       <c r="L61" s="32">
-        <f>-L55-('Debt'!L15-'Debt'!K15+'Debt'!L16-'Debt'!K16)+'Debt'!L45+'Debt'!L46+L16</f>
+        <f>-L55-L25-('Debt'!L15-'Debt'!K15+'Debt'!L16-'Debt'!K16)+'Debt'!L45+'Debt'!L46+L16</f>
         <v>1874.7599999999998</v>
       </c>
       <c r="M61" s="32">
-        <f>-M55-('Debt'!M15-'Debt'!L15+'Debt'!M16-'Debt'!L16)+'Debt'!M45+'Debt'!M46+M16</f>
+        <f>-M55-M25-('Debt'!M15-'Debt'!L15+'Debt'!M16-'Debt'!L16)+'Debt'!M45+'Debt'!M46+M16</f>
         <v>1874.7599999999998</v>
       </c>
       <c r="N61" s="32">
-        <f>-N55-('Debt'!N15-'Debt'!M15+'Debt'!N16-'Debt'!M16)+'Debt'!N45+'Debt'!N46+N16</f>
+        <f>-N55-N25-('Debt'!N15-'Debt'!M15+'Debt'!N16-'Debt'!M16)+'Debt'!N45+'Debt'!N46+N16</f>
         <v>1874.7599999999998</v>
       </c>
       <c r="O61" s="32">
-        <f>-O55-('Debt'!O15-'Debt'!N15+'Debt'!O16-'Debt'!N16)+'Debt'!O45+'Debt'!O46+O16</f>
+        <f>-O55-O25-('Debt'!O15-'Debt'!N15+'Debt'!O16-'Debt'!N16)+'Debt'!O45+'Debt'!O46+O16</f>
         <v>3980.8693749999998</v>
       </c>
       <c r="P61" s="32">
-        <f>-P55-('Debt'!P15-'Debt'!O15+'Debt'!P16-'Debt'!O16)+'Debt'!P45+'Debt'!P46+P16</f>
+        <f>-P55-P25-('Debt'!P15-'Debt'!O15+'Debt'!P16-'Debt'!O16)+'Debt'!P45+'Debt'!P46+P16</f>
         <v>3951.57625</v>
       </c>
       <c r="Q61" s="32">
-        <f>-Q55-('Debt'!Q15-'Debt'!P15+'Debt'!Q16-'Debt'!P16)+'Debt'!Q45+'Debt'!Q46+Q16</f>
+        <f>-Q55-Q25-('Debt'!Q15-'Debt'!P15+'Debt'!Q16-'Debt'!P16)+'Debt'!Q45+'Debt'!Q46+Q16</f>
         <v>3922.283125</v>
       </c>
       <c r="R61" s="32">
-        <f>-R55-('Debt'!R15-'Debt'!Q15+'Debt'!R16-'Debt'!Q16)+'Debt'!R45+'Debt'!R46+R16</f>
+        <f>-R55-R25-('Debt'!R15-'Debt'!Q15+'Debt'!R16-'Debt'!Q16)+'Debt'!R45+'Debt'!R46+R16</f>
         <v>3892.99</v>
       </c>
       <c r="S61" s="32">
-        <f>-S55-('Debt'!S15-'Debt'!R15+'Debt'!S16-'Debt'!R16)+'Debt'!S45+'Debt'!S46+S16</f>
+        <f>-S55-S25-('Debt'!S15-'Debt'!R15+'Debt'!S16-'Debt'!R16)+'Debt'!S45+'Debt'!S46+S16</f>
         <v>3863.6968749999996</v>
       </c>
       <c r="T61" s="32">
-        <f>-T55-('Debt'!T15-'Debt'!S15+'Debt'!T16-'Debt'!S16)+'Debt'!T45+'Debt'!T46+T16</f>
+        <f>-T55-T25-('Debt'!T15-'Debt'!S15+'Debt'!T16-'Debt'!S16)+'Debt'!T45+'Debt'!T46+T16</f>
         <v>3834.40375</v>
       </c>
       <c r="U61" s="32">
-        <f>-U55-('Debt'!U15-'Debt'!T15+'Debt'!U16-'Debt'!T16)+'Debt'!U45+'Debt'!U46+U16</f>
+        <f>-U55-U25-('Debt'!U15-'Debt'!T15+'Debt'!U16-'Debt'!T16)+'Debt'!U45+'Debt'!U46+U16</f>
         <v>3805.1106250000003</v>
       </c>
       <c r="V61" s="32">
-        <f>-V55-('Debt'!V15-'Debt'!U15+'Debt'!V16-'Debt'!U16)+'Debt'!V45+'Debt'!V46+V16</f>
+        <f>-V55-V25-('Debt'!V15-'Debt'!U15+'Debt'!V16-'Debt'!U16)+'Debt'!V45+'Debt'!V46+V16</f>
         <v>3775.8175</v>
       </c>
       <c r="W61" s="32">
-        <f>-W55-('Debt'!W15-'Debt'!V15+'Debt'!W16-'Debt'!V16)+'Debt'!W45+'Debt'!W46+W16</f>
+        <f>-W55-W25-('Debt'!W15-'Debt'!V15+'Debt'!W16-'Debt'!V16)+'Debt'!W45+'Debt'!W46+W16</f>
         <v>3746.524375</v>
       </c>
       <c r="X61" s="32">
-        <f>-X55-('Debt'!X15-'Debt'!W15+'Debt'!X16-'Debt'!W16)+'Debt'!X45+'Debt'!X46+X16</f>
+        <f>-X55-X25-('Debt'!X15-'Debt'!W15+'Debt'!X16-'Debt'!W16)+'Debt'!X45+'Debt'!X46+X16</f>
         <v>3717.23125</v>
       </c>
       <c r="Y61" s="32">
-        <f>-Y55-('Debt'!Y15-'Debt'!X15+'Debt'!Y16-'Debt'!X16)+'Debt'!Y45+'Debt'!Y46+Y16</f>
+        <f>-Y55-Y25-('Debt'!Y15-'Debt'!X15+'Debt'!Y16-'Debt'!X16)+'Debt'!Y45+'Debt'!Y46+Y16</f>
         <v>3687.9381249999997</v>
       </c>
       <c r="Z61" s="32">
-        <f>-Z55-('Debt'!Z15-'Debt'!Y15+'Debt'!Z16-'Debt'!Y16)+'Debt'!Z45+'Debt'!Z46+Z16</f>
+        <f>-Z55-Z25-('Debt'!Z15-'Debt'!Y15+'Debt'!Z16-'Debt'!Y16)+'Debt'!Z45+'Debt'!Z46+Z16</f>
         <v>3658.645</v>
       </c>
       <c r="AA61" s="32">
-        <f>-AA55-('Debt'!AA15-'Debt'!Z15+'Debt'!AA16-'Debt'!Z16)+'Debt'!AA45+'Debt'!AA46+AA16</f>
+        <f>-AA55-AA25-('Debt'!AA15-'Debt'!Z15+'Debt'!AA16-'Debt'!Z16)+'Debt'!AA45+'Debt'!AA46+AA16</f>
         <v>3629.351875</v>
       </c>
       <c r="AB61" s="32">
-        <f>-AB55-('Debt'!AB15-'Debt'!AA15+'Debt'!AB16-'Debt'!AA16)+'Debt'!AB45+'Debt'!AB46+AB16</f>
+        <f>-AB55-AB25-('Debt'!AB15-'Debt'!AA15+'Debt'!AB16-'Debt'!AA16)+'Debt'!AB45+'Debt'!AB46+AB16</f>
         <v>3600.0587499999997</v>
       </c>
       <c r="AC61" s="32">
-        <f>-AC55-('Debt'!AC15-'Debt'!AB15+'Debt'!AC16-'Debt'!AB16)+'Debt'!AC45+'Debt'!AC46+AC16</f>
+        <f>-AC55-AC25-('Debt'!AC15-'Debt'!AB15+'Debt'!AC16-'Debt'!AB16)+'Debt'!AC45+'Debt'!AC46+AC16</f>
         <v>3570.765625</v>
       </c>
       <c r="AD61" s="32">
-        <f>-AD55-('Debt'!AD15-'Debt'!AC15+'Debt'!AD16-'Debt'!AC16)+'Debt'!AD45+'Debt'!AD46+AD16</f>
+        <f>-AD55-AD25-('Debt'!AD15-'Debt'!AC15+'Debt'!AD16-'Debt'!AC16)+'Debt'!AD45+'Debt'!AD46+AD16</f>
         <v>3541.4725</v>
       </c>
       <c r="AE61" s="32">
-        <f>-AE55-('Debt'!AE15-'Debt'!AD15+'Debt'!AE16-'Debt'!AD16)+'Debt'!AE45+'Debt'!AE46+AE16</f>
+        <f>-AE55-AE25-('Debt'!AE15-'Debt'!AD15+'Debt'!AE16-'Debt'!AD16)+'Debt'!AE45+'Debt'!AE46+AE16</f>
         <v>3512.1793749999997</v>
       </c>
       <c r="AF61" s="32">
-        <f>-AF55-('Debt'!AF15-'Debt'!AE15+'Debt'!AF16-'Debt'!AE16)+'Debt'!AF45+'Debt'!AF46+AF16</f>
+        <f>-AF55-AF25-('Debt'!AF15-'Debt'!AE15+'Debt'!AF16-'Debt'!AE16)+'Debt'!AF45+'Debt'!AF46+AF16</f>
         <v>3482.8862499999996</v>
       </c>
       <c r="AG61" s="32">
-        <f>-AG55-('Debt'!AG15-'Debt'!AF15+'Debt'!AG16-'Debt'!AF16)+'Debt'!AG45+'Debt'!AG46+AG16</f>
+        <f>-AG55-AG25-('Debt'!AG15-'Debt'!AF15+'Debt'!AG16-'Debt'!AF16)+'Debt'!AG45+'Debt'!AG46+AG16</f>
         <v>3453.593125</v>
       </c>
       <c r="AH61" s="32">
-        <f>-AH55-('Debt'!AH15-'Debt'!AG15+'Debt'!AH16-'Debt'!AG16)+'Debt'!AH45+'Debt'!AH46+AH16</f>
+        <f>-AH55-AH25-('Debt'!AH15-'Debt'!AG15+'Debt'!AH16-'Debt'!AG16)+'Debt'!AH45+'Debt'!AH46+AH16</f>
         <v>3424.3</v>
       </c>
       <c r="AI61" s="32">
-        <f>-AI55-('Debt'!AI15-'Debt'!AH15+'Debt'!AI16-'Debt'!AH16)+'Debt'!AI45+'Debt'!AI46+AI16</f>
+        <f>-AI55-AI25-('Debt'!AI15-'Debt'!AH15+'Debt'!AI16-'Debt'!AH16)+'Debt'!AI45+'Debt'!AI46+AI16</f>
         <v>3395.006875</v>
       </c>
       <c r="AJ61" s="32">
-        <f>-AJ55-('Debt'!AJ15-'Debt'!AI15+'Debt'!AJ16-'Debt'!AI16)+'Debt'!AJ45+'Debt'!AJ46+AJ16</f>
+        <f>-AJ55-AJ25-('Debt'!AJ15-'Debt'!AI15+'Debt'!AJ16-'Debt'!AI16)+'Debt'!AJ45+'Debt'!AJ46+AJ16</f>
         <v>3365.71375</v>
       </c>
       <c r="AK61" s="32">
-        <f>-AK55-('Debt'!AK15-'Debt'!AJ15+'Debt'!AK16-'Debt'!AJ16)+'Debt'!AK45+'Debt'!AK46+AK16</f>
+        <f>-AK55-AK25-('Debt'!AK15-'Debt'!AJ15+'Debt'!AK16-'Debt'!AJ16)+'Debt'!AK45+'Debt'!AK46+AK16</f>
         <v>3336.4206249999997</v>
       </c>
       <c r="AL61" s="32">
-        <f>-AL55-('Debt'!AL15-'Debt'!AK15+'Debt'!AL16-'Debt'!AK16)+'Debt'!AL45+'Debt'!AL46+AL16</f>
+        <f>-AL55-AL25-('Debt'!AL15-'Debt'!AK15+'Debt'!AL16-'Debt'!AK16)+'Debt'!AL45+'Debt'!AL46+AL16</f>
         <v>3307.1275</v>
       </c>
       <c r="AM61" s="32">
-        <f>-AM55-('Debt'!AM15-'Debt'!AL15+'Debt'!AM16-'Debt'!AL16)+'Debt'!AM45+'Debt'!AM46+AM16</f>
+        <f>-AM55-AM25-('Debt'!AM15-'Debt'!AL15+'Debt'!AM16-'Debt'!AL16)+'Debt'!AM45+'Debt'!AM46+AM16</f>
         <v>3277.834375</v>
       </c>
       <c r="AN61" s="32">
-        <f>-AN55-('Debt'!AN15-'Debt'!AM15+'Debt'!AN16-'Debt'!AM16)+'Debt'!AN45+'Debt'!AN46+AN16</f>
+        <f>-AN55-AN25-('Debt'!AN15-'Debt'!AM15+'Debt'!AN16-'Debt'!AM16)+'Debt'!AN45+'Debt'!AN46+AN16</f>
         <v>3248.5412499999998</v>
       </c>
       <c r="AO61" s="32">
-        <f>-AO55-('Debt'!AO15-'Debt'!AN15+'Debt'!AO16-'Debt'!AN16)+'Debt'!AO45+'Debt'!AO46+AO16</f>
+        <f>-AO55-AO25-('Debt'!AO15-'Debt'!AN15+'Debt'!AO16-'Debt'!AN16)+'Debt'!AO45+'Debt'!AO46+AO16</f>
         <v>3219.248125</v>
       </c>
       <c r="AP61" s="32">
-        <f>-AP55-('Debt'!AP15-'Debt'!AO15+'Debt'!AP16-'Debt'!AO16)+'Debt'!AP45+'Debt'!AP46+AP16</f>
+        <f>-AP55-AP25-('Debt'!AP15-'Debt'!AO15+'Debt'!AP16-'Debt'!AO16)+'Debt'!AP45+'Debt'!AP46+AP16</f>
         <v>3189.955</v>
       </c>
       <c r="AQ61" s="32">
-        <f>-AQ55-('Debt'!AQ15-'Debt'!AP15+'Debt'!AQ16-'Debt'!AP16)+'Debt'!AQ45+'Debt'!AQ46+AQ16</f>
+        <f>-AQ55-AQ25-('Debt'!AQ15-'Debt'!AP15+'Debt'!AQ16-'Debt'!AP16)+'Debt'!AQ45+'Debt'!AQ46+AQ16</f>
         <v>3160.661875</v>
       </c>
       <c r="AR61" s="32">
-        <f>-AR55-('Debt'!AR15-'Debt'!AQ15+'Debt'!AR16-'Debt'!AQ16)+'Debt'!AR45+'Debt'!AR46+AR16</f>
+        <f>-AR55-AR25-('Debt'!AR15-'Debt'!AQ15+'Debt'!AR16-'Debt'!AQ16)+'Debt'!AR45+'Debt'!AR46+AR16</f>
         <v>3131.3687499999996</v>
       </c>
       <c r="AS61" s="32">
-        <f>-AS55-('Debt'!AS15-'Debt'!AR15+'Debt'!AS16-'Debt'!AR16)+'Debt'!AS45+'Debt'!AS46+AS16</f>
+        <f>-AS55-AS25-('Debt'!AS15-'Debt'!AR15+'Debt'!AS16-'Debt'!AR16)+'Debt'!AS45+'Debt'!AS46+AS16</f>
         <v>3102.075625</v>
       </c>
       <c r="AT61" s="32">
-        <f>-AT55-('Debt'!AT15-'Debt'!AS15+'Debt'!AT16-'Debt'!AS16)+'Debt'!AT45+'Debt'!AT46+AT16</f>
+        <f>-AT55-AT25-('Debt'!AT15-'Debt'!AS15+'Debt'!AT16-'Debt'!AS16)+'Debt'!AT45+'Debt'!AT46+AT16</f>
         <v>3072.7825000000003</v>
       </c>
       <c r="AU61" s="32">
-        <f>-AU55-('Debt'!AU15-'Debt'!AT15+'Debt'!AU16-'Debt'!AT16)+'Debt'!AU45+'Debt'!AU46+AU16</f>
+        <f>-AU55-AU25-('Debt'!AU15-'Debt'!AT15+'Debt'!AU16-'Debt'!AT16)+'Debt'!AU45+'Debt'!AU46+AU16</f>
         <v>3043.489375</v>
       </c>
       <c r="AV61" s="32">
-        <f>-AV55-('Debt'!AV15-'Debt'!AU15+'Debt'!AV16-'Debt'!AU16)+'Debt'!AV45+'Debt'!AV46+AV16</f>
+        <f>-AV55-AV25-('Debt'!AV15-'Debt'!AU15+'Debt'!AV16-'Debt'!AU16)+'Debt'!AV45+'Debt'!AV46+AV16</f>
         <v>3014.19625</v>
       </c>
       <c r="AW61" s="32">
-        <f>-AW55-('Debt'!AW15-'Debt'!AV15+'Debt'!AW16-'Debt'!AV16)+'Debt'!AW45+'Debt'!AW46+AW16</f>
+        <f>-AW55-AW25-('Debt'!AW15-'Debt'!AV15+'Debt'!AW16-'Debt'!AV16)+'Debt'!AW45+'Debt'!AW46+AW16</f>
         <v>2984.903125</v>
       </c>
       <c r="AX61" s="32">
-        <f>-AX55-('Debt'!AX15-'Debt'!AW15+'Debt'!AX16-'Debt'!AW16)+'Debt'!AX45+'Debt'!AX46+AX16</f>
+        <f>-AX55-AX25-('Debt'!AX15-'Debt'!AW15+'Debt'!AX16-'Debt'!AW16)+'Debt'!AX45+'Debt'!AX46+AX16</f>
         <v>2955.61</v>
       </c>
       <c r="AY61" s="32">
-        <f>-AY55-('Debt'!AY15-'Debt'!AX15+'Debt'!AY16-'Debt'!AX16)+'Debt'!AY45+'Debt'!AY46+AY16</f>
+        <f>-AY55-AY25-('Debt'!AY15-'Debt'!AX15+'Debt'!AY16-'Debt'!AX16)+'Debt'!AY45+'Debt'!AY46+AY16</f>
         <v>2926.316875</v>
       </c>
       <c r="AZ61" s="32">
-        <f>-AZ55-('Debt'!AZ15-'Debt'!AY15+'Debt'!AZ16-'Debt'!AY16)+'Debt'!AZ45+'Debt'!AZ46+AZ16</f>
+        <f>-AZ55-AZ25-('Debt'!AZ15-'Debt'!AY15+'Debt'!AZ16-'Debt'!AY16)+'Debt'!AZ45+'Debt'!AZ46+AZ16</f>
         <v>2897.02375</v>
       </c>
       <c r="BA61" s="32">
-        <f>-BA55-('Debt'!BA15-'Debt'!AZ15+'Debt'!BA16-'Debt'!AZ16)+'Debt'!BA45+'Debt'!BA46+BA16</f>
+        <f>-BA55-BA25-('Debt'!BA15-'Debt'!AZ15+'Debt'!BA16-'Debt'!AZ16)+'Debt'!BA45+'Debt'!BA46+BA16</f>
         <v>2867.730625</v>
       </c>
       <c r="BB61" s="32">
-        <f>-BB55-('Debt'!BB15-'Debt'!BA15+'Debt'!BB16-'Debt'!BA16)+'Debt'!BB45+'Debt'!BB46+BB16</f>
+        <f>-BB55-BB25-('Debt'!BB15-'Debt'!BA15+'Debt'!BB16-'Debt'!BA16)+'Debt'!BB45+'Debt'!BB46+BB16</f>
         <v>2838.4375</v>
       </c>
       <c r="BC61" s="32">
-        <f>-BC55-('Debt'!BC15-'Debt'!BB15+'Debt'!BC16-'Debt'!BB16)+'Debt'!BC45+'Debt'!BC46+BC16</f>
+        <f>-BC55-BC25-('Debt'!BC15-'Debt'!BB15+'Debt'!BC16-'Debt'!BB16)+'Debt'!BC45+'Debt'!BC46+BC16</f>
         <v>2809.144375</v>
       </c>
       <c r="BD61" s="32">
-        <f>-BD55-('Debt'!BD15-'Debt'!BC15+'Debt'!BD16-'Debt'!BC16)+'Debt'!BD45+'Debt'!BD46+BD16</f>
+        <f>-BD55-BD25-('Debt'!BD15-'Debt'!BC15+'Debt'!BD16-'Debt'!BC16)+'Debt'!BD45+'Debt'!BD46+BD16</f>
         <v>2779.8512499999997</v>
       </c>
       <c r="BE61" s="32">
-        <f>-BE55-('Debt'!BE15-'Debt'!BD15+'Debt'!BE16-'Debt'!BD16)+'Debt'!BE45+'Debt'!BE46+BE16</f>
+        <f>-BE55-BE25-('Debt'!BE15-'Debt'!BD15+'Debt'!BE16-'Debt'!BD16)+'Debt'!BE45+'Debt'!BE46+BE16</f>
         <v>2750.558125</v>
       </c>
       <c r="BF61" s="32">
-        <f>-BF55-('Debt'!BF15-'Debt'!BE15+'Debt'!BF16-'Debt'!BE16)+'Debt'!BF45+'Debt'!BF46+BF16</f>
+        <f>-BF55-BF25-('Debt'!BF15-'Debt'!BE15+'Debt'!BF16-'Debt'!BE16)+'Debt'!BF45+'Debt'!BF46+BF16</f>
         <v>2721.265</v>
       </c>
       <c r="BG61" s="32">
-        <f>-BG55-('Debt'!BG15-'Debt'!BF15+'Debt'!BG16-'Debt'!BF16)+'Debt'!BG45+'Debt'!BG46+BG16</f>
+        <f>-BG55-BG25-('Debt'!BG15-'Debt'!BF15+'Debt'!BG16-'Debt'!BF16)+'Debt'!BG45+'Debt'!BG46+BG16</f>
         <v>2691.971875</v>
       </c>
       <c r="BH61" s="32">
-        <f>-BH55-('Debt'!BH15-'Debt'!BG15+'Debt'!BH16-'Debt'!BG16)+'Debt'!BH45+'Debt'!BH46+BH16</f>
+        <f>-BH55-BH25-('Debt'!BH15-'Debt'!BG15+'Debt'!BH16-'Debt'!BG16)+'Debt'!BH45+'Debt'!BH46+BH16</f>
         <v>2662.67875</v>
       </c>
       <c r="BI61" s="32">
-        <f>-BI55-('Debt'!BI15-'Debt'!BH15+'Debt'!BI16-'Debt'!BH16)+'Debt'!BI45+'Debt'!BI46+BI16</f>
+        <f>-BI55-BI25-('Debt'!BI15-'Debt'!BH15+'Debt'!BI16-'Debt'!BH16)+'Debt'!BI45+'Debt'!BI46+BI16</f>
         <v>2633.385625</v>
       </c>
       <c r="BJ61" s="32">
-        <f>-BJ55-('Debt'!BJ15-'Debt'!BI15+'Debt'!BJ16-'Debt'!BI16)+'Debt'!BJ45+'Debt'!BJ46+BJ16</f>
+        <f>-BJ55-BJ25-('Debt'!BJ15-'Debt'!BI15+'Debt'!BJ16-'Debt'!BI16)+'Debt'!BJ45+'Debt'!BJ46+BJ16</f>
         <v>2604.0924999999997</v>
       </c>
       <c r="BK61" s="32">
-        <f>-BK55-('Debt'!BK15-'Debt'!BJ15+'Debt'!BK16-'Debt'!BJ16)+'Debt'!BK45+'Debt'!BK46+BK16</f>
+        <f>-BK55-BK25-('Debt'!BK15-'Debt'!BJ15+'Debt'!BK16-'Debt'!BJ16)+'Debt'!BK45+'Debt'!BK46+BK16</f>
         <v>2574.799375</v>
       </c>
       <c r="BL61" s="32">
-        <f>-BL55-('Debt'!BL15-'Debt'!BK15+'Debt'!BL16-'Debt'!BK16)+'Debt'!BL45+'Debt'!BL46+BL16</f>
+        <f>-BL55-BL25-('Debt'!BL15-'Debt'!BK15+'Debt'!BL16-'Debt'!BK16)+'Debt'!BL45+'Debt'!BL46+BL16</f>
         <v>27375.723080009728</v>
       </c>
       <c r="BM61" s="32">
-        <f>-BM55-('Debt'!BM15-'Debt'!BL15+'Debt'!BM16-'Debt'!BL16)+'Debt'!BM45+'Debt'!BM46+BM16</f>
+        <f>-BM55-BM25-('Debt'!BM15-'Debt'!BL15+'Debt'!BM16-'Debt'!BL16)+'Debt'!BM45+'Debt'!BM46+BM16</f>
         <v>3369.406192003235</v>
       </c>
       <c r="BN61" s="32">
-        <f>-BN55-('Debt'!BN15-'Debt'!BM15+'Debt'!BN16-'Debt'!BM16)+'Debt'!BN45+'Debt'!BN46+BN16</f>
+        <f>-BN55-BN25-('Debt'!BN15-'Debt'!BM15+'Debt'!BN16-'Debt'!BM16)+'Debt'!BN45+'Debt'!BN46+BN16</f>
         <v>3363.2894198627455</v>
       </c>
       <c r="BO61" s="32">
-        <f>-BO55-('Debt'!BO15-'Debt'!BN15+'Debt'!BO16-'Debt'!BN16)+'Debt'!BO45+'Debt'!BO46+BO16</f>
+        <f>-BO55-BO25-('Debt'!BO15-'Debt'!BN15+'Debt'!BO16-'Debt'!BN16)+'Debt'!BO45+'Debt'!BO46+BO16</f>
         <v>3337.431860650441</v>
       </c>
       <c r="BP61" s="32">
-        <f>-BP55-('Debt'!BP15-'Debt'!BO15+'Debt'!BP16-'Debt'!BO16)+'Debt'!BP45+'Debt'!BP46+BP16</f>
+        <f>-BP55-BP25-('Debt'!BP15-'Debt'!BO15+'Debt'!BP16-'Debt'!BO16)+'Debt'!BP45+'Debt'!BP46+BP16</f>
         <v>3322.424727090719</v>
       </c>
       <c r="BQ61" s="32">
-        <f>-BQ55-('Debt'!BQ15-'Debt'!BP15+'Debt'!BQ16-'Debt'!BP16)+'Debt'!BQ45+'Debt'!BQ46+BQ16</f>
+        <f>-BQ55-BQ25-('Debt'!BQ15-'Debt'!BP15+'Debt'!BQ16-'Debt'!BP16)+'Debt'!BQ45+'Debt'!BQ46+BQ16</f>
         <v>3316.3076676863334</v>
       </c>
       <c r="BR61" s="32">
-        <f>-BR55-('Debt'!BR15-'Debt'!BQ15+'Debt'!BR16-'Debt'!BQ16)+'Debt'!BR45+'Debt'!BR46+BR16</f>
+        <f>-BR55-BR25-('Debt'!BR15-'Debt'!BQ15+'Debt'!BR16-'Debt'!BQ16)+'Debt'!BR45+'Debt'!BR46+BR16</f>
         <v>3310.190608281946</v>
       </c>
       <c r="BS61" s="32">
-        <f>-BS55-('Debt'!BS15-'Debt'!BR15+'Debt'!BS16-'Debt'!BR16)+'Debt'!BS45+'Debt'!BS46+BS16</f>
+        <f>-BS55-BS25-('Debt'!BS15-'Debt'!BR15+'Debt'!BS16-'Debt'!BR16)+'Debt'!BS45+'Debt'!BS46+BS16</f>
         <v>3284.2802692265186</v>
       </c>
       <c r="BT61" s="32">
-        <f>-BT55-('Debt'!BT15-'Debt'!BS15+'Debt'!BT16-'Debt'!BS16)+'Debt'!BT45+'Debt'!BT46+BT16</f>
+        <f>-BT55-BT25-('Debt'!BT15-'Debt'!BS15+'Debt'!BT16-'Debt'!BS16)+'Debt'!BT45+'Debt'!BT46+BT16</f>
         <v>3269.2736200897416</v>
       </c>
       <c r="BU61" s="32">
-        <f>-BU55-('Debt'!BU15-'Debt'!BT15+'Debt'!BU16-'Debt'!BT16)+'Debt'!BU45+'Debt'!BU46+BU16</f>
+        <f>-BU55-BU25-('Debt'!BU15-'Debt'!BT15+'Debt'!BU16-'Debt'!BT16)+'Debt'!BU45+'Debt'!BU46+BU16</f>
         <v>3263.1563021870606</v>
       </c>
       <c r="BV61" s="32">
-        <f>-BV55-('Debt'!BV15-'Debt'!BU15+'Debt'!BV16-'Debt'!BU16)+'Debt'!BV45+'Debt'!BV46+BV16</f>
+        <f>-BV55-BV25-('Debt'!BV15-'Debt'!BU15+'Debt'!BV16-'Debt'!BU16)+'Debt'!BV45+'Debt'!BV46+BV16</f>
         <v>3257.038984284379</v>
       </c>
       <c r="BW61" s="32">
-        <f>-BW55-('Debt'!BW15-'Debt'!BV15+'Debt'!BW16-'Debt'!BV16)+'Debt'!BW45+'Debt'!BW46+BW16</f>
+        <f>-BW55-BW25-('Debt'!BW15-'Debt'!BV15+'Debt'!BW16-'Debt'!BV16)+'Debt'!BW45+'Debt'!BW46+BW16</f>
         <v>3231.0754898860805</v>
       </c>
       <c r="BX61" s="32">
-        <f>-BX55-('Debt'!BX15-'Debt'!BW15+'Debt'!BX16-'Debt'!BW16)+'Debt'!BX45+'Debt'!BX46+BX16</f>
+        <f>-BX55-BX25-('Debt'!BX15-'Debt'!BW15+'Debt'!BX16-'Debt'!BW16)+'Debt'!BX45+'Debt'!BX46+BX16</f>
         <v>3216.069278232581</v>
       </c>
       <c r="BY61" s="32">
-        <f>-BY55-('Debt'!BY15-'Debt'!BX15+'Debt'!BY16-'Debt'!BX16)+'Debt'!BY45+'Debt'!BY46+BY16</f>
+        <f>-BY55-BY25-('Debt'!BY15-'Debt'!BX15+'Debt'!BY16-'Debt'!BX16)+'Debt'!BY45+'Debt'!BY46+BY16</f>
         <v>5316.061101484016</v>
       </c>
       <c r="BZ61" s="32">
-        <f>-BZ55-('Debt'!BZ15-'Debt'!BY15+'Debt'!BZ16-'Debt'!BY16)+'Debt'!BZ45+'Debt'!BZ46+BZ16</f>
+        <f>-BZ55-BZ25-('Debt'!BZ15-'Debt'!BY15+'Debt'!BZ16-'Debt'!BY16)+'Debt'!BZ45+'Debt'!BZ46+BZ16</f>
         <v>5280.650424735448</v>
       </c>
       <c r="CA61" s="32">
-        <f>-CA55-('Debt'!CA15-'Debt'!BZ15+'Debt'!CA16-'Debt'!BZ16)+'Debt'!CA45+'Debt'!CA46+CA16</f>
+        <f>-CA55-CA25-('Debt'!CA15-'Debt'!BZ15+'Debt'!CA16-'Debt'!BZ16)+'Debt'!CA45+'Debt'!CA46+CA16</f>
         <v>3119.230897713078</v>
       </c>
       <c r="CB61" s="32">
-        <f>-CB55-('Debt'!CB15-'Debt'!CA15+'Debt'!CB16-'Debt'!CA16)+'Debt'!CB45+'Debt'!CB46+CB16</f>
+        <f>-CB55-CB25-('Debt'!CB15-'Debt'!CA15+'Debt'!CB16-'Debt'!CA16)+'Debt'!CB45+'Debt'!CB46+CB16</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CC61" s="32">
-        <f>-CC55-('Debt'!CC15-'Debt'!CB15+'Debt'!CC16-'Debt'!CB16)+'Debt'!CC45+'Debt'!CC46+CC16</f>
+        <f>-CC55-CC25-('Debt'!CC15-'Debt'!CB15+'Debt'!CC16-'Debt'!CB16)+'Debt'!CC45+'Debt'!CC46+CC16</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CD61" s="32">
-        <f>-CD55-('Debt'!CD15-'Debt'!CC15+'Debt'!CD16-'Debt'!CC16)+'Debt'!CD45+'Debt'!CD46+CD16</f>
+        <f>-CD55-CD25-('Debt'!CD15-'Debt'!CC15+'Debt'!CD16-'Debt'!CC16)+'Debt'!CD45+'Debt'!CD46+CD16</f>
         <v>3110.3541541349086</v>
       </c>
       <c r="CE61" s="32">
-        <f>-CE55-('Debt'!CE15-'Debt'!CD15+'Debt'!CE16-'Debt'!CD16)+'Debt'!CE45+'Debt'!CE46+CE16</f>
+        <f>-CE55-CE25-('Debt'!CE15-'Debt'!CD15+'Debt'!CE16-'Debt'!CD16)+'Debt'!CE45+'Debt'!CE46+CE16</f>
         <v>3090.400740930274</v>
       </c>
       <c r="CF61" s="32">
-        <f>-CF55-('Debt'!CF15-'Debt'!CE15+'Debt'!CF16-'Debt'!CE16)+'Debt'!CF45+'Debt'!CF46+CF16</f>
+        <f>-CF55-CF25-('Debt'!CF15-'Debt'!CE15+'Debt'!CF16-'Debt'!CE16)+'Debt'!CF45+'Debt'!CF46+CF16</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CG61" s="32">
-        <f>-CG55-('Debt'!CG15-'Debt'!CF15+'Debt'!CG16-'Debt'!CF16)+'Debt'!CG45+'Debt'!CG46+CG16</f>
+        <f>-CG55-CG25-('Debt'!CG15-'Debt'!CF15+'Debt'!CG16-'Debt'!CF16)+'Debt'!CG45+'Debt'!CG46+CG16</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CH61" s="32">
-        <f>-CH55-('Debt'!CH15-'Debt'!CG15+'Debt'!CH16-'Debt'!CG16)+'Debt'!CH45+'Debt'!CH46+CH16</f>
+        <f>-CH55-CH25-('Debt'!CH15-'Debt'!CG15+'Debt'!CH16-'Debt'!CG16)+'Debt'!CH45+'Debt'!CH46+CH16</f>
         <v>3081.5310877618454</v>
       </c>
       <c r="CI61" s="32">
-        <f>-CI55-('Debt'!CI15-'Debt'!CH15+'Debt'!CI16-'Debt'!CH16)+'Debt'!CI45+'Debt'!CI46+CI16</f>
+        <f>-CI55-CI25-('Debt'!CI15-'Debt'!CH15+'Debt'!CI16-'Debt'!CH16)+'Debt'!CI45+'Debt'!CI46+CI16</f>
         <v>3061.5232063707645</v>
       </c>
       <c r="CJ61" s="32">
-        <f>-CJ55-('Debt'!CJ15-'Debt'!CI15+'Debt'!CJ16-'Debt'!CI16)+'Debt'!CJ45+'Debt'!CJ46+CJ16</f>
+        <f>-CJ55-CJ25-('Debt'!CJ15-'Debt'!CI15+'Debt'!CJ16-'Debt'!CI16)+'Debt'!CJ45+'Debt'!CJ46+CJ16</f>
         <v>3193.8188300401507</v>
       </c>
       <c r="CK61" s="32">
-        <f>-CK55-('Debt'!CK15-'Debt'!CJ15+'Debt'!CK16-'Debt'!CJ16)+'Debt'!CK45+'Debt'!CK46+CK16</f>
+        <f>-CK55-CK25-('Debt'!CK15-'Debt'!CJ15+'Debt'!CK16-'Debt'!CJ16)+'Debt'!CK45+'Debt'!CK46+CK16</f>
         <v>3193.8188300401507</v>
       </c>
       <c r="CL61" s="32">
-        <f>-CL55-('Debt'!CL15-'Debt'!CK15+'Debt'!CL16-'Debt'!CK16)+'Debt'!CL45+'Debt'!CL46+CL16</f>
+        <f>-CL55-CL25-('Debt'!CL15-'Debt'!CK15+'Debt'!CL16-'Debt'!CK16)+'Debt'!CL45+'Debt'!CL46+CL16</f>
         <v>3800.288402540151</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="47" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D63" s="15">
         <f>(1+IRR(E57:CL57,0.020547644500372275))^4-1</f>
@@ -37391,10 +37758,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="47" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D64" s="15">
         <f>(1+IRR(E56:CL56,0.018842248557486396))^4-1</f>
@@ -37403,10 +37770,10 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="47" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D65" s="15">
         <f>(1+IRR(E59:CL59,0.03784631241217884))^4-1</f>
@@ -37415,10 +37782,10 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="47" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D66" s="15">
         <f>(1+IRR(E58:CL58,0.03126734292077549))^4-1</f>
@@ -37427,10 +37794,10 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="47" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D67" s="15">
         <f>(1+IRR(E60:CL60,0.024425729620145553))^4-1</f>
@@ -37439,10 +37806,10 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="47" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D68" s="15">
         <f>(1+IRR(E61:CL61,0.01682783163204693))^4-1</f>
@@ -37451,16 +37818,16 @@
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" s="38" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="73" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
@@ -37552,15 +37919,15 @@
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" s="38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="34" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D75" s="46">
         <f>'입력값'!C17</f>
@@ -37569,10 +37936,10 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="34" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C76" s="45" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D76" s="46">
         <f>'입력값'!C25</f>
@@ -37581,36 +37948,36 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="34" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C77" s="45" t="s">
-        <v>415</v>
-      </c>
-      <c r="D77" s="66">
+        <v>418</v>
+      </c>
+      <c r="D77" s="67">
         <f>'입력값'!C26</f>
         <v>1.1</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="34" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C78" s="45" t="s">
-        <v>417</v>
-      </c>
-      <c r="D78" s="66">
+        <v>420</v>
+      </c>
+      <c r="D78" s="67">
         <f>'입력값'!C27</f>
         <v>1.15</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="34" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C79" s="45" t="s">
-        <v>419</v>
-      </c>
-      <c r="D79" s="67">
+        <v>422</v>
+      </c>
+      <c r="D79" s="68">
         <f>'입력값'!C28</f>
         <v>2</v>
       </c>
@@ -37626,7 +37993,7 @@
   <sheetPr>
     <tabColor rgb="FF14483A"/>
   </sheetPr>
-  <dimension ref="A1:CM33"/>
+  <dimension ref="A1:CM34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -38092,55 +38459,67 @@
         <v>48</v>
       </c>
       <c r="D28" s="14">
-        <f>MIN('CF(Q)'!E17:CL17)</f>
+        <f>'CF(Q)'!D25</f>
         <v>0</v>
       </c>
       <c r="E28" s="18" t="str">
-        <f>IF(D28&gt;=-1,"운영자금 충족 (OK)","경고: 운영 중 현금 부족 — 추가 출자·브리지가 필요하고 위 Equity IRR 은 과대평가된 값입니다")</f>
-        <v>운영자금 충족 (OK)</v>
+        <f>IF(D28&lt;=1,"추가 출자 없음 (OK)","경고: 영업현금으로 원리금을 못 덮는 분기가 있어 주주가 이 금액을 더 넣어야 합니다 — 위 Equity IRR 에 이미 유출로 반영됨")</f>
+        <v>추가 출자 없음 (OK)</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
         <v>49</v>
       </c>
       <c r="D29" s="14">
-        <f>'Revenue'!D14</f>
-        <v>405788.8886999999</v>
+        <f>MIN('CF(Q)'!E17:CL17)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30" s="14">
-        <f>'Opex'!D10</f>
-        <v>106510.04740942549</v>
+        <f>'Revenue'!D14</f>
+        <v>405788.8886999999</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D31" s="14">
-        <f>'Debt'!D45</f>
-        <v>68428.74</v>
+        <f>'Opex'!D10</f>
+        <v>106510.04740942549</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D32" s="14">
-        <f>-'IS(Q)'!D28</f>
-        <v>18618.801256538776</v>
+        <f>'Debt'!D45</f>
+        <v>68428.74</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D33" s="14">
+        <f>-'IS(Q)'!D28</f>
+        <v>18618.801256538776</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="14">
         <f>'CF(Q)'!D16</f>
         <v>80440.30003403581</v>
       </c>

--- a/contract/sample-output.xlsx
+++ b/contract/sample-output.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="425">
   <si>
     <t>샘플 태양광 100MW</t>
   </si>
@@ -157,6 +157,12 @@
   </si>
   <si>
     <t>출자자+대주단 합산 — 자본·대출 투입 vs 원리금·이자·배당 회수 (원본 IRR 시트 정의)</t>
+  </si>
+  <si>
+    <t>Project IRR 세후(무차입 기준) [%]</t>
+  </si>
+  <si>
+    <t>참고값(스냅샷) — 차입이 없다고 보고 법인세를 다시 계산한 교과서 정의. 레버리지 효과는 Equity IRR 세후와 이 값을 비교하세요</t>
   </si>
   <si>
     <t>최소 단순DSCR(연 합산) [x]</t>
@@ -1907,12 +1913,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2015,7 +2021,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" s="20">
         <v>100</v>
@@ -2023,7 +2029,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" s="21">
         <v>1410.69</v>
@@ -2031,7 +2037,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" s="21">
         <v>150.03</v>
@@ -2039,7 +2045,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" s="22">
         <v>154.8</v>
@@ -2047,7 +2053,7 @@
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C11" s="23">
         <v>0</v>
@@ -2055,7 +2061,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="23">
         <v>0.5</v>
@@ -2063,7 +2069,7 @@
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="23">
         <v>0</v>
@@ -2071,7 +2077,7 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" s="24">
         <v>3.77</v>
@@ -2079,7 +2085,7 @@
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15" s="23">
         <v>95</v>
@@ -2087,7 +2093,7 @@
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C16" s="25">
         <v>20</v>
@@ -2095,7 +2101,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C17" s="21">
         <v>20</v>
@@ -2103,7 +2109,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C18" s="21">
         <v>49.8</v>
@@ -2111,7 +2117,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C19" s="23">
         <v>0.7</v>
@@ -2119,7 +2125,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C20" s="23">
         <v>0</v>
@@ -2127,7 +2133,7 @@
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C21" s="21">
         <v>0</v>
@@ -2135,7 +2141,7 @@
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" s="21">
         <v>0</v>
@@ -2143,7 +2149,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" s="21">
         <v>50</v>
@@ -2151,7 +2157,7 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C24" s="26">
         <v>6</v>
@@ -2159,7 +2165,7 @@
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C25" s="21">
         <v>10</v>
@@ -2167,7 +2173,7 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C26" s="27">
         <v>1.1</v>
@@ -2175,7 +2181,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C27" s="27">
         <v>1.15</v>
@@ -2183,7 +2189,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C28" s="28">
         <v>2</v>
@@ -2191,7 +2197,7 @@
     </row>
     <row r="30" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -2286,7 +2292,7 @@
     <row r="31" spans="2:2" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C32" s="23">
         <v>80</v>
@@ -2294,7 +2300,7 @@
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C33" s="23">
         <v>0</v>
@@ -2302,7 +2308,7 @@
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C34" s="23">
         <v>0</v>
@@ -2310,7 +2316,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C35" s="23">
         <v>10</v>
@@ -2318,7 +2324,7 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" s="23">
         <v>0</v>
@@ -2326,7 +2332,7 @@
     </row>
     <row r="38" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -2420,33 +2426,33 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G40" s="29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H40" s="29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I40" s="29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C41" s="21">
         <v>855.35</v>
@@ -2472,7 +2478,7 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C42" s="21">
         <v>492.56</v>
@@ -2498,7 +2504,7 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C43" s="32">
         <f>C9</f>
@@ -2510,7 +2516,7 @@
     </row>
     <row r="45" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -2604,279 +2610,279 @@
     </row>
     <row r="47" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B47" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G47" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H47" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I47" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K47" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L47" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M47" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N47" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O47" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P47" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q47" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R47" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S47" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T47" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U47" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V47" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W47" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X47" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y47" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z47" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA47" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB47" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC47" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD47" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AE47" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF47" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG47" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AH47" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AI47" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ47" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK47" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL47" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM47" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN47" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO47" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP47" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AQ47" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR47" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AS47" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AT47" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU47" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV47" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AW47" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX47" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AY47" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AZ47" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BA47" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BB47" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC47" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BD47" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE47" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF47" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BG47" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BH47" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BI47" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ47" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BK47" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL47" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BM47" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN47" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BO47" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BP47" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BQ47" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BR47" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BS47" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BT47" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BU47" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BV47" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BW47" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BX47" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BY47" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BZ47" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CA47" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CB47" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CC47" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD47" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CE47" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CF47" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CG47" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CH47" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CI47" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CJ47" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="CK47" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="CL47" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D49" s="36">
         <f>SUM(E49:CL49)</f>
@@ -2903,7 +2909,7 @@
     </row>
     <row r="51" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -2997,15 +3003,15 @@
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C54" s="23">
         <v>60</v>
@@ -3013,7 +3019,7 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="19" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C55" s="23">
         <v>40</v>
@@ -3021,12 +3027,12 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="38" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -3055,12 +3061,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -3154,36 +3160,36 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D6" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="I6" s="29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C7" s="32">
         <f>'입력값'!C9*100</f>
@@ -3192,14 +3198,14 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C8" s="32">
         <f>'입력값'!C41*100</f>
         <v>85535</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E8" s="40">
         <f>'입력값'!D41</f>
@@ -3222,19 +3228,19 @@
         <v>1</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" s="32">
         <f>'입력값'!C42*100</f>
         <v>49256</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E9" s="40">
         <f>'입력값'!D42</f>
@@ -3257,12 +3263,12 @@
         <v>1</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="42" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C10" s="43">
         <f>C8+C9</f>
@@ -3271,7 +3277,7 @@
     </row>
     <row r="12" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -3365,7 +3371,7 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="32" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C14" s="32">
         <f>'Debt'!D12</f>
@@ -3374,7 +3380,7 @@
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="32" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C15" s="32">
         <f>$D$30*100+'Debt'!D12</f>
@@ -3383,7 +3389,7 @@
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C16" s="32">
         <f>'입력값'!C8*100</f>
@@ -3392,7 +3398,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C17" s="32">
         <f>$D$30*100+$D$32*100+'Debt'!D12</f>
@@ -3401,7 +3407,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C18" s="32">
         <f>$D$31*100+$D$33*100+$D$34*100</f>
@@ -3410,7 +3416,7 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C19" s="14">
         <f>C18-C17</f>
@@ -3423,7 +3429,7 @@
     </row>
     <row r="21" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
@@ -3517,16 +3523,16 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
@@ -3563,11 +3569,11 @@
     </row>
     <row r="28" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="44" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -3659,15 +3665,15 @@
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D30" s="46">
         <f>'입력값'!C8</f>
@@ -3676,10 +3682,10 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D31" s="46">
         <f>'입력값'!C9</f>
@@ -3688,10 +3694,10 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="34" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D32" s="46">
         <f>'입력값'!C23</f>
@@ -3700,10 +3706,10 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D33" s="46">
         <f>'입력값'!C41</f>
@@ -3712,10 +3718,10 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D34" s="46">
         <f>'입력값'!C42</f>
@@ -3749,12 +3755,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -3848,279 +3854,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(E8:CL8)</f>
@@ -4393,10 +4399,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(E9:CL9)</f>
@@ -4664,10 +4670,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>233</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>231</v>
       </c>
       <c r="D10" s="32">
         <f>SUM(E10:CL10)</f>
@@ -4939,10 +4945,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="34" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D11" s="32">
         <f>SUM(E11:CL11)</f>
@@ -5214,10 +5220,10 @@
     </row>
     <row r="12" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B12" s="47" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D12" s="14">
         <f>SUM(E12:CL12)</f>
@@ -5570,10 +5576,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E13" s="32">
         <f>E8+E9+E12</f>
@@ -5922,10 +5928,10 @@
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E14" s="32">
         <f>MIN(MAX(E13-(0),0),$D$57*100)*($D$57*100)/IF(($D$57*100)=0,1,$D$57*100)</f>
@@ -6274,10 +6280,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E15" s="32">
         <f>MIN(MAX(E13-($D$57*100),0),$D$58*100+$D$61*100)*($D$58*100)/IF(($D$58*100+$D$61*100)=0,1,$D$58*100+$D$61*100)</f>
@@ -6626,10 +6632,10 @@
     </row>
     <row r="16" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E16" s="32">
         <f>MIN(MAX(E13-($D$57*100),0),$D$58*100+$D$61*100)*($D$61*100)/IF(($D$58*100+$D$61*100)=0,1,$D$58*100+$D$61*100)</f>
@@ -6978,7 +6984,7 @@
     </row>
     <row r="19" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -7072,276 +7078,276 @@
     </row>
     <row r="21" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B21" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F21" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H21" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L21" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M21" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O21" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P21" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q21" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R21" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S21" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T21" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U21" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V21" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W21" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X21" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y21" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z21" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA21" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB21" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC21" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD21" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AE21" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF21" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG21" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AH21" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AI21" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK21" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL21" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM21" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN21" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO21" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP21" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AQ21" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR21" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AS21" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AT21" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU21" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV21" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AW21" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX21" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AY21" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AZ21" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BA21" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BB21" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC21" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BD21" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE21" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF21" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BG21" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BH21" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BI21" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ21" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BK21" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL21" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BM21" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN21" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BO21" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BP21" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BQ21" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BR21" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BS21" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BT21" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BU21" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BV21" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BW21" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BX21" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BY21" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BZ21" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CA21" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CB21" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CC21" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD21" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CE21" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CF21" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CG21" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CH21" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CI21" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CJ21" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="CK21" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="CL21" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B23" s="48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C23" s="49"/>
       <c r="D23" s="49"/>
@@ -7435,10 +7441,10 @@
     </row>
     <row r="24" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E24" s="32">
         <v>0</v>
@@ -7786,10 +7792,10 @@
     </row>
     <row r="25" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D25" s="32">
         <f>SUM(E25:CL25)</f>
@@ -8142,10 +8148,10 @@
     </row>
     <row r="26" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D26" s="32">
         <f>SUM(E26:CL26)</f>
@@ -8498,10 +8504,10 @@
     </row>
     <row r="27" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D27" s="14">
         <f>SUM(E27:CL27)</f>
@@ -8848,10 +8854,10 @@
     </row>
     <row r="28" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D28" s="14">
         <f>SUM(E28:CL28)</f>
@@ -9182,10 +9188,10 @@
     </row>
     <row r="29" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B29" s="47" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E29" s="14">
         <f>E24+E25-E28</f>
@@ -9534,10 +9540,10 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D30" s="32">
         <f>CL29</f>
@@ -9550,7 +9556,7 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F31" s="50" t="str">
         <f>IF(AND(E15&lt;1,F15&gt;1),"인출 시작 분기 일치 (OK)","경고: 첫 인출 분기가 생성 당시(2024-09-30)와 달라졌습니다. 상환 스케줄이 들어간 열은 고정이라 실제와 어긋납니다 — 화면(HTML)에서 다시 생성하세요.")</f>
@@ -9559,7 +9565,7 @@
     </row>
     <row r="33" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B33" s="48" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C33" s="49"/>
       <c r="D33" s="49"/>
@@ -9653,10 +9659,10 @@
     </row>
     <row r="34" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E34" s="32">
         <v>0</v>
@@ -10004,10 +10010,10 @@
     </row>
     <row r="35" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B35" s="34" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D35" s="32">
         <f>SUM(E35:CL35)</f>
@@ -10360,10 +10366,10 @@
     </row>
     <row r="36" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D36" s="32">
         <f>SUM(E36:CL36)</f>
@@ -10716,10 +10722,10 @@
     </row>
     <row r="37" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D37" s="14">
         <f>SUM(E37:CL37)</f>
@@ -11066,10 +11072,10 @@
     </row>
     <row r="38" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D38" s="14">
         <f>SUM(E38:CL38)</f>
@@ -11400,10 +11406,10 @@
     </row>
     <row r="39" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B39" s="47" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E39" s="14">
         <f>E34+E35-E38</f>
@@ -11752,10 +11758,10 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D40" s="32">
         <f>CL39</f>
@@ -11768,7 +11774,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F41" s="50" t="str">
         <f>IF(AND(E16&lt;1,F16&gt;1),"인출 시작 분기 일치 (OK)","경고: 첫 인출 분기가 생성 당시(2024-09-30)와 달라졌습니다. 상환 스케줄이 들어간 열은 고정이라 실제와 어긋납니다 — 화면(HTML)에서 다시 생성하세요.")</f>
@@ -11777,7 +11783,7 @@
     </row>
     <row r="43" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
@@ -11871,10 +11877,10 @@
     </row>
     <row r="44" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E44" s="32">
         <f>E24+E34</f>
@@ -12223,10 +12229,10 @@
     </row>
     <row r="45" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B45" s="34" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D45" s="14">
         <f>SUM(E45:CL45)</f>
@@ -12579,10 +12585,10 @@
     </row>
     <row r="46" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D46" s="14">
         <f>SUM(E46:CL46)</f>
@@ -12935,10 +12941,10 @@
     </row>
     <row r="47" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B47" s="48" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D47" s="43">
         <f>SUM(E47:CL47)</f>
@@ -13292,10 +13298,10 @@
     </row>
     <row r="48" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B48" s="34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E48" s="32">
         <f>E29+E39</f>
@@ -13644,10 +13650,10 @@
     </row>
     <row r="50" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B50" s="34" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E50" s="32">
         <f>0</f>
@@ -13996,10 +14002,10 @@
     </row>
     <row r="51" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B51" s="34" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E51" s="32">
         <f>E50</f>
@@ -14348,11 +14354,11 @@
     </row>
     <row r="54" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B54" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="44" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -14444,15 +14450,15 @@
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="34" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D56" s="46">
         <f>'입력값'!C8</f>
@@ -14461,10 +14467,10 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D57" s="46">
         <f>'입력값'!C9</f>
@@ -14473,10 +14479,10 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D58" s="46">
         <f>'입력값'!C41</f>
@@ -14485,10 +14491,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D59" s="52">
         <f>'입력값'!D41</f>
@@ -14497,10 +14503,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D60" s="52">
         <f>'입력값'!E41</f>
@@ -14509,10 +14515,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D61" s="46">
         <f>'입력값'!C42</f>
@@ -14521,10 +14527,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D62" s="52">
         <f>'입력값'!D42</f>
@@ -14533,10 +14539,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D63" s="52">
         <f>'입력값'!E42</f>
@@ -14545,10 +14551,10 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="34" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E64" s="53">
         <f>'입력값'!E49</f>
@@ -14602,12 +14608,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -14701,279 +14707,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E8" s="54">
         <v>0</v>
@@ -15236,10 +15242,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E9" s="55">
         <v>0</v>
@@ -15502,10 +15508,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D11" s="56">
         <f>SUM(E11:CL11)</f>
@@ -15858,10 +15864,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="57"/>
@@ -16192,10 +16198,10 @@
     </row>
     <row r="14" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B14" s="48" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D14" s="43">
         <f>SUM(E14:CL14)</f>
@@ -16543,7 +16549,7 @@
     </row>
     <row r="16" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -16637,10 +16643,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E18" s="32">
         <f>MIN(1,3)/3*E14</f>
@@ -16988,10 +16994,10 @@
     </row>
     <row r="19" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B19" s="48" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D19" s="43">
         <f>SUM(E19:CL19)</f>
@@ -17345,16 +17351,16 @@
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="38" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="44" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -17446,15 +17452,15 @@
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="34" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D25" s="58">
         <f>'입력값'!C7</f>
@@ -17463,10 +17469,10 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D26" s="59">
         <f>'입력값'!C10</f>
@@ -17475,10 +17481,10 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D27" s="60">
         <f>'입력값'!C11</f>
@@ -17487,10 +17493,10 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D28" s="60">
         <f>'입력값'!C12</f>
@@ -17499,10 +17505,10 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="34" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D29" s="60">
         <f>'입력값'!C13</f>
@@ -17511,10 +17517,10 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D30" s="61">
         <f>'입력값'!C14</f>
@@ -17548,12 +17554,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -17647,279 +17653,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(E8:CL8)</f>
@@ -18266,10 +18272,10 @@
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(E9:CL9)</f>
@@ -18616,10 +18622,10 @@
     </row>
     <row r="10" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B10" s="48" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D10" s="43">
         <f>SUM(E10:CL10)</f>
@@ -18973,16 +18979,16 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="38" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="44" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -19074,15 +19080,15 @@
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D17" s="46">
         <f>'입력값'!C18</f>
@@ -19091,10 +19097,10 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D18" s="60">
         <f>'입력값'!C19</f>
@@ -19103,10 +19109,10 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D19" s="60">
         <f>'입력값'!C20</f>
@@ -19140,12 +19146,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -19239,279 +19245,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B8" s="47" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D8" s="14">
         <f>SUM(E8:CL8)</f>
@@ -19864,10 +19870,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="47" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D10" s="14">
         <f>SUM(E10:CL10)</f>
@@ -20220,10 +20226,10 @@
     </row>
     <row r="12" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B12" s="48" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D12" s="43">
         <f>SUM(E12:CL12)</f>
@@ -20577,10 +20583,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E13" s="40" t="str">
         <f>IF(E8&lt;=0,"",E12/E8)</f>
@@ -20929,10 +20935,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D15" s="32">
         <f>SUM(E15:CL15)</f>
@@ -21279,10 +21285,10 @@
     </row>
     <row r="16" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D16" s="32">
         <f>SUM(E16:CL16)</f>
@@ -21629,10 +21635,10 @@
     </row>
     <row r="17" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D17" s="32">
         <f>SUM(E17:CL17)</f>
@@ -21979,10 +21985,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D18" s="32">
         <f>SUM(E18:CL18)</f>
@@ -22329,10 +22335,10 @@
     </row>
     <row r="19" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B19" s="47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D19" s="14">
         <f>SUM(E19:CL19)</f>
@@ -22685,10 +22691,10 @@
     </row>
     <row r="20" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E20" s="40" t="str">
         <f>IF(E8&lt;=0,"",E19/E8)</f>
@@ -23037,15 +23043,15 @@
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="47" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D23" s="32">
         <f>SUM(E23:CL23)</f>
@@ -23398,10 +23404,10 @@
     </row>
     <row r="24" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B24" s="34" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D24" s="32">
         <f>SUM(E24:CL24)</f>
@@ -23754,10 +23760,10 @@
     </row>
     <row r="25" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B25" s="47" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D25" s="14">
         <f>SUM(E25:CL25)</f>
@@ -24110,10 +24116,10 @@
     </row>
     <row r="27" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B27" s="47" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D27" s="14">
         <f>SUM(E27:CL27)</f>
@@ -24466,10 +24472,10 @@
     </row>
     <row r="28" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D28" s="32">
         <f>SUM(E28:CL28)</f>
@@ -24822,10 +24828,10 @@
     </row>
     <row r="29" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B29" s="48" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D29" s="43">
         <f>SUM(E29:CL29)</f>
@@ -25179,7 +25185,7 @@
     </row>
     <row r="32" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -25273,10 +25279,10 @@
     </row>
     <row r="34" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D34" s="32">
         <f>SUM(E34:CL34)</f>
@@ -25629,7 +25635,7 @@
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E36" s="13">
         <v>2024</v>
@@ -25700,10 +25706,10 @@
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E37" s="32">
         <f>E34+F34+G34</f>
@@ -25796,10 +25802,10 @@
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E38" s="32">
         <f>0</f>
@@ -25892,10 +25898,10 @@
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" s="34" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E39" s="32">
         <f>IF(E37&lt;=0,0,MIN(E38,E37*$D$63/100))</f>
@@ -25988,10 +25994,10 @@
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E40" s="32">
         <f>IF(E37&lt;=0,E38-E37,E38-E39)</f>
@@ -26084,10 +26090,10 @@
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E41" s="32">
         <f>MAX(0,E37-E39)</f>
@@ -26180,10 +26186,10 @@
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E42" s="32">
         <f>IF(E37&lt;=0,0,MIN(MAX(E41,0),200)*0.09+MIN(MAX(E41-200,0),19800)*0.19+MIN(MAX(E41-20000,0),280000)*0.21+MAX(E41-300000,0)*0.24)</f>
@@ -26276,10 +26282,10 @@
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E43" s="32">
         <f>E41*$D$64/100</f>
@@ -26372,10 +26378,10 @@
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B44" s="34" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E44" s="32">
         <f>0</f>
@@ -26468,10 +26474,10 @@
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" s="34" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E45" s="32">
         <f>(0)*$D$65/100</f>
@@ -26564,10 +26570,10 @@
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E46" s="32">
         <f>MAX(0,E42-(E44+E45))</f>
@@ -26660,10 +26666,10 @@
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" s="34" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E47" s="32">
         <f>IF(E37&lt;=0,0,MAX(E43,E46))</f>
@@ -26756,10 +26762,10 @@
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" s="34" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E48" s="32">
         <f>E42-E47</f>
@@ -26852,10 +26858,10 @@
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" s="34" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E49" s="32">
         <f>E44+E45-E48</f>
@@ -26948,10 +26954,10 @@
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" s="47" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E50" s="14">
         <f>E47*(1+$D$66/100)+E48*$D$67/100</f>
@@ -27044,10 +27050,10 @@
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" s="34" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E51" s="32">
         <f>MAX(0,E27)+MAX(0,F27)+MAX(0,G27)</f>
@@ -27140,16 +27146,16 @@
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="38" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="44" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -27241,15 +27247,15 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D58" s="60">
         <f>'입력값'!C15</f>
@@ -27258,10 +27264,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D59" s="62">
         <f>'입력값'!C16</f>
@@ -27270,10 +27276,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D60" s="46">
         <f>'입력값'!C17</f>
@@ -27282,10 +27288,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D61" s="46">
         <f>'입력값'!C21</f>
@@ -27294,10 +27300,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D62" s="46">
         <f>'입력값'!C22</f>
@@ -27306,10 +27312,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="34" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D63" s="60">
         <f>'입력값'!C32</f>
@@ -27318,10 +27324,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="34" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D64" s="60">
         <f>'입력값'!C33</f>
@@ -27330,10 +27336,10 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="34" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D65" s="60">
         <f>'입력값'!C34</f>
@@ -27342,10 +27348,10 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="34" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C66" s="45" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D66" s="60">
         <f>'입력값'!C35</f>
@@ -27354,10 +27360,10 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="34" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C67" s="45" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D67" s="60">
         <f>'입력값'!C36</f>
@@ -27391,12 +27397,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -27490,279 +27496,279 @@
     </row>
     <row r="6" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B6" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q6" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T6" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U6" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA6" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB6" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC6" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD6" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AE6" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF6" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG6" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AH6" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AI6" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ6" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK6" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM6" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN6" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO6" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP6" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AQ6" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR6" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AS6" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AT6" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU6" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV6" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AW6" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX6" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AY6" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AZ6" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BA6" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BB6" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC6" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BD6" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE6" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF6" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BG6" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BH6" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BI6" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ6" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BK6" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL6" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN6" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BO6" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BP6" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BQ6" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BR6" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BS6" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BT6" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BU6" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BV6" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BW6" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BX6" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BY6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BZ6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CA6" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CB6" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CC6" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD6" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CE6" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CF6" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CG6" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CH6" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CI6" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CJ6" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="CK6" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="CL6" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B9" s="48" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D9" s="43">
         <f>SUM(E9:CL9)</f>
@@ -28116,10 +28122,10 @@
     </row>
     <row r="10" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B10" s="34" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D10" s="32">
         <f>SUM(E10:CL10)</f>
@@ -28472,10 +28478,10 @@
     </row>
     <row r="11" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -28770,10 +28776,10 @@
     </row>
     <row r="13" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B13" s="47" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D13" s="14">
         <f>SUM(E13:CL13)</f>
@@ -29126,10 +29132,10 @@
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B14" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D14" s="32">
         <f>SUM(E14:CL14)</f>
@@ -29482,10 +29488,10 @@
     </row>
     <row r="15" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E15" s="32">
         <f>0</f>
@@ -29834,10 +29840,10 @@
     </row>
     <row r="16" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B16" s="48" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D16" s="43">
         <f>SUM(E16:CL16)</f>
@@ -30191,10 +30197,10 @@
     </row>
     <row r="17" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B17" s="34" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E17" s="32">
         <f>E18-E16+E25</f>
@@ -30543,10 +30549,10 @@
     </row>
     <row r="18" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B18" s="34" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E18" s="32">
         <f>E15+E13</f>
@@ -30895,10 +30901,10 @@
     </row>
     <row r="19" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E19" s="32">
         <v>0</v>
@@ -31161,10 +31167,10 @@
     </row>
     <row r="20" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E20" s="32">
         <f>0</f>
@@ -31513,10 +31519,10 @@
     </row>
     <row r="21" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B21" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E21" s="32">
         <f>E20</f>
@@ -31865,10 +31871,10 @@
     </row>
     <row r="22" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B22" s="34" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E22" s="32">
         <f>0</f>
@@ -32217,10 +32223,10 @@
     </row>
     <row r="23" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B23" s="34" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E23" s="32">
         <f>0</f>
@@ -32569,10 +32575,10 @@
     </row>
     <row r="24" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="64">
@@ -32923,10 +32929,10 @@
     </row>
     <row r="25" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B25" s="48" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D25" s="43">
         <f>SUM(E25:CL25)</f>
@@ -33280,7 +33286,7 @@
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B26" s="34" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E26" s="13">
         <v>2025</v>
@@ -33339,10 +33345,10 @@
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" s="34" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E27" s="32">
         <f>K10</f>
@@ -33419,10 +33425,10 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" s="34" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E28" s="32">
         <f>K9</f>
@@ -33499,10 +33505,10 @@
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" s="34" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E29" s="66">
         <f>IF(E27=0,"",E28/E27)</f>
@@ -33579,10 +33585,10 @@
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B30" s="34" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E30" s="66">
         <f>IF(E27=0,"",(H15+H20+E28)/E27)</f>
@@ -33659,111 +33665,111 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="34" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="34" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="34" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="34" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="34" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="34" t="s">
+        <v>390</v>
+      </c>
+      <c r="C37" s="35" t="s">
         <v>388</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="34" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="34" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="34" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="34" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -33857,10 +33863,10 @@
     </row>
     <row r="46" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B46" s="34" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E46" s="32">
         <f>0</f>
@@ -34209,10 +34215,10 @@
     </row>
     <row r="47" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B47" s="47" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D47" s="17">
         <f>MIN(E29:V29)</f>
@@ -34565,10 +34571,10 @@
     </row>
     <row r="48" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B48" s="47" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D48" s="17">
         <f>MIN(E30:V30)</f>
@@ -34903,10 +34909,10 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="47" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D49" s="14">
         <f>CL17</f>
@@ -34915,7 +34921,7 @@
     </row>
     <row r="51" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -35009,279 +35015,279 @@
     </row>
     <row r="53" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B53" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G53" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H53" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I53" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L53" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M53" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N53" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O53" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P53" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q53" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R53" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S53" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T53" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U53" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V53" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W53" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X53" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y53" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z53" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA53" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB53" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AC53" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AD53" s="33" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AE53" s="33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF53" s="33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG53" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AH53" s="33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AI53" s="33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ53" s="33" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK53" s="33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL53" s="33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AM53" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN53" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AO53" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AP53" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AQ53" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR53" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AS53" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AT53" s="33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU53" s="33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV53" s="33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AW53" s="33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX53" s="33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AY53" s="33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AZ53" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BA53" s="33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BB53" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BC53" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BD53" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE53" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF53" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BG53" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BH53" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BI53" s="33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ53" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BK53" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL53" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BM53" s="33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN53" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BO53" s="33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BP53" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BQ53" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BR53" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BS53" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BT53" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BU53" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BV53" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="BW53" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="BX53" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BY53" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BZ53" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="CA53" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CB53" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CC53" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD53" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CE53" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="CF53" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="CG53" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="CH53" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CI53" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CJ53" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="CK53" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="CL53" s="33" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D55" s="32">
         <f>SUM(E55:CL55)</f>
@@ -35634,10 +35640,10 @@
     </row>
     <row r="56" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B56" s="34" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E56" s="32">
         <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E28+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
@@ -35986,10 +35992,10 @@
     </row>
     <row r="57" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B57" s="34" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E57" s="32">
         <f>'Revenue'!E14-'Opex'!E10+'IS(Q)'!E18+'Revenue'!E19-('Debt'!E8)</f>
@@ -36338,10 +36344,10 @@
     </row>
     <row r="58" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B58" s="34" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E58" s="32">
         <f>E13-E55-E25</f>
@@ -36690,10 +36696,10 @@
     </row>
     <row r="59" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B59" s="34" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E59" s="32">
         <f>E13-'IS(Q)'!E28-E19-E55-E25</f>
@@ -37042,10 +37048,10 @@
     </row>
     <row r="60" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B60" s="34" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E60" s="32">
         <f>E16-E55-E25</f>
@@ -37394,10 +37400,10 @@
     </row>
     <row r="61" spans="2:90" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E61" s="32">
         <f>-E55-E25-('Debt'!E15+'Debt'!E16)+'Debt'!E45+'Debt'!E46+E16</f>
@@ -37746,10 +37752,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="47" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D63" s="15">
         <f>(1+IRR(E57:CL57,0.020547644500372275))^4-1</f>
@@ -37758,10 +37764,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="47" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D64" s="15">
         <f>(1+IRR(E56:CL56,0.018842248557486396))^4-1</f>
@@ -37770,10 +37776,10 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="47" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D65" s="15">
         <f>(1+IRR(E59:CL59,0.03784631241217884))^4-1</f>
@@ -37782,10 +37788,10 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="47" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D66" s="15">
         <f>(1+IRR(E58:CL58,0.03126734292077549))^4-1</f>
@@ -37794,10 +37800,10 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="47" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D67" s="15">
         <f>(1+IRR(E60:CL60,0.024425729620145553))^4-1</f>
@@ -37806,10 +37812,10 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="47" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D68" s="15">
         <f>(1+IRR(E61:CL61,0.01682783163204693))^4-1</f>
@@ -37818,16 +37824,16 @@
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" s="38" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="73" spans="2:91" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="44" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
@@ -37919,15 +37925,15 @@
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" s="38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="34" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C75" s="45" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D75" s="46">
         <f>'입력값'!C17</f>
@@ -37936,10 +37942,10 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="34" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C76" s="45" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D76" s="46">
         <f>'입력값'!C25</f>
@@ -37948,10 +37954,10 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="34" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C77" s="45" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D77" s="67">
         <f>'입력값'!C26</f>
@@ -37960,10 +37966,10 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="34" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C78" s="45" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D78" s="67">
         <f>'입력값'!C27</f>
@@ -37972,10 +37978,10 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="34" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C79" s="45" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D79" s="68">
         <f>'입력값'!C28</f>
@@ -37993,7 +37999,7 @@
   <sheetPr>
     <tabColor rgb="FF14483A"/>
   </sheetPr>
-  <dimension ref="A1:CM34"/>
+  <dimension ref="A1:CM35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -38436,90 +38442,101 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="17">
-        <f>'CF(Q)'!D47</f>
-        <v>1.0073021924292676</v>
+      <c r="D26" s="15">
+        <v>0.0687888112840489</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D27" s="17">
+        <f>'CF(Q)'!D47</f>
+        <v>1.0073021924292676</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="17">
         <f>'CF(Q)'!D48</f>
         <v>1.187143523658971</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="14">
-        <f>'CF(Q)'!D25</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="18" t="str">
-        <f>IF(D28&lt;=1,"추가 출자 없음 (OK)","경고: 영업현금으로 원리금을 못 덮는 분기가 있어 주주가 이 금액을 더 넣어야 합니다 — 위 Equity IRR 에 이미 유출로 반영됨")</f>
-        <v>추가 출자 없음 (OK)</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29" s="14">
-        <f>MIN('CF(Q)'!E17:CL17)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>50</v>
+        <f>'CF(Q)'!D25</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="18" t="str">
+        <f>IF(D29&lt;=1,"추가 출자 없음 (OK)","경고: 영업현금으로 원리금을 못 덮는 분기가 있어 주주가 이 금액을 더 넣어야 합니다 — 위 Equity IRR 에 이미 유출로 반영됨")</f>
+        <v>추가 출자 없음 (OK)</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D30" s="14">
-        <f>'Revenue'!D14</f>
-        <v>405788.8886999999</v>
+        <f>MIN('CF(Q)'!E17:CL17)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D31" s="14">
-        <f>'Opex'!D10</f>
-        <v>106510.04740942549</v>
+        <f>'Revenue'!D14</f>
+        <v>405788.8886999999</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D32" s="14">
-        <f>'Debt'!D45</f>
-        <v>68428.74</v>
+        <f>'Opex'!D10</f>
+        <v>106510.04740942549</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D33" s="14">
-        <f>-'IS(Q)'!D28</f>
-        <v>18618.801256538776</v>
+        <f>'Debt'!D45</f>
+        <v>68428.74</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D34" s="14">
+        <f>-'IS(Q)'!D28</f>
+        <v>18618.801256538776</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="14">
         <f>'CF(Q)'!D16</f>
         <v>80440.30003403581</v>
       </c>
